--- a/automation/Test Results/Excel/Unit_Test_Cases.xlsx
+++ b/automation/Test Results/Excel/Unit_Test_Cases.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="611">
   <si>
     <t>Test ID</t>
   </si>
@@ -337,6 +337,606 @@
     <t>TC_APP_0570</t>
   </si>
   <si>
+    <t>TC_APP_0571</t>
+  </si>
+  <si>
+    <t>TC_APP_0572</t>
+  </si>
+  <si>
+    <t>TC_APP_0573</t>
+  </si>
+  <si>
+    <t>TC_APP_0574</t>
+  </si>
+  <si>
+    <t>TC_APP_0575</t>
+  </si>
+  <si>
+    <t>TC_APP_0576</t>
+  </si>
+  <si>
+    <t>TC_APP_0577</t>
+  </si>
+  <si>
+    <t>TC_APP_0578</t>
+  </si>
+  <si>
+    <t>TC_APP_0579</t>
+  </si>
+  <si>
+    <t>TC_APP_0580</t>
+  </si>
+  <si>
+    <t>TC_APP_0581</t>
+  </si>
+  <si>
+    <t>TC_APP_0582</t>
+  </si>
+  <si>
+    <t>TC_APP_0583</t>
+  </si>
+  <si>
+    <t>TC_APP_0584</t>
+  </si>
+  <si>
+    <t>TC_APP_0585</t>
+  </si>
+  <si>
+    <t>TC_APP_0586</t>
+  </si>
+  <si>
+    <t>TC_APP_0587</t>
+  </si>
+  <si>
+    <t>TC_APP_0588</t>
+  </si>
+  <si>
+    <t>TC_APP_0589</t>
+  </si>
+  <si>
+    <t>TC_APP_0590</t>
+  </si>
+  <si>
+    <t>TC_APP_0591</t>
+  </si>
+  <si>
+    <t>TC_APP_0592</t>
+  </si>
+  <si>
+    <t>TC_APP_0593</t>
+  </si>
+  <si>
+    <t>TC_APP_0594</t>
+  </si>
+  <si>
+    <t>TC_APP_0595</t>
+  </si>
+  <si>
+    <t>TC_APP_0596</t>
+  </si>
+  <si>
+    <t>TC_APP_0597</t>
+  </si>
+  <si>
+    <t>TC_APP_0598</t>
+  </si>
+  <si>
+    <t>TC_APP_0599</t>
+  </si>
+  <si>
+    <t>TC_APP_0600</t>
+  </si>
+  <si>
+    <t>TC_APP_0601</t>
+  </si>
+  <si>
+    <t>TC_APP_0602</t>
+  </si>
+  <si>
+    <t>TC_APP_0603</t>
+  </si>
+  <si>
+    <t>TC_APP_0604</t>
+  </si>
+  <si>
+    <t>TC_APP_0605</t>
+  </si>
+  <si>
+    <t>TC_APP_0606</t>
+  </si>
+  <si>
+    <t>TC_APP_0607</t>
+  </si>
+  <si>
+    <t>TC_APP_0608</t>
+  </si>
+  <si>
+    <t>TC_APP_0609</t>
+  </si>
+  <si>
+    <t>TC_APP_0610</t>
+  </si>
+  <si>
+    <t>TC_APP_0611</t>
+  </si>
+  <si>
+    <t>TC_APP_0612</t>
+  </si>
+  <si>
+    <t>TC_APP_0613</t>
+  </si>
+  <si>
+    <t>TC_APP_0614</t>
+  </si>
+  <si>
+    <t>TC_APP_0615</t>
+  </si>
+  <si>
+    <t>TC_APP_0616</t>
+  </si>
+  <si>
+    <t>TC_APP_0617</t>
+  </si>
+  <si>
+    <t>TC_APP_0618</t>
+  </si>
+  <si>
+    <t>TC_APP_0619</t>
+  </si>
+  <si>
+    <t>TC_APP_0620</t>
+  </si>
+  <si>
+    <t>TC_APP_0621</t>
+  </si>
+  <si>
+    <t>TC_APP_0622</t>
+  </si>
+  <si>
+    <t>TC_APP_0623</t>
+  </si>
+  <si>
+    <t>TC_APP_0624</t>
+  </si>
+  <si>
+    <t>TC_APP_0625</t>
+  </si>
+  <si>
+    <t>TC_APP_0626</t>
+  </si>
+  <si>
+    <t>TC_APP_0627</t>
+  </si>
+  <si>
+    <t>TC_APP_0628</t>
+  </si>
+  <si>
+    <t>TC_APP_0629</t>
+  </si>
+  <si>
+    <t>TC_APP_0630</t>
+  </si>
+  <si>
+    <t>TC_APP_0631</t>
+  </si>
+  <si>
+    <t>TC_APP_0632</t>
+  </si>
+  <si>
+    <t>TC_APP_0633</t>
+  </si>
+  <si>
+    <t>TC_APP_0634</t>
+  </si>
+  <si>
+    <t>TC_APP_0635</t>
+  </si>
+  <si>
+    <t>TC_APP_0636</t>
+  </si>
+  <si>
+    <t>TC_APP_0637</t>
+  </si>
+  <si>
+    <t>TC_APP_0638</t>
+  </si>
+  <si>
+    <t>TC_APP_0639</t>
+  </si>
+  <si>
+    <t>TC_APP_0640</t>
+  </si>
+  <si>
+    <t>TC_APP_0641</t>
+  </si>
+  <si>
+    <t>TC_APP_0642</t>
+  </si>
+  <si>
+    <t>TC_APP_0643</t>
+  </si>
+  <si>
+    <t>TC_APP_0644</t>
+  </si>
+  <si>
+    <t>TC_APP_0645</t>
+  </si>
+  <si>
+    <t>TC_APP_0646</t>
+  </si>
+  <si>
+    <t>TC_APP_0647</t>
+  </si>
+  <si>
+    <t>TC_APP_0648</t>
+  </si>
+  <si>
+    <t>TC_APP_0649</t>
+  </si>
+  <si>
+    <t>TC_APP_0650</t>
+  </si>
+  <si>
+    <t>TC_APP_0651</t>
+  </si>
+  <si>
+    <t>TC_APP_0652</t>
+  </si>
+  <si>
+    <t>TC_APP_0653</t>
+  </si>
+  <si>
+    <t>TC_APP_0654</t>
+  </si>
+  <si>
+    <t>TC_APP_0655</t>
+  </si>
+  <si>
+    <t>TC_APP_0656</t>
+  </si>
+  <si>
+    <t>TC_APP_0657</t>
+  </si>
+  <si>
+    <t>TC_APP_0658</t>
+  </si>
+  <si>
+    <t>TC_APP_0659</t>
+  </si>
+  <si>
+    <t>TC_APP_0660</t>
+  </si>
+  <si>
+    <t>TC_APP_0661</t>
+  </si>
+  <si>
+    <t>TC_APP_0662</t>
+  </si>
+  <si>
+    <t>TC_APP_0663</t>
+  </si>
+  <si>
+    <t>TC_APP_0664</t>
+  </si>
+  <si>
+    <t>TC_APP_0665</t>
+  </si>
+  <si>
+    <t>TC_APP_0666</t>
+  </si>
+  <si>
+    <t>TC_APP_0667</t>
+  </si>
+  <si>
+    <t>TC_APP_0668</t>
+  </si>
+  <si>
+    <t>TC_APP_0669</t>
+  </si>
+  <si>
+    <t>TC_APP_0670</t>
+  </si>
+  <si>
+    <t>TC_APP_0671</t>
+  </si>
+  <si>
+    <t>TC_APP_0672</t>
+  </si>
+  <si>
+    <t>TC_APP_0673</t>
+  </si>
+  <si>
+    <t>TC_APP_0674</t>
+  </si>
+  <si>
+    <t>TC_APP_0675</t>
+  </si>
+  <si>
+    <t>TC_APP_0676</t>
+  </si>
+  <si>
+    <t>TC_APP_0677</t>
+  </si>
+  <si>
+    <t>TC_APP_0678</t>
+  </si>
+  <si>
+    <t>TC_APP_0679</t>
+  </si>
+  <si>
+    <t>TC_APP_0680</t>
+  </si>
+  <si>
+    <t>TC_APP_0681</t>
+  </si>
+  <si>
+    <t>TC_APP_0682</t>
+  </si>
+  <si>
+    <t>TC_APP_0683</t>
+  </si>
+  <si>
+    <t>TC_APP_0684</t>
+  </si>
+  <si>
+    <t>TC_APP_0685</t>
+  </si>
+  <si>
+    <t>TC_APP_0686</t>
+  </si>
+  <si>
+    <t>TC_APP_0687</t>
+  </si>
+  <si>
+    <t>TC_APP_0688</t>
+  </si>
+  <si>
+    <t>TC_APP_0689</t>
+  </si>
+  <si>
+    <t>TC_APP_0690</t>
+  </si>
+  <si>
+    <t>TC_APP_0691</t>
+  </si>
+  <si>
+    <t>TC_APP_0692</t>
+  </si>
+  <si>
+    <t>TC_APP_0693</t>
+  </si>
+  <si>
+    <t>TC_APP_0694</t>
+  </si>
+  <si>
+    <t>TC_APP_0695</t>
+  </si>
+  <si>
+    <t>TC_APP_0696</t>
+  </si>
+  <si>
+    <t>TC_APP_0697</t>
+  </si>
+  <si>
+    <t>TC_APP_0698</t>
+  </si>
+  <si>
+    <t>TC_APP_0699</t>
+  </si>
+  <si>
+    <t>TC_APP_0700</t>
+  </si>
+  <si>
+    <t>TC_APP_0701</t>
+  </si>
+  <si>
+    <t>TC_APP_0702</t>
+  </si>
+  <si>
+    <t>TC_APP_0703</t>
+  </si>
+  <si>
+    <t>TC_APP_0704</t>
+  </si>
+  <si>
+    <t>TC_APP_0705</t>
+  </si>
+  <si>
+    <t>TC_APP_0706</t>
+  </si>
+  <si>
+    <t>TC_APP_0707</t>
+  </si>
+  <si>
+    <t>TC_APP_0708</t>
+  </si>
+  <si>
+    <t>TC_APP_0709</t>
+  </si>
+  <si>
+    <t>TC_APP_0710</t>
+  </si>
+  <si>
+    <t>TC_APP_0711</t>
+  </si>
+  <si>
+    <t>TC_APP_0712</t>
+  </si>
+  <si>
+    <t>TC_APP_0713</t>
+  </si>
+  <si>
+    <t>TC_APP_0714</t>
+  </si>
+  <si>
+    <t>TC_APP_0715</t>
+  </si>
+  <si>
+    <t>TC_APP_0716</t>
+  </si>
+  <si>
+    <t>TC_APP_0717</t>
+  </si>
+  <si>
+    <t>TC_APP_0718</t>
+  </si>
+  <si>
+    <t>TC_APP_0719</t>
+  </si>
+  <si>
+    <t>TC_APP_0720</t>
+  </si>
+  <si>
+    <t>TC_APP_0721</t>
+  </si>
+  <si>
+    <t>TC_APP_0722</t>
+  </si>
+  <si>
+    <t>TC_APP_0723</t>
+  </si>
+  <si>
+    <t>TC_APP_0724</t>
+  </si>
+  <si>
+    <t>TC_APP_0725</t>
+  </si>
+  <si>
+    <t>TC_APP_0726</t>
+  </si>
+  <si>
+    <t>TC_APP_0727</t>
+  </si>
+  <si>
+    <t>TC_APP_0728</t>
+  </si>
+  <si>
+    <t>TC_APP_0729</t>
+  </si>
+  <si>
+    <t>TC_APP_0730</t>
+  </si>
+  <si>
+    <t>TC_APP_0731</t>
+  </si>
+  <si>
+    <t>TC_APP_0732</t>
+  </si>
+  <si>
+    <t>TC_APP_0733</t>
+  </si>
+  <si>
+    <t>TC_APP_0734</t>
+  </si>
+  <si>
+    <t>TC_APP_0735</t>
+  </si>
+  <si>
+    <t>TC_APP_0736</t>
+  </si>
+  <si>
+    <t>TC_APP_0737</t>
+  </si>
+  <si>
+    <t>TC_APP_0738</t>
+  </si>
+  <si>
+    <t>TC_APP_0739</t>
+  </si>
+  <si>
+    <t>TC_APP_0740</t>
+  </si>
+  <si>
+    <t>TC_APP_0741</t>
+  </si>
+  <si>
+    <t>TC_APP_0742</t>
+  </si>
+  <si>
+    <t>TC_APP_0743</t>
+  </si>
+  <si>
+    <t>TC_APP_0744</t>
+  </si>
+  <si>
+    <t>TC_APP_0745</t>
+  </si>
+  <si>
+    <t>TC_APP_0746</t>
+  </si>
+  <si>
+    <t>TC_APP_0747</t>
+  </si>
+  <si>
+    <t>TC_APP_0748</t>
+  </si>
+  <si>
+    <t>TC_APP_0749</t>
+  </si>
+  <si>
+    <t>TC_APP_0750</t>
+  </si>
+  <si>
+    <t>TC_APP_0751</t>
+  </si>
+  <si>
+    <t>TC_APP_0752</t>
+  </si>
+  <si>
+    <t>TC_APP_0753</t>
+  </si>
+  <si>
+    <t>TC_APP_0754</t>
+  </si>
+  <si>
+    <t>TC_APP_0755</t>
+  </si>
+  <si>
+    <t>TC_APP_0756</t>
+  </si>
+  <si>
+    <t>TC_APP_0757</t>
+  </si>
+  <si>
+    <t>TC_APP_0758</t>
+  </si>
+  <si>
+    <t>TC_APP_0759</t>
+  </si>
+  <si>
+    <t>TC_APP_0760</t>
+  </si>
+  <si>
+    <t>TC_APP_0761</t>
+  </si>
+  <si>
+    <t>TC_APP_0762</t>
+  </si>
+  <si>
+    <t>TC_APP_0763</t>
+  </si>
+  <si>
+    <t>TC_APP_0764</t>
+  </si>
+  <si>
+    <t>TC_APP_0765</t>
+  </si>
+  <si>
+    <t>TC_APP_0766</t>
+  </si>
+  <si>
+    <t>TC_APP_0767</t>
+  </si>
+  <si>
+    <t>TC_APP_0768</t>
+  </si>
+  <si>
+    <t>TC_APP_0769</t>
+  </si>
+  <si>
+    <t>TC_APP_0770</t>
+  </si>
+  <si>
     <t>Appium</t>
   </si>
   <si>
@@ -641,6 +1241,606 @@
   </si>
   <si>
     <t>App Unit Test 100</t>
+  </si>
+  <si>
+    <t>App Unit Test 101</t>
+  </si>
+  <si>
+    <t>App Unit Test 102</t>
+  </si>
+  <si>
+    <t>App Unit Test 103</t>
+  </si>
+  <si>
+    <t>App Unit Test 104</t>
+  </si>
+  <si>
+    <t>App Unit Test 105</t>
+  </si>
+  <si>
+    <t>App Unit Test 106</t>
+  </si>
+  <si>
+    <t>App Unit Test 107</t>
+  </si>
+  <si>
+    <t>App Unit Test 108</t>
+  </si>
+  <si>
+    <t>App Unit Test 109</t>
+  </si>
+  <si>
+    <t>App Unit Test 110</t>
+  </si>
+  <si>
+    <t>App Unit Test 111</t>
+  </si>
+  <si>
+    <t>App Unit Test 112</t>
+  </si>
+  <si>
+    <t>App Unit Test 113</t>
+  </si>
+  <si>
+    <t>App Unit Test 114</t>
+  </si>
+  <si>
+    <t>App Unit Test 115</t>
+  </si>
+  <si>
+    <t>App Unit Test 116</t>
+  </si>
+  <si>
+    <t>App Unit Test 117</t>
+  </si>
+  <si>
+    <t>App Unit Test 118</t>
+  </si>
+  <si>
+    <t>App Unit Test 119</t>
+  </si>
+  <si>
+    <t>App Unit Test 120</t>
+  </si>
+  <si>
+    <t>App Unit Test 121</t>
+  </si>
+  <si>
+    <t>App Unit Test 122</t>
+  </si>
+  <si>
+    <t>App Unit Test 123</t>
+  </si>
+  <si>
+    <t>App Unit Test 124</t>
+  </si>
+  <si>
+    <t>App Unit Test 125</t>
+  </si>
+  <si>
+    <t>App Unit Test 126</t>
+  </si>
+  <si>
+    <t>App Unit Test 127</t>
+  </si>
+  <si>
+    <t>App Unit Test 128</t>
+  </si>
+  <si>
+    <t>App Unit Test 129</t>
+  </si>
+  <si>
+    <t>App Unit Test 130</t>
+  </si>
+  <si>
+    <t>App Unit Test 131</t>
+  </si>
+  <si>
+    <t>App Unit Test 132</t>
+  </si>
+  <si>
+    <t>App Unit Test 133</t>
+  </si>
+  <si>
+    <t>App Unit Test 134</t>
+  </si>
+  <si>
+    <t>App Unit Test 135</t>
+  </si>
+  <si>
+    <t>App Unit Test 136</t>
+  </si>
+  <si>
+    <t>App Unit Test 137</t>
+  </si>
+  <si>
+    <t>App Unit Test 138</t>
+  </si>
+  <si>
+    <t>App Unit Test 139</t>
+  </si>
+  <si>
+    <t>App Unit Test 140</t>
+  </si>
+  <si>
+    <t>App Unit Test 141</t>
+  </si>
+  <si>
+    <t>App Unit Test 142</t>
+  </si>
+  <si>
+    <t>App Unit Test 143</t>
+  </si>
+  <si>
+    <t>App Unit Test 144</t>
+  </si>
+  <si>
+    <t>App Unit Test 145</t>
+  </si>
+  <si>
+    <t>App Unit Test 146</t>
+  </si>
+  <si>
+    <t>App Unit Test 147</t>
+  </si>
+  <si>
+    <t>App Unit Test 148</t>
+  </si>
+  <si>
+    <t>App Unit Test 149</t>
+  </si>
+  <si>
+    <t>App Unit Test 150</t>
+  </si>
+  <si>
+    <t>App Unit Test 151</t>
+  </si>
+  <si>
+    <t>App Unit Test 152</t>
+  </si>
+  <si>
+    <t>App Unit Test 153</t>
+  </si>
+  <si>
+    <t>App Unit Test 154</t>
+  </si>
+  <si>
+    <t>App Unit Test 155</t>
+  </si>
+  <si>
+    <t>App Unit Test 156</t>
+  </si>
+  <si>
+    <t>App Unit Test 157</t>
+  </si>
+  <si>
+    <t>App Unit Test 158</t>
+  </si>
+  <si>
+    <t>App Unit Test 159</t>
+  </si>
+  <si>
+    <t>App Unit Test 160</t>
+  </si>
+  <si>
+    <t>App Unit Test 161</t>
+  </si>
+  <si>
+    <t>App Unit Test 162</t>
+  </si>
+  <si>
+    <t>App Unit Test 163</t>
+  </si>
+  <si>
+    <t>App Unit Test 164</t>
+  </si>
+  <si>
+    <t>App Unit Test 165</t>
+  </si>
+  <si>
+    <t>App Unit Test 166</t>
+  </si>
+  <si>
+    <t>App Unit Test 167</t>
+  </si>
+  <si>
+    <t>App Unit Test 168</t>
+  </si>
+  <si>
+    <t>App Unit Test 169</t>
+  </si>
+  <si>
+    <t>App Unit Test 170</t>
+  </si>
+  <si>
+    <t>App Unit Test 171</t>
+  </si>
+  <si>
+    <t>App Unit Test 172</t>
+  </si>
+  <si>
+    <t>App Unit Test 173</t>
+  </si>
+  <si>
+    <t>App Unit Test 174</t>
+  </si>
+  <si>
+    <t>App Unit Test 175</t>
+  </si>
+  <si>
+    <t>App Unit Test 176</t>
+  </si>
+  <si>
+    <t>App Unit Test 177</t>
+  </si>
+  <si>
+    <t>App Unit Test 178</t>
+  </si>
+  <si>
+    <t>App Unit Test 179</t>
+  </si>
+  <si>
+    <t>App Unit Test 180</t>
+  </si>
+  <si>
+    <t>App Unit Test 181</t>
+  </si>
+  <si>
+    <t>App Unit Test 182</t>
+  </si>
+  <si>
+    <t>App Unit Test 183</t>
+  </si>
+  <si>
+    <t>App Unit Test 184</t>
+  </si>
+  <si>
+    <t>App Unit Test 185</t>
+  </si>
+  <si>
+    <t>App Unit Test 186</t>
+  </si>
+  <si>
+    <t>App Unit Test 187</t>
+  </si>
+  <si>
+    <t>App Unit Test 188</t>
+  </si>
+  <si>
+    <t>App Unit Test 189</t>
+  </si>
+  <si>
+    <t>App Unit Test 190</t>
+  </si>
+  <si>
+    <t>App Unit Test 191</t>
+  </si>
+  <si>
+    <t>App Unit Test 192</t>
+  </si>
+  <si>
+    <t>App Unit Test 193</t>
+  </si>
+  <si>
+    <t>App Unit Test 194</t>
+  </si>
+  <si>
+    <t>App Unit Test 195</t>
+  </si>
+  <si>
+    <t>App Unit Test 196</t>
+  </si>
+  <si>
+    <t>App Unit Test 197</t>
+  </si>
+  <si>
+    <t>App Unit Test 198</t>
+  </si>
+  <si>
+    <t>App Unit Test 199</t>
+  </si>
+  <si>
+    <t>App Unit Test 200</t>
+  </si>
+  <si>
+    <t>App Unit Test 201</t>
+  </si>
+  <si>
+    <t>App Unit Test 202</t>
+  </si>
+  <si>
+    <t>App Unit Test 203</t>
+  </si>
+  <si>
+    <t>App Unit Test 204</t>
+  </si>
+  <si>
+    <t>App Unit Test 205</t>
+  </si>
+  <si>
+    <t>App Unit Test 206</t>
+  </si>
+  <si>
+    <t>App Unit Test 207</t>
+  </si>
+  <si>
+    <t>App Unit Test 208</t>
+  </si>
+  <si>
+    <t>App Unit Test 209</t>
+  </si>
+  <si>
+    <t>App Unit Test 210</t>
+  </si>
+  <si>
+    <t>App Unit Test 211</t>
+  </si>
+  <si>
+    <t>App Unit Test 212</t>
+  </si>
+  <si>
+    <t>App Unit Test 213</t>
+  </si>
+  <si>
+    <t>App Unit Test 214</t>
+  </si>
+  <si>
+    <t>App Unit Test 215</t>
+  </si>
+  <si>
+    <t>App Unit Test 216</t>
+  </si>
+  <si>
+    <t>App Unit Test 217</t>
+  </si>
+  <si>
+    <t>App Unit Test 218</t>
+  </si>
+  <si>
+    <t>App Unit Test 219</t>
+  </si>
+  <si>
+    <t>App Unit Test 220</t>
+  </si>
+  <si>
+    <t>App Unit Test 221</t>
+  </si>
+  <si>
+    <t>App Unit Test 222</t>
+  </si>
+  <si>
+    <t>App Unit Test 223</t>
+  </si>
+  <si>
+    <t>App Unit Test 224</t>
+  </si>
+  <si>
+    <t>App Unit Test 225</t>
+  </si>
+  <si>
+    <t>App Unit Test 226</t>
+  </si>
+  <si>
+    <t>App Unit Test 227</t>
+  </si>
+  <si>
+    <t>App Unit Test 228</t>
+  </si>
+  <si>
+    <t>App Unit Test 229</t>
+  </si>
+  <si>
+    <t>App Unit Test 230</t>
+  </si>
+  <si>
+    <t>App Unit Test 231</t>
+  </si>
+  <si>
+    <t>App Unit Test 232</t>
+  </si>
+  <si>
+    <t>App Unit Test 233</t>
+  </si>
+  <si>
+    <t>App Unit Test 234</t>
+  </si>
+  <si>
+    <t>App Unit Test 235</t>
+  </si>
+  <si>
+    <t>App Unit Test 236</t>
+  </si>
+  <si>
+    <t>App Unit Test 237</t>
+  </si>
+  <si>
+    <t>App Unit Test 238</t>
+  </si>
+  <si>
+    <t>App Unit Test 239</t>
+  </si>
+  <si>
+    <t>App Unit Test 240</t>
+  </si>
+  <si>
+    <t>App Unit Test 241</t>
+  </si>
+  <si>
+    <t>App Unit Test 242</t>
+  </si>
+  <si>
+    <t>App Unit Test 243</t>
+  </si>
+  <si>
+    <t>App Unit Test 244</t>
+  </si>
+  <si>
+    <t>App Unit Test 245</t>
+  </si>
+  <si>
+    <t>App Unit Test 246</t>
+  </si>
+  <si>
+    <t>App Unit Test 247</t>
+  </si>
+  <si>
+    <t>App Unit Test 248</t>
+  </si>
+  <si>
+    <t>App Unit Test 249</t>
+  </si>
+  <si>
+    <t>App Unit Test 250</t>
+  </si>
+  <si>
+    <t>App Unit Test 251</t>
+  </si>
+  <si>
+    <t>App Unit Test 252</t>
+  </si>
+  <si>
+    <t>App Unit Test 253</t>
+  </si>
+  <si>
+    <t>App Unit Test 254</t>
+  </si>
+  <si>
+    <t>App Unit Test 255</t>
+  </si>
+  <si>
+    <t>App Unit Test 256</t>
+  </si>
+  <si>
+    <t>App Unit Test 257</t>
+  </si>
+  <si>
+    <t>App Unit Test 258</t>
+  </si>
+  <si>
+    <t>App Unit Test 259</t>
+  </si>
+  <si>
+    <t>App Unit Test 260</t>
+  </si>
+  <si>
+    <t>App Unit Test 261</t>
+  </si>
+  <si>
+    <t>App Unit Test 262</t>
+  </si>
+  <si>
+    <t>App Unit Test 263</t>
+  </si>
+  <si>
+    <t>App Unit Test 264</t>
+  </si>
+  <si>
+    <t>App Unit Test 265</t>
+  </si>
+  <si>
+    <t>App Unit Test 266</t>
+  </si>
+  <si>
+    <t>App Unit Test 267</t>
+  </si>
+  <si>
+    <t>App Unit Test 268</t>
+  </si>
+  <si>
+    <t>App Unit Test 269</t>
+  </si>
+  <si>
+    <t>App Unit Test 270</t>
+  </si>
+  <si>
+    <t>App Unit Test 271</t>
+  </si>
+  <si>
+    <t>App Unit Test 272</t>
+  </si>
+  <si>
+    <t>App Unit Test 273</t>
+  </si>
+  <si>
+    <t>App Unit Test 274</t>
+  </si>
+  <si>
+    <t>App Unit Test 275</t>
+  </si>
+  <si>
+    <t>App Unit Test 276</t>
+  </si>
+  <si>
+    <t>App Unit Test 277</t>
+  </si>
+  <si>
+    <t>App Unit Test 278</t>
+  </si>
+  <si>
+    <t>App Unit Test 279</t>
+  </si>
+  <si>
+    <t>App Unit Test 280</t>
+  </si>
+  <si>
+    <t>App Unit Test 281</t>
+  </si>
+  <si>
+    <t>App Unit Test 282</t>
+  </si>
+  <si>
+    <t>App Unit Test 283</t>
+  </si>
+  <si>
+    <t>App Unit Test 284</t>
+  </si>
+  <si>
+    <t>App Unit Test 285</t>
+  </si>
+  <si>
+    <t>App Unit Test 286</t>
+  </si>
+  <si>
+    <t>App Unit Test 287</t>
+  </si>
+  <si>
+    <t>App Unit Test 288</t>
+  </si>
+  <si>
+    <t>App Unit Test 289</t>
+  </si>
+  <si>
+    <t>App Unit Test 290</t>
+  </si>
+  <si>
+    <t>App Unit Test 291</t>
+  </si>
+  <si>
+    <t>App Unit Test 292</t>
+  </si>
+  <si>
+    <t>App Unit Test 293</t>
+  </si>
+  <si>
+    <t>App Unit Test 294</t>
+  </si>
+  <si>
+    <t>App Unit Test 295</t>
+  </si>
+  <si>
+    <t>App Unit Test 296</t>
+  </si>
+  <si>
+    <t>App Unit Test 297</t>
+  </si>
+  <si>
+    <t>App Unit Test 298</t>
+  </si>
+  <si>
+    <t>App Unit Test 299</t>
+  </si>
+  <si>
+    <t>App Unit Test 300</t>
   </si>
   <si>
     <t>Pass</t>
@@ -1004,7 +2204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G301"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1035,22 +2235,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>309</v>
       </c>
       <c r="E2" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F2">
-        <v>0.78</v>
+        <v>0.17</v>
       </c>
       <c r="G2" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1058,22 +2258,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>310</v>
       </c>
       <c r="E3" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F3">
-        <v>0.59</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G3" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1081,22 +2281,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>311</v>
       </c>
       <c r="E4" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F4">
-        <v>0.96</v>
+        <v>0.23</v>
       </c>
       <c r="G4" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1104,22 +2304,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>312</v>
       </c>
       <c r="E5" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F5">
-        <v>0.77</v>
+        <v>0.32</v>
       </c>
       <c r="G5" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1127,22 +2327,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>313</v>
       </c>
       <c r="E6" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F6">
-        <v>0.48</v>
+        <v>0.14</v>
       </c>
       <c r="G6" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1150,22 +2350,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>314</v>
       </c>
       <c r="E7" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F7">
-        <v>0.58</v>
+        <v>0.16</v>
       </c>
       <c r="G7" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1173,22 +2373,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>315</v>
       </c>
       <c r="E8" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F8">
-        <v>0.16</v>
+        <v>0.65</v>
       </c>
       <c r="G8" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1196,22 +2396,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>316</v>
       </c>
       <c r="E9" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F9">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="G9" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1219,22 +2419,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>317</v>
       </c>
       <c r="E10" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F10">
-        <v>0.53</v>
+        <v>0.98</v>
       </c>
       <c r="G10" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1242,22 +2442,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>318</v>
       </c>
       <c r="E11" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F11">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="G11" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1265,22 +2465,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>319</v>
       </c>
       <c r="E12" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F12">
-        <v>0.45</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G12" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1288,22 +2488,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="E13" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F13">
-        <v>0.2</v>
+        <v>0.82</v>
       </c>
       <c r="G13" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1311,22 +2511,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>321</v>
       </c>
       <c r="E14" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F14">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="G14" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1334,22 +2534,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>322</v>
       </c>
       <c r="E15" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F15">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="G15" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1357,22 +2557,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>323</v>
       </c>
       <c r="E16" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F16">
-        <v>0.76</v>
+        <v>0.97</v>
       </c>
       <c r="G16" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1380,22 +2580,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>324</v>
       </c>
       <c r="E17" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F17">
-        <v>0.68</v>
+        <v>0.51</v>
       </c>
       <c r="G17" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1403,22 +2603,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D18" t="s">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="E18" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F18">
-        <v>0.54</v>
+        <v>0.41</v>
       </c>
       <c r="G18" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1426,22 +2626,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>326</v>
       </c>
       <c r="E19" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F19">
-        <v>0.46</v>
+        <v>0.3</v>
       </c>
       <c r="G19" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1449,22 +2649,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>327</v>
       </c>
       <c r="E20" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F20">
-        <v>0.95</v>
+        <v>0.16</v>
       </c>
       <c r="G20" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1472,22 +2672,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>328</v>
       </c>
       <c r="E21" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F21">
-        <v>0.37</v>
+        <v>0.84</v>
       </c>
       <c r="G21" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1495,22 +2695,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>329</v>
       </c>
       <c r="E22" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F22">
-        <v>0.64</v>
+        <v>0.9</v>
       </c>
       <c r="G22" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1518,22 +2718,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D23" t="s">
-        <v>130</v>
+        <v>330</v>
       </c>
       <c r="E23" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F23">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="G23" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1541,22 +2741,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>331</v>
       </c>
       <c r="E24" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F24">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
       <c r="G24" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1564,22 +2764,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>332</v>
       </c>
       <c r="E25" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F25">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="G25" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1587,22 +2787,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>333</v>
       </c>
       <c r="E26" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F26">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="G26" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1610,22 +2810,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>334</v>
       </c>
       <c r="E27" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F27">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="G27" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1633,22 +2833,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>335</v>
       </c>
       <c r="E28" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F28">
-        <v>0.37</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G28" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1656,22 +2856,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>336</v>
       </c>
       <c r="E29" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F29">
-        <v>0.23</v>
+        <v>0.9</v>
       </c>
       <c r="G29" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1679,22 +2879,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>337</v>
       </c>
       <c r="E30" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F30">
-        <v>0.74</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G30" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1702,22 +2902,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D31" t="s">
-        <v>138</v>
+        <v>338</v>
       </c>
       <c r="E31" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F31">
-        <v>0.24</v>
+        <v>0.95</v>
       </c>
       <c r="G31" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1725,22 +2925,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D32" t="s">
-        <v>139</v>
+        <v>339</v>
       </c>
       <c r="E32" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F32">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="G32" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1748,22 +2948,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D33" t="s">
-        <v>140</v>
+        <v>340</v>
       </c>
       <c r="E33" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F33">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="G33" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1771,22 +2971,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D34" t="s">
-        <v>141</v>
+        <v>341</v>
       </c>
       <c r="E34" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F34">
-        <v>0.63</v>
+        <v>0.19</v>
       </c>
       <c r="G34" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1794,22 +2994,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D35" t="s">
-        <v>142</v>
+        <v>342</v>
       </c>
       <c r="E35" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F35">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="G35" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1817,22 +3017,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C36" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D36" t="s">
-        <v>143</v>
+        <v>343</v>
       </c>
       <c r="E36" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F36">
-        <v>0.36</v>
+        <v>0.91</v>
       </c>
       <c r="G36" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1840,22 +3040,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D37" t="s">
-        <v>144</v>
+        <v>344</v>
       </c>
       <c r="E37" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F37">
-        <v>0.18</v>
+        <v>0.97</v>
       </c>
       <c r="G37" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1863,22 +3063,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C38" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>345</v>
       </c>
       <c r="E38" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F38">
-        <v>0.45</v>
+        <v>0.73</v>
       </c>
       <c r="G38" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1886,22 +3086,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C39" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D39" t="s">
-        <v>146</v>
+        <v>346</v>
       </c>
       <c r="E39" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F39">
-        <v>0.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G39" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1909,22 +3109,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C40" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D40" t="s">
-        <v>147</v>
+        <v>347</v>
       </c>
       <c r="E40" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F40">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="G40" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1932,22 +3132,22 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C41" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D41" t="s">
-        <v>148</v>
+        <v>348</v>
       </c>
       <c r="E41" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F41">
-        <v>0.11</v>
+        <v>0.65</v>
       </c>
       <c r="G41" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1955,22 +3155,22 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C42" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D42" t="s">
-        <v>149</v>
+        <v>349</v>
       </c>
       <c r="E42" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F42">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="G42" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1978,22 +3178,22 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C43" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D43" t="s">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="E43" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F43">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G43" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2001,22 +3201,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C44" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D44" t="s">
-        <v>151</v>
+        <v>351</v>
       </c>
       <c r="E44" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F44">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="G44" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2024,22 +3224,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C45" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D45" t="s">
-        <v>152</v>
+        <v>352</v>
       </c>
       <c r="E45" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F45">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="G45" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2047,22 +3247,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C46" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D46" t="s">
-        <v>153</v>
+        <v>353</v>
       </c>
       <c r="E46" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F46">
-        <v>0.78</v>
+        <v>0.18</v>
       </c>
       <c r="G46" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2070,22 +3270,22 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C47" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D47" t="s">
-        <v>154</v>
+        <v>354</v>
       </c>
       <c r="E47" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F47">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="G47" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2093,22 +3293,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C48" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D48" t="s">
-        <v>155</v>
+        <v>355</v>
       </c>
       <c r="E48" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F48">
-        <v>0.91</v>
+        <v>0.34</v>
       </c>
       <c r="G48" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2116,22 +3316,22 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C49" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D49" t="s">
-        <v>156</v>
+        <v>356</v>
       </c>
       <c r="E49" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F49">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="G49" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2139,22 +3339,22 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C50" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D50" t="s">
-        <v>157</v>
+        <v>357</v>
       </c>
       <c r="E50" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F50">
-        <v>0.49</v>
+        <v>0.24</v>
       </c>
       <c r="G50" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2162,22 +3362,22 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C51" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D51" t="s">
-        <v>158</v>
+        <v>358</v>
       </c>
       <c r="E51" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F51">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G51" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2185,22 +3385,22 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C52" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D52" t="s">
-        <v>159</v>
+        <v>359</v>
       </c>
       <c r="E52" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F52">
-        <v>0.29</v>
+        <v>0.62</v>
       </c>
       <c r="G52" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2208,22 +3408,22 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C53" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D53" t="s">
-        <v>160</v>
+        <v>360</v>
       </c>
       <c r="E53" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F53">
-        <v>0.84</v>
+        <v>0.38</v>
       </c>
       <c r="G53" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2231,22 +3431,22 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C54" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D54" t="s">
-        <v>161</v>
+        <v>361</v>
       </c>
       <c r="E54" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F54">
-        <v>0.82</v>
+        <v>0.16</v>
       </c>
       <c r="G54" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2254,22 +3454,22 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C55" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D55" t="s">
-        <v>162</v>
+        <v>362</v>
       </c>
       <c r="E55" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F55">
-        <v>0.17</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G55" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2277,22 +3477,22 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C56" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D56" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="E56" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F56">
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
       <c r="G56" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2300,22 +3500,22 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C57" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D57" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E57" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F57">
-        <v>0.6</v>
+        <v>0.11</v>
       </c>
       <c r="G57" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2323,22 +3523,22 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C58" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D58" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="E58" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F58">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="G58" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2346,22 +3546,22 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C59" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D59" t="s">
-        <v>166</v>
+        <v>366</v>
       </c>
       <c r="E59" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G59" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2369,22 +3569,22 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C60" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D60" t="s">
-        <v>167</v>
+        <v>367</v>
       </c>
       <c r="E60" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F60">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="G60" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2392,22 +3592,22 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C61" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D61" t="s">
-        <v>168</v>
+        <v>368</v>
       </c>
       <c r="E61" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F61">
-        <v>0.37</v>
+        <v>0.24</v>
       </c>
       <c r="G61" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2415,22 +3615,22 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C62" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D62" t="s">
-        <v>169</v>
+        <v>369</v>
       </c>
       <c r="E62" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F62">
-        <v>0.83</v>
+        <v>0.16</v>
       </c>
       <c r="G62" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2438,22 +3638,22 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C63" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D63" t="s">
-        <v>170</v>
+        <v>370</v>
       </c>
       <c r="E63" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F63">
-        <v>0.59</v>
+        <v>0.16</v>
       </c>
       <c r="G63" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2461,22 +3661,22 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C64" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D64" t="s">
-        <v>171</v>
+        <v>371</v>
       </c>
       <c r="E64" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F64">
-        <v>0.76</v>
+        <v>0.46</v>
       </c>
       <c r="G64" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2484,22 +3684,22 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C65" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D65" t="s">
-        <v>172</v>
+        <v>372</v>
       </c>
       <c r="E65" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F65">
-        <v>0.67</v>
+        <v>0.41</v>
       </c>
       <c r="G65" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2507,22 +3707,22 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C66" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D66" t="s">
-        <v>173</v>
+        <v>373</v>
       </c>
       <c r="E66" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F66">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="G66" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2530,22 +3730,22 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C67" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D67" t="s">
-        <v>174</v>
+        <v>374</v>
       </c>
       <c r="E67" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="G67" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2553,22 +3753,22 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C68" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D68" t="s">
-        <v>175</v>
+        <v>375</v>
       </c>
       <c r="E68" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F68">
-        <v>0.13</v>
+        <v>0.86</v>
       </c>
       <c r="G68" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2576,22 +3776,22 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C69" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D69" t="s">
-        <v>176</v>
+        <v>376</v>
       </c>
       <c r="E69" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F69">
-        <v>0.48</v>
+        <v>0.79</v>
       </c>
       <c r="G69" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2599,22 +3799,22 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C70" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D70" t="s">
-        <v>177</v>
+        <v>377</v>
       </c>
       <c r="E70" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F70">
-        <v>0.75</v>
+        <v>0.41</v>
       </c>
       <c r="G70" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2622,22 +3822,22 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C71" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D71" t="s">
-        <v>178</v>
+        <v>378</v>
       </c>
       <c r="E71" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F71">
-        <v>0.44</v>
+        <v>0.74</v>
       </c>
       <c r="G71" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2645,22 +3845,22 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C72" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D72" t="s">
-        <v>179</v>
+        <v>379</v>
       </c>
       <c r="E72" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F72">
-        <v>0.63</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G72" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2668,22 +3868,22 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C73" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D73" t="s">
-        <v>180</v>
+        <v>380</v>
       </c>
       <c r="E73" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F73">
-        <v>0.57</v>
+        <v>0.47</v>
       </c>
       <c r="G73" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2691,22 +3891,22 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C74" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D74" t="s">
-        <v>181</v>
+        <v>381</v>
       </c>
       <c r="E74" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F74">
-        <v>0.19</v>
+        <v>0.88</v>
       </c>
       <c r="G74" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2714,22 +3914,22 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C75" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D75" t="s">
-        <v>182</v>
+        <v>382</v>
       </c>
       <c r="E75" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F75">
         <v>0.33</v>
       </c>
       <c r="G75" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2737,22 +3937,22 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C76" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D76" t="s">
-        <v>183</v>
+        <v>383</v>
       </c>
       <c r="E76" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F76">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="G76" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2760,22 +3960,22 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C77" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D77" t="s">
-        <v>184</v>
+        <v>384</v>
       </c>
       <c r="E77" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F77">
-        <v>0.35</v>
+        <v>0.57</v>
       </c>
       <c r="G77" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2783,22 +3983,22 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C78" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D78" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="E78" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F78">
-        <v>0.52</v>
+        <v>0.88</v>
       </c>
       <c r="G78" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2806,22 +4006,22 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C79" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D79" t="s">
-        <v>186</v>
+        <v>386</v>
       </c>
       <c r="E79" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F79">
-        <v>0.72</v>
+        <v>0.88</v>
       </c>
       <c r="G79" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2829,22 +4029,22 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C80" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D80" t="s">
-        <v>187</v>
+        <v>387</v>
       </c>
       <c r="E80" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F80">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="G80" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2852,22 +4052,22 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C81" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D81" t="s">
-        <v>188</v>
+        <v>388</v>
       </c>
       <c r="E81" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F81">
-        <v>0.48</v>
+        <v>0.99</v>
       </c>
       <c r="G81" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2875,22 +4075,22 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C82" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D82" t="s">
-        <v>189</v>
+        <v>389</v>
       </c>
       <c r="E82" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F82">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2898,22 +4098,22 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C83" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D83" t="s">
-        <v>190</v>
+        <v>390</v>
       </c>
       <c r="E83" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F83">
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
       <c r="G83" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2921,22 +4121,22 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C84" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D84" t="s">
-        <v>191</v>
+        <v>391</v>
       </c>
       <c r="E84" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F84">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="G84" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2944,22 +4144,22 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C85" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D85" t="s">
-        <v>192</v>
+        <v>392</v>
       </c>
       <c r="E85" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F85">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="G85" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2967,22 +4167,22 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C86" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D86" t="s">
-        <v>193</v>
+        <v>393</v>
       </c>
       <c r="E86" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F86">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="G86" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2990,22 +4190,22 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C87" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D87" t="s">
-        <v>194</v>
+        <v>394</v>
       </c>
       <c r="E87" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F87">
-        <v>0.58</v>
+        <v>0.83</v>
       </c>
       <c r="G87" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3013,22 +4213,22 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C88" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D88" t="s">
-        <v>195</v>
+        <v>395</v>
       </c>
       <c r="E88" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F88">
-        <v>0.77</v>
+        <v>0.63</v>
       </c>
       <c r="G88" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3036,22 +4236,22 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C89" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D89" t="s">
-        <v>196</v>
+        <v>396</v>
       </c>
       <c r="E89" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F89">
-        <v>0.74</v>
+        <v>0.9</v>
       </c>
       <c r="G89" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3059,22 +4259,22 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C90" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D90" t="s">
-        <v>197</v>
+        <v>397</v>
       </c>
       <c r="E90" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F90">
-        <v>0.33</v>
+        <v>0.59</v>
       </c>
       <c r="G90" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3082,22 +4282,22 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C91" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D91" t="s">
-        <v>198</v>
+        <v>398</v>
       </c>
       <c r="E91" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F91">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="G91" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3105,22 +4305,22 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C92" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D92" t="s">
-        <v>199</v>
+        <v>399</v>
       </c>
       <c r="E92" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F92">
-        <v>0.86</v>
+        <v>0.68</v>
       </c>
       <c r="G92" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3128,22 +4328,22 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C93" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D93" t="s">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E93" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F93">
-        <v>0.33</v>
+        <v>0.83</v>
       </c>
       <c r="G93" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3151,22 +4351,22 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C94" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D94" t="s">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="E94" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F94">
-        <v>0.37</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G94" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3174,22 +4374,22 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C95" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D95" t="s">
-        <v>202</v>
+        <v>402</v>
       </c>
       <c r="E95" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F95">
-        <v>0.83</v>
+        <v>0.28</v>
       </c>
       <c r="G95" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3197,22 +4397,22 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C96" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D96" t="s">
-        <v>203</v>
+        <v>403</v>
       </c>
       <c r="E96" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F96">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="G96" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3220,22 +4420,22 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C97" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D97" t="s">
-        <v>204</v>
+        <v>404</v>
       </c>
       <c r="E97" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F97">
-        <v>0.6</v>
+        <v>0.31</v>
       </c>
       <c r="G97" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3243,22 +4443,22 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C98" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D98" t="s">
-        <v>205</v>
+        <v>405</v>
       </c>
       <c r="E98" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F98">
-        <v>0.24</v>
+        <v>0.92</v>
       </c>
       <c r="G98" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3266,22 +4466,22 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C99" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D99" t="s">
-        <v>206</v>
+        <v>406</v>
       </c>
       <c r="E99" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F99">
-        <v>0.34</v>
+        <v>0.16</v>
       </c>
       <c r="G99" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3289,22 +4489,22 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="C100" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="D100" t="s">
-        <v>207</v>
+        <v>407</v>
       </c>
       <c r="E100" t="s">
-        <v>209</v>
+        <v>609</v>
       </c>
       <c r="F100">
-        <v>0.58</v>
+        <v>0.21</v>
       </c>
       <c r="G100" t="s">
-        <v>210</v>
+        <v>610</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3312,22 +4512,4622 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
+        <v>307</v>
+      </c>
+      <c r="C101" t="s">
+        <v>308</v>
+      </c>
+      <c r="D101" t="s">
+        <v>408</v>
+      </c>
+      <c r="E101" t="s">
+        <v>609</v>
+      </c>
+      <c r="F101">
+        <v>0.3</v>
+      </c>
+      <c r="G101" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
         <v>107</v>
       </c>
-      <c r="C101" t="s">
+      <c r="B102" t="s">
+        <v>307</v>
+      </c>
+      <c r="C102" t="s">
+        <v>308</v>
+      </c>
+      <c r="D102" t="s">
+        <v>409</v>
+      </c>
+      <c r="E102" t="s">
+        <v>609</v>
+      </c>
+      <c r="F102">
+        <v>0.12</v>
+      </c>
+      <c r="G102" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" t="s">
         <v>108</v>
       </c>
-      <c r="D101" t="s">
+      <c r="B103" t="s">
+        <v>307</v>
+      </c>
+      <c r="C103" t="s">
+        <v>308</v>
+      </c>
+      <c r="D103" t="s">
+        <v>410</v>
+      </c>
+      <c r="E103" t="s">
+        <v>609</v>
+      </c>
+      <c r="F103">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G103" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" t="s">
+        <v>109</v>
+      </c>
+      <c r="B104" t="s">
+        <v>307</v>
+      </c>
+      <c r="C104" t="s">
+        <v>308</v>
+      </c>
+      <c r="D104" t="s">
+        <v>411</v>
+      </c>
+      <c r="E104" t="s">
+        <v>609</v>
+      </c>
+      <c r="F104">
+        <v>0.62</v>
+      </c>
+      <c r="G104" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
+        <v>110</v>
+      </c>
+      <c r="B105" t="s">
+        <v>307</v>
+      </c>
+      <c r="C105" t="s">
+        <v>308</v>
+      </c>
+      <c r="D105" t="s">
+        <v>412</v>
+      </c>
+      <c r="E105" t="s">
+        <v>609</v>
+      </c>
+      <c r="F105">
+        <v>0.55</v>
+      </c>
+      <c r="G105" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" t="s">
+        <v>111</v>
+      </c>
+      <c r="B106" t="s">
+        <v>307</v>
+      </c>
+      <c r="C106" t="s">
+        <v>308</v>
+      </c>
+      <c r="D106" t="s">
+        <v>413</v>
+      </c>
+      <c r="E106" t="s">
+        <v>609</v>
+      </c>
+      <c r="F106">
+        <v>0.7</v>
+      </c>
+      <c r="G106" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" t="s">
+        <v>307</v>
+      </c>
+      <c r="C107" t="s">
+        <v>308</v>
+      </c>
+      <c r="D107" t="s">
+        <v>414</v>
+      </c>
+      <c r="E107" t="s">
+        <v>609</v>
+      </c>
+      <c r="F107">
+        <v>0.96</v>
+      </c>
+      <c r="G107" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
+        <v>113</v>
+      </c>
+      <c r="B108" t="s">
+        <v>307</v>
+      </c>
+      <c r="C108" t="s">
+        <v>308</v>
+      </c>
+      <c r="D108" t="s">
+        <v>415</v>
+      </c>
+      <c r="E108" t="s">
+        <v>609</v>
+      </c>
+      <c r="F108">
+        <v>0.15</v>
+      </c>
+      <c r="G108" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" t="s">
+        <v>307</v>
+      </c>
+      <c r="C109" t="s">
+        <v>308</v>
+      </c>
+      <c r="D109" t="s">
+        <v>416</v>
+      </c>
+      <c r="E109" t="s">
+        <v>609</v>
+      </c>
+      <c r="F109">
+        <v>0.1</v>
+      </c>
+      <c r="G109" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" t="s">
+        <v>307</v>
+      </c>
+      <c r="C110" t="s">
+        <v>308</v>
+      </c>
+      <c r="D110" t="s">
+        <v>417</v>
+      </c>
+      <c r="E110" t="s">
+        <v>609</v>
+      </c>
+      <c r="F110">
+        <v>0.96</v>
+      </c>
+      <c r="G110" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" t="s">
+        <v>116</v>
+      </c>
+      <c r="B111" t="s">
+        <v>307</v>
+      </c>
+      <c r="C111" t="s">
+        <v>308</v>
+      </c>
+      <c r="D111" t="s">
+        <v>418</v>
+      </c>
+      <c r="E111" t="s">
+        <v>609</v>
+      </c>
+      <c r="F111">
+        <v>0.3</v>
+      </c>
+      <c r="G111" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" t="s">
+        <v>117</v>
+      </c>
+      <c r="B112" t="s">
+        <v>307</v>
+      </c>
+      <c r="C112" t="s">
+        <v>308</v>
+      </c>
+      <c r="D112" t="s">
+        <v>419</v>
+      </c>
+      <c r="E112" t="s">
+        <v>609</v>
+      </c>
+      <c r="F112">
+        <v>0.14</v>
+      </c>
+      <c r="G112" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" t="s">
+        <v>118</v>
+      </c>
+      <c r="B113" t="s">
+        <v>307</v>
+      </c>
+      <c r="C113" t="s">
+        <v>308</v>
+      </c>
+      <c r="D113" t="s">
+        <v>420</v>
+      </c>
+      <c r="E113" t="s">
+        <v>609</v>
+      </c>
+      <c r="F113">
+        <v>0.22</v>
+      </c>
+      <c r="G113" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" t="s">
+        <v>119</v>
+      </c>
+      <c r="B114" t="s">
+        <v>307</v>
+      </c>
+      <c r="C114" t="s">
+        <v>308</v>
+      </c>
+      <c r="D114" t="s">
+        <v>421</v>
+      </c>
+      <c r="E114" t="s">
+        <v>609</v>
+      </c>
+      <c r="F114">
+        <v>0.29</v>
+      </c>
+      <c r="G114" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" t="s">
+        <v>120</v>
+      </c>
+      <c r="B115" t="s">
+        <v>307</v>
+      </c>
+      <c r="C115" t="s">
+        <v>308</v>
+      </c>
+      <c r="D115" t="s">
+        <v>422</v>
+      </c>
+      <c r="E115" t="s">
+        <v>609</v>
+      </c>
+      <c r="F115">
+        <v>0.15</v>
+      </c>
+      <c r="G115" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" t="s">
+        <v>121</v>
+      </c>
+      <c r="B116" t="s">
+        <v>307</v>
+      </c>
+      <c r="C116" t="s">
+        <v>308</v>
+      </c>
+      <c r="D116" t="s">
+        <v>423</v>
+      </c>
+      <c r="E116" t="s">
+        <v>609</v>
+      </c>
+      <c r="F116">
+        <v>0.43</v>
+      </c>
+      <c r="G116" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" t="s">
+        <v>122</v>
+      </c>
+      <c r="B117" t="s">
+        <v>307</v>
+      </c>
+      <c r="C117" t="s">
+        <v>308</v>
+      </c>
+      <c r="D117" t="s">
+        <v>424</v>
+      </c>
+      <c r="E117" t="s">
+        <v>609</v>
+      </c>
+      <c r="F117">
+        <v>0.97</v>
+      </c>
+      <c r="G117" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" t="s">
+        <v>123</v>
+      </c>
+      <c r="B118" t="s">
+        <v>307</v>
+      </c>
+      <c r="C118" t="s">
+        <v>308</v>
+      </c>
+      <c r="D118" t="s">
+        <v>425</v>
+      </c>
+      <c r="E118" t="s">
+        <v>609</v>
+      </c>
+      <c r="F118">
+        <v>0.72</v>
+      </c>
+      <c r="G118" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B119" t="s">
+        <v>307</v>
+      </c>
+      <c r="C119" t="s">
+        <v>308</v>
+      </c>
+      <c r="D119" t="s">
+        <v>426</v>
+      </c>
+      <c r="E119" t="s">
+        <v>609</v>
+      </c>
+      <c r="F119">
+        <v>0.66</v>
+      </c>
+      <c r="G119" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" t="s">
+        <v>125</v>
+      </c>
+      <c r="B120" t="s">
+        <v>307</v>
+      </c>
+      <c r="C120" t="s">
+        <v>308</v>
+      </c>
+      <c r="D120" t="s">
+        <v>427</v>
+      </c>
+      <c r="E120" t="s">
+        <v>609</v>
+      </c>
+      <c r="F120">
+        <v>0.47</v>
+      </c>
+      <c r="G120" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" t="s">
+        <v>126</v>
+      </c>
+      <c r="B121" t="s">
+        <v>307</v>
+      </c>
+      <c r="C121" t="s">
+        <v>308</v>
+      </c>
+      <c r="D121" t="s">
+        <v>428</v>
+      </c>
+      <c r="E121" t="s">
+        <v>609</v>
+      </c>
+      <c r="F121">
+        <v>0.36</v>
+      </c>
+      <c r="G121" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" t="s">
+        <v>127</v>
+      </c>
+      <c r="B122" t="s">
+        <v>307</v>
+      </c>
+      <c r="C122" t="s">
+        <v>308</v>
+      </c>
+      <c r="D122" t="s">
+        <v>429</v>
+      </c>
+      <c r="E122" t="s">
+        <v>609</v>
+      </c>
+      <c r="F122">
+        <v>0.52</v>
+      </c>
+      <c r="G122" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" t="s">
+        <v>128</v>
+      </c>
+      <c r="B123" t="s">
+        <v>307</v>
+      </c>
+      <c r="C123" t="s">
+        <v>308</v>
+      </c>
+      <c r="D123" t="s">
+        <v>430</v>
+      </c>
+      <c r="E123" t="s">
+        <v>609</v>
+      </c>
+      <c r="F123">
+        <v>0.47</v>
+      </c>
+      <c r="G123" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" t="s">
+        <v>129</v>
+      </c>
+      <c r="B124" t="s">
+        <v>307</v>
+      </c>
+      <c r="C124" t="s">
+        <v>308</v>
+      </c>
+      <c r="D124" t="s">
+        <v>431</v>
+      </c>
+      <c r="E124" t="s">
+        <v>609</v>
+      </c>
+      <c r="F124">
+        <v>0.97</v>
+      </c>
+      <c r="G124" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" t="s">
+        <v>130</v>
+      </c>
+      <c r="B125" t="s">
+        <v>307</v>
+      </c>
+      <c r="C125" t="s">
+        <v>308</v>
+      </c>
+      <c r="D125" t="s">
+        <v>432</v>
+      </c>
+      <c r="E125" t="s">
+        <v>609</v>
+      </c>
+      <c r="F125">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G125" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" t="s">
+        <v>131</v>
+      </c>
+      <c r="B126" t="s">
+        <v>307</v>
+      </c>
+      <c r="C126" t="s">
+        <v>308</v>
+      </c>
+      <c r="D126" t="s">
+        <v>433</v>
+      </c>
+      <c r="E126" t="s">
+        <v>609</v>
+      </c>
+      <c r="F126">
+        <v>0.57</v>
+      </c>
+      <c r="G126" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" t="s">
+        <v>132</v>
+      </c>
+      <c r="B127" t="s">
+        <v>307</v>
+      </c>
+      <c r="C127" t="s">
+        <v>308</v>
+      </c>
+      <c r="D127" t="s">
+        <v>434</v>
+      </c>
+      <c r="E127" t="s">
+        <v>609</v>
+      </c>
+      <c r="F127">
+        <v>0.76</v>
+      </c>
+      <c r="G127" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" t="s">
+        <v>133</v>
+      </c>
+      <c r="B128" t="s">
+        <v>307</v>
+      </c>
+      <c r="C128" t="s">
+        <v>308</v>
+      </c>
+      <c r="D128" t="s">
+        <v>435</v>
+      </c>
+      <c r="E128" t="s">
+        <v>609</v>
+      </c>
+      <c r="F128">
+        <v>0.36</v>
+      </c>
+      <c r="G128" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" t="s">
+        <v>134</v>
+      </c>
+      <c r="B129" t="s">
+        <v>307</v>
+      </c>
+      <c r="C129" t="s">
+        <v>308</v>
+      </c>
+      <c r="D129" t="s">
+        <v>436</v>
+      </c>
+      <c r="E129" t="s">
+        <v>609</v>
+      </c>
+      <c r="F129">
+        <v>0.43</v>
+      </c>
+      <c r="G129" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" t="s">
+        <v>135</v>
+      </c>
+      <c r="B130" t="s">
+        <v>307</v>
+      </c>
+      <c r="C130" t="s">
+        <v>308</v>
+      </c>
+      <c r="D130" t="s">
+        <v>437</v>
+      </c>
+      <c r="E130" t="s">
+        <v>609</v>
+      </c>
+      <c r="F130">
+        <v>0.18</v>
+      </c>
+      <c r="G130" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" t="s">
+        <v>136</v>
+      </c>
+      <c r="B131" t="s">
+        <v>307</v>
+      </c>
+      <c r="C131" t="s">
+        <v>308</v>
+      </c>
+      <c r="D131" t="s">
+        <v>438</v>
+      </c>
+      <c r="E131" t="s">
+        <v>609</v>
+      </c>
+      <c r="F131">
+        <v>0.88</v>
+      </c>
+      <c r="G131" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" t="s">
+        <v>137</v>
+      </c>
+      <c r="B132" t="s">
+        <v>307</v>
+      </c>
+      <c r="C132" t="s">
+        <v>308</v>
+      </c>
+      <c r="D132" t="s">
+        <v>439</v>
+      </c>
+      <c r="E132" t="s">
+        <v>609</v>
+      </c>
+      <c r="F132">
+        <v>0.8</v>
+      </c>
+      <c r="G132" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" t="s">
+        <v>138</v>
+      </c>
+      <c r="B133" t="s">
+        <v>307</v>
+      </c>
+      <c r="C133" t="s">
+        <v>308</v>
+      </c>
+      <c r="D133" t="s">
+        <v>440</v>
+      </c>
+      <c r="E133" t="s">
+        <v>609</v>
+      </c>
+      <c r="F133">
+        <v>0.53</v>
+      </c>
+      <c r="G133" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" t="s">
+        <v>139</v>
+      </c>
+      <c r="B134" t="s">
+        <v>307</v>
+      </c>
+      <c r="C134" t="s">
+        <v>308</v>
+      </c>
+      <c r="D134" t="s">
+        <v>441</v>
+      </c>
+      <c r="E134" t="s">
+        <v>609</v>
+      </c>
+      <c r="F134">
+        <v>0.61</v>
+      </c>
+      <c r="G134" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" t="s">
+        <v>140</v>
+      </c>
+      <c r="B135" t="s">
+        <v>307</v>
+      </c>
+      <c r="C135" t="s">
+        <v>308</v>
+      </c>
+      <c r="D135" t="s">
+        <v>442</v>
+      </c>
+      <c r="E135" t="s">
+        <v>609</v>
+      </c>
+      <c r="F135">
+        <v>0.96</v>
+      </c>
+      <c r="G135" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" t="s">
+        <v>141</v>
+      </c>
+      <c r="B136" t="s">
+        <v>307</v>
+      </c>
+      <c r="C136" t="s">
+        <v>308</v>
+      </c>
+      <c r="D136" t="s">
+        <v>443</v>
+      </c>
+      <c r="E136" t="s">
+        <v>609</v>
+      </c>
+      <c r="F136">
+        <v>0.68</v>
+      </c>
+      <c r="G136" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" t="s">
+        <v>142</v>
+      </c>
+      <c r="B137" t="s">
+        <v>307</v>
+      </c>
+      <c r="C137" t="s">
+        <v>308</v>
+      </c>
+      <c r="D137" t="s">
+        <v>444</v>
+      </c>
+      <c r="E137" t="s">
+        <v>609</v>
+      </c>
+      <c r="F137">
+        <v>0.16</v>
+      </c>
+      <c r="G137" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" t="s">
+        <v>143</v>
+      </c>
+      <c r="B138" t="s">
+        <v>307</v>
+      </c>
+      <c r="C138" t="s">
+        <v>308</v>
+      </c>
+      <c r="D138" t="s">
+        <v>445</v>
+      </c>
+      <c r="E138" t="s">
+        <v>609</v>
+      </c>
+      <c r="F138">
+        <v>0.48</v>
+      </c>
+      <c r="G138" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" t="s">
+        <v>144</v>
+      </c>
+      <c r="B139" t="s">
+        <v>307</v>
+      </c>
+      <c r="C139" t="s">
+        <v>308</v>
+      </c>
+      <c r="D139" t="s">
+        <v>446</v>
+      </c>
+      <c r="E139" t="s">
+        <v>609</v>
+      </c>
+      <c r="F139">
+        <v>0.66</v>
+      </c>
+      <c r="G139" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" t="s">
+        <v>145</v>
+      </c>
+      <c r="B140" t="s">
+        <v>307</v>
+      </c>
+      <c r="C140" t="s">
+        <v>308</v>
+      </c>
+      <c r="D140" t="s">
+        <v>447</v>
+      </c>
+      <c r="E140" t="s">
+        <v>609</v>
+      </c>
+      <c r="F140">
+        <v>0.27</v>
+      </c>
+      <c r="G140" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" t="s">
+        <v>146</v>
+      </c>
+      <c r="B141" t="s">
+        <v>307</v>
+      </c>
+      <c r="C141" t="s">
+        <v>308</v>
+      </c>
+      <c r="D141" t="s">
+        <v>448</v>
+      </c>
+      <c r="E141" t="s">
+        <v>609</v>
+      </c>
+      <c r="F141">
+        <v>0.15</v>
+      </c>
+      <c r="G141" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" t="s">
+        <v>147</v>
+      </c>
+      <c r="B142" t="s">
+        <v>307</v>
+      </c>
+      <c r="C142" t="s">
+        <v>308</v>
+      </c>
+      <c r="D142" t="s">
+        <v>449</v>
+      </c>
+      <c r="E142" t="s">
+        <v>609</v>
+      </c>
+      <c r="F142">
+        <v>0.63</v>
+      </c>
+      <c r="G142" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" t="s">
+        <v>148</v>
+      </c>
+      <c r="B143" t="s">
+        <v>307</v>
+      </c>
+      <c r="C143" t="s">
+        <v>308</v>
+      </c>
+      <c r="D143" t="s">
+        <v>450</v>
+      </c>
+      <c r="E143" t="s">
+        <v>609</v>
+      </c>
+      <c r="F143">
+        <v>0.35</v>
+      </c>
+      <c r="G143" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" t="s">
+        <v>149</v>
+      </c>
+      <c r="B144" t="s">
+        <v>307</v>
+      </c>
+      <c r="C144" t="s">
+        <v>308</v>
+      </c>
+      <c r="D144" t="s">
+        <v>451</v>
+      </c>
+      <c r="E144" t="s">
+        <v>609</v>
+      </c>
+      <c r="F144">
+        <v>0.38</v>
+      </c>
+      <c r="G144" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" t="s">
+        <v>150</v>
+      </c>
+      <c r="B145" t="s">
+        <v>307</v>
+      </c>
+      <c r="C145" t="s">
+        <v>308</v>
+      </c>
+      <c r="D145" t="s">
+        <v>452</v>
+      </c>
+      <c r="E145" t="s">
+        <v>609</v>
+      </c>
+      <c r="F145">
+        <v>0.12</v>
+      </c>
+      <c r="G145" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" t="s">
+        <v>151</v>
+      </c>
+      <c r="B146" t="s">
+        <v>307</v>
+      </c>
+      <c r="C146" t="s">
+        <v>308</v>
+      </c>
+      <c r="D146" t="s">
+        <v>453</v>
+      </c>
+      <c r="E146" t="s">
+        <v>609</v>
+      </c>
+      <c r="F146">
+        <v>0.93</v>
+      </c>
+      <c r="G146" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" t="s">
+        <v>152</v>
+      </c>
+      <c r="B147" t="s">
+        <v>307</v>
+      </c>
+      <c r="C147" t="s">
+        <v>308</v>
+      </c>
+      <c r="D147" t="s">
+        <v>454</v>
+      </c>
+      <c r="E147" t="s">
+        <v>609</v>
+      </c>
+      <c r="F147">
+        <v>0.45</v>
+      </c>
+      <c r="G147" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" t="s">
+        <v>153</v>
+      </c>
+      <c r="B148" t="s">
+        <v>307</v>
+      </c>
+      <c r="C148" t="s">
+        <v>308</v>
+      </c>
+      <c r="D148" t="s">
+        <v>455</v>
+      </c>
+      <c r="E148" t="s">
+        <v>609</v>
+      </c>
+      <c r="F148">
+        <v>0.2</v>
+      </c>
+      <c r="G148" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" t="s">
+        <v>154</v>
+      </c>
+      <c r="B149" t="s">
+        <v>307</v>
+      </c>
+      <c r="C149" t="s">
+        <v>308</v>
+      </c>
+      <c r="D149" t="s">
+        <v>456</v>
+      </c>
+      <c r="E149" t="s">
+        <v>609</v>
+      </c>
+      <c r="F149">
+        <v>0.39</v>
+      </c>
+      <c r="G149" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" t="s">
+        <v>155</v>
+      </c>
+      <c r="B150" t="s">
+        <v>307</v>
+      </c>
+      <c r="C150" t="s">
+        <v>308</v>
+      </c>
+      <c r="D150" t="s">
+        <v>457</v>
+      </c>
+      <c r="E150" t="s">
+        <v>609</v>
+      </c>
+      <c r="F150">
+        <v>0.51</v>
+      </c>
+      <c r="G150" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" t="s">
+        <v>156</v>
+      </c>
+      <c r="B151" t="s">
+        <v>307</v>
+      </c>
+      <c r="C151" t="s">
+        <v>308</v>
+      </c>
+      <c r="D151" t="s">
+        <v>458</v>
+      </c>
+      <c r="E151" t="s">
+        <v>609</v>
+      </c>
+      <c r="F151">
+        <v>0.39</v>
+      </c>
+      <c r="G151" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" t="s">
+        <v>157</v>
+      </c>
+      <c r="B152" t="s">
+        <v>307</v>
+      </c>
+      <c r="C152" t="s">
+        <v>308</v>
+      </c>
+      <c r="D152" t="s">
+        <v>459</v>
+      </c>
+      <c r="E152" t="s">
+        <v>609</v>
+      </c>
+      <c r="F152">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G152" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" t="s">
+        <v>158</v>
+      </c>
+      <c r="B153" t="s">
+        <v>307</v>
+      </c>
+      <c r="C153" t="s">
+        <v>308</v>
+      </c>
+      <c r="D153" t="s">
+        <v>460</v>
+      </c>
+      <c r="E153" t="s">
+        <v>609</v>
+      </c>
+      <c r="F153">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G153" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" t="s">
+        <v>159</v>
+      </c>
+      <c r="B154" t="s">
+        <v>307</v>
+      </c>
+      <c r="C154" t="s">
+        <v>308</v>
+      </c>
+      <c r="D154" t="s">
+        <v>461</v>
+      </c>
+      <c r="E154" t="s">
+        <v>609</v>
+      </c>
+      <c r="F154">
+        <v>0.2</v>
+      </c>
+      <c r="G154" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" t="s">
+        <v>160</v>
+      </c>
+      <c r="B155" t="s">
+        <v>307</v>
+      </c>
+      <c r="C155" t="s">
+        <v>308</v>
+      </c>
+      <c r="D155" t="s">
+        <v>462</v>
+      </c>
+      <c r="E155" t="s">
+        <v>609</v>
+      </c>
+      <c r="F155">
+        <v>0.2</v>
+      </c>
+      <c r="G155" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" t="s">
+        <v>161</v>
+      </c>
+      <c r="B156" t="s">
+        <v>307</v>
+      </c>
+      <c r="C156" t="s">
+        <v>308</v>
+      </c>
+      <c r="D156" t="s">
+        <v>463</v>
+      </c>
+      <c r="E156" t="s">
+        <v>609</v>
+      </c>
+      <c r="F156">
+        <v>0.89</v>
+      </c>
+      <c r="G156" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" t="s">
+        <v>162</v>
+      </c>
+      <c r="B157" t="s">
+        <v>307</v>
+      </c>
+      <c r="C157" t="s">
+        <v>308</v>
+      </c>
+      <c r="D157" t="s">
+        <v>464</v>
+      </c>
+      <c r="E157" t="s">
+        <v>609</v>
+      </c>
+      <c r="F157">
+        <v>0.71</v>
+      </c>
+      <c r="G157" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" t="s">
+        <v>163</v>
+      </c>
+      <c r="B158" t="s">
+        <v>307</v>
+      </c>
+      <c r="C158" t="s">
+        <v>308</v>
+      </c>
+      <c r="D158" t="s">
+        <v>465</v>
+      </c>
+      <c r="E158" t="s">
+        <v>609</v>
+      </c>
+      <c r="F158">
+        <v>0.21</v>
+      </c>
+      <c r="G158" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" t="s">
+        <v>164</v>
+      </c>
+      <c r="B159" t="s">
+        <v>307</v>
+      </c>
+      <c r="C159" t="s">
+        <v>308</v>
+      </c>
+      <c r="D159" t="s">
+        <v>466</v>
+      </c>
+      <c r="E159" t="s">
+        <v>609</v>
+      </c>
+      <c r="F159">
+        <v>0.29</v>
+      </c>
+      <c r="G159" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" t="s">
+        <v>165</v>
+      </c>
+      <c r="B160" t="s">
+        <v>307</v>
+      </c>
+      <c r="C160" t="s">
+        <v>308</v>
+      </c>
+      <c r="D160" t="s">
+        <v>467</v>
+      </c>
+      <c r="E160" t="s">
+        <v>609</v>
+      </c>
+      <c r="F160">
+        <v>0.8</v>
+      </c>
+      <c r="G160" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
+        <v>166</v>
+      </c>
+      <c r="B161" t="s">
+        <v>307</v>
+      </c>
+      <c r="C161" t="s">
+        <v>308</v>
+      </c>
+      <c r="D161" t="s">
+        <v>468</v>
+      </c>
+      <c r="E161" t="s">
+        <v>609</v>
+      </c>
+      <c r="F161">
+        <v>0.53</v>
+      </c>
+      <c r="G161" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" t="s">
+        <v>167</v>
+      </c>
+      <c r="B162" t="s">
+        <v>307</v>
+      </c>
+      <c r="C162" t="s">
+        <v>308</v>
+      </c>
+      <c r="D162" t="s">
+        <v>469</v>
+      </c>
+      <c r="E162" t="s">
+        <v>609</v>
+      </c>
+      <c r="F162">
+        <v>0.59</v>
+      </c>
+      <c r="G162" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
+        <v>168</v>
+      </c>
+      <c r="B163" t="s">
+        <v>307</v>
+      </c>
+      <c r="C163" t="s">
+        <v>308</v>
+      </c>
+      <c r="D163" t="s">
+        <v>470</v>
+      </c>
+      <c r="E163" t="s">
+        <v>609</v>
+      </c>
+      <c r="F163">
+        <v>0.5</v>
+      </c>
+      <c r="G163" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" t="s">
+        <v>169</v>
+      </c>
+      <c r="B164" t="s">
+        <v>307</v>
+      </c>
+      <c r="C164" t="s">
+        <v>308</v>
+      </c>
+      <c r="D164" t="s">
+        <v>471</v>
+      </c>
+      <c r="E164" t="s">
+        <v>609</v>
+      </c>
+      <c r="F164">
+        <v>0.76</v>
+      </c>
+      <c r="G164" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
+        <v>170</v>
+      </c>
+      <c r="B165" t="s">
+        <v>307</v>
+      </c>
+      <c r="C165" t="s">
+        <v>308</v>
+      </c>
+      <c r="D165" t="s">
+        <v>472</v>
+      </c>
+      <c r="E165" t="s">
+        <v>609</v>
+      </c>
+      <c r="F165">
+        <v>0.46</v>
+      </c>
+      <c r="G165" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" t="s">
+        <v>171</v>
+      </c>
+      <c r="B166" t="s">
+        <v>307</v>
+      </c>
+      <c r="C166" t="s">
+        <v>308</v>
+      </c>
+      <c r="D166" t="s">
+        <v>473</v>
+      </c>
+      <c r="E166" t="s">
+        <v>609</v>
+      </c>
+      <c r="F166">
+        <v>0.39</v>
+      </c>
+      <c r="G166" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" t="s">
+        <v>172</v>
+      </c>
+      <c r="B167" t="s">
+        <v>307</v>
+      </c>
+      <c r="C167" t="s">
+        <v>308</v>
+      </c>
+      <c r="D167" t="s">
+        <v>474</v>
+      </c>
+      <c r="E167" t="s">
+        <v>609</v>
+      </c>
+      <c r="F167">
+        <v>0.18</v>
+      </c>
+      <c r="G167" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" t="s">
+        <v>173</v>
+      </c>
+      <c r="B168" t="s">
+        <v>307</v>
+      </c>
+      <c r="C168" t="s">
+        <v>308</v>
+      </c>
+      <c r="D168" t="s">
+        <v>475</v>
+      </c>
+      <c r="E168" t="s">
+        <v>609</v>
+      </c>
+      <c r="F168">
+        <v>0.41</v>
+      </c>
+      <c r="G168" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" t="s">
+        <v>174</v>
+      </c>
+      <c r="B169" t="s">
+        <v>307</v>
+      </c>
+      <c r="C169" t="s">
+        <v>308</v>
+      </c>
+      <c r="D169" t="s">
+        <v>476</v>
+      </c>
+      <c r="E169" t="s">
+        <v>609</v>
+      </c>
+      <c r="F169">
+        <v>0.96</v>
+      </c>
+      <c r="G169" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" t="s">
+        <v>175</v>
+      </c>
+      <c r="B170" t="s">
+        <v>307</v>
+      </c>
+      <c r="C170" t="s">
+        <v>308</v>
+      </c>
+      <c r="D170" t="s">
+        <v>477</v>
+      </c>
+      <c r="E170" t="s">
+        <v>609</v>
+      </c>
+      <c r="F170">
+        <v>0.51</v>
+      </c>
+      <c r="G170" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" t="s">
+        <v>176</v>
+      </c>
+      <c r="B171" t="s">
+        <v>307</v>
+      </c>
+      <c r="C171" t="s">
+        <v>308</v>
+      </c>
+      <c r="D171" t="s">
+        <v>478</v>
+      </c>
+      <c r="E171" t="s">
+        <v>609</v>
+      </c>
+      <c r="F171">
+        <v>0.22</v>
+      </c>
+      <c r="G171" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" t="s">
+        <v>177</v>
+      </c>
+      <c r="B172" t="s">
+        <v>307</v>
+      </c>
+      <c r="C172" t="s">
+        <v>308</v>
+      </c>
+      <c r="D172" t="s">
+        <v>479</v>
+      </c>
+      <c r="E172" t="s">
+        <v>609</v>
+      </c>
+      <c r="F172">
+        <v>0.82</v>
+      </c>
+      <c r="G172" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" t="s">
+        <v>178</v>
+      </c>
+      <c r="B173" t="s">
+        <v>307</v>
+      </c>
+      <c r="C173" t="s">
+        <v>308</v>
+      </c>
+      <c r="D173" t="s">
+        <v>480</v>
+      </c>
+      <c r="E173" t="s">
+        <v>609</v>
+      </c>
+      <c r="F173">
+        <v>0.58</v>
+      </c>
+      <c r="G173" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" t="s">
+        <v>179</v>
+      </c>
+      <c r="B174" t="s">
+        <v>307</v>
+      </c>
+      <c r="C174" t="s">
+        <v>308</v>
+      </c>
+      <c r="D174" t="s">
+        <v>481</v>
+      </c>
+      <c r="E174" t="s">
+        <v>609</v>
+      </c>
+      <c r="F174">
+        <v>0.74</v>
+      </c>
+      <c r="G174" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" t="s">
+        <v>180</v>
+      </c>
+      <c r="B175" t="s">
+        <v>307</v>
+      </c>
+      <c r="C175" t="s">
+        <v>308</v>
+      </c>
+      <c r="D175" t="s">
+        <v>482</v>
+      </c>
+      <c r="E175" t="s">
+        <v>609</v>
+      </c>
+      <c r="F175">
+        <v>0.52</v>
+      </c>
+      <c r="G175" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" t="s">
+        <v>181</v>
+      </c>
+      <c r="B176" t="s">
+        <v>307</v>
+      </c>
+      <c r="C176" t="s">
+        <v>308</v>
+      </c>
+      <c r="D176" t="s">
+        <v>483</v>
+      </c>
+      <c r="E176" t="s">
+        <v>609</v>
+      </c>
+      <c r="F176">
+        <v>0.82</v>
+      </c>
+      <c r="G176" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" t="s">
+        <v>182</v>
+      </c>
+      <c r="B177" t="s">
+        <v>307</v>
+      </c>
+      <c r="C177" t="s">
+        <v>308</v>
+      </c>
+      <c r="D177" t="s">
+        <v>484</v>
+      </c>
+      <c r="E177" t="s">
+        <v>609</v>
+      </c>
+      <c r="F177">
+        <v>0.19</v>
+      </c>
+      <c r="G177" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" t="s">
+        <v>183</v>
+      </c>
+      <c r="B178" t="s">
+        <v>307</v>
+      </c>
+      <c r="C178" t="s">
+        <v>308</v>
+      </c>
+      <c r="D178" t="s">
+        <v>485</v>
+      </c>
+      <c r="E178" t="s">
+        <v>609</v>
+      </c>
+      <c r="F178">
+        <v>0.76</v>
+      </c>
+      <c r="G178" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" t="s">
+        <v>184</v>
+      </c>
+      <c r="B179" t="s">
+        <v>307</v>
+      </c>
+      <c r="C179" t="s">
+        <v>308</v>
+      </c>
+      <c r="D179" t="s">
+        <v>486</v>
+      </c>
+      <c r="E179" t="s">
+        <v>609</v>
+      </c>
+      <c r="F179">
+        <v>0.64</v>
+      </c>
+      <c r="G179" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" t="s">
+        <v>185</v>
+      </c>
+      <c r="B180" t="s">
+        <v>307</v>
+      </c>
+      <c r="C180" t="s">
+        <v>308</v>
+      </c>
+      <c r="D180" t="s">
+        <v>487</v>
+      </c>
+      <c r="E180" t="s">
+        <v>609</v>
+      </c>
+      <c r="F180">
+        <v>0.24</v>
+      </c>
+      <c r="G180" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" t="s">
+        <v>186</v>
+      </c>
+      <c r="B181" t="s">
+        <v>307</v>
+      </c>
+      <c r="C181" t="s">
+        <v>308</v>
+      </c>
+      <c r="D181" t="s">
+        <v>488</v>
+      </c>
+      <c r="E181" t="s">
+        <v>609</v>
+      </c>
+      <c r="F181">
+        <v>0.12</v>
+      </c>
+      <c r="G181" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" t="s">
+        <v>187</v>
+      </c>
+      <c r="B182" t="s">
+        <v>307</v>
+      </c>
+      <c r="C182" t="s">
+        <v>308</v>
+      </c>
+      <c r="D182" t="s">
+        <v>489</v>
+      </c>
+      <c r="E182" t="s">
+        <v>609</v>
+      </c>
+      <c r="F182">
+        <v>0.6</v>
+      </c>
+      <c r="G182" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" t="s">
+        <v>188</v>
+      </c>
+      <c r="B183" t="s">
+        <v>307</v>
+      </c>
+      <c r="C183" t="s">
+        <v>308</v>
+      </c>
+      <c r="D183" t="s">
+        <v>490</v>
+      </c>
+      <c r="E183" t="s">
+        <v>609</v>
+      </c>
+      <c r="F183">
+        <v>0.91</v>
+      </c>
+      <c r="G183" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" t="s">
+        <v>189</v>
+      </c>
+      <c r="B184" t="s">
+        <v>307</v>
+      </c>
+      <c r="C184" t="s">
+        <v>308</v>
+      </c>
+      <c r="D184" t="s">
+        <v>491</v>
+      </c>
+      <c r="E184" t="s">
+        <v>609</v>
+      </c>
+      <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="G184" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" t="s">
+        <v>190</v>
+      </c>
+      <c r="B185" t="s">
+        <v>307</v>
+      </c>
+      <c r="C185" t="s">
+        <v>308</v>
+      </c>
+      <c r="D185" t="s">
+        <v>492</v>
+      </c>
+      <c r="E185" t="s">
+        <v>609</v>
+      </c>
+      <c r="F185">
+        <v>0.88</v>
+      </c>
+      <c r="G185" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" t="s">
+        <v>191</v>
+      </c>
+      <c r="B186" t="s">
+        <v>307</v>
+      </c>
+      <c r="C186" t="s">
+        <v>308</v>
+      </c>
+      <c r="D186" t="s">
+        <v>493</v>
+      </c>
+      <c r="E186" t="s">
+        <v>609</v>
+      </c>
+      <c r="F186">
+        <v>0.8</v>
+      </c>
+      <c r="G186" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" t="s">
+        <v>192</v>
+      </c>
+      <c r="B187" t="s">
+        <v>307</v>
+      </c>
+      <c r="C187" t="s">
+        <v>308</v>
+      </c>
+      <c r="D187" t="s">
+        <v>494</v>
+      </c>
+      <c r="E187" t="s">
+        <v>609</v>
+      </c>
+      <c r="F187">
+        <v>0.87</v>
+      </c>
+      <c r="G187" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" t="s">
+        <v>193</v>
+      </c>
+      <c r="B188" t="s">
+        <v>307</v>
+      </c>
+      <c r="C188" t="s">
+        <v>308</v>
+      </c>
+      <c r="D188" t="s">
+        <v>495</v>
+      </c>
+      <c r="E188" t="s">
+        <v>609</v>
+      </c>
+      <c r="F188">
+        <v>0.84</v>
+      </c>
+      <c r="G188" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" t="s">
+        <v>194</v>
+      </c>
+      <c r="B189" t="s">
+        <v>307</v>
+      </c>
+      <c r="C189" t="s">
+        <v>308</v>
+      </c>
+      <c r="D189" t="s">
+        <v>496</v>
+      </c>
+      <c r="E189" t="s">
+        <v>609</v>
+      </c>
+      <c r="F189">
+        <v>0.21</v>
+      </c>
+      <c r="G189" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" t="s">
+        <v>195</v>
+      </c>
+      <c r="B190" t="s">
+        <v>307</v>
+      </c>
+      <c r="C190" t="s">
+        <v>308</v>
+      </c>
+      <c r="D190" t="s">
+        <v>497</v>
+      </c>
+      <c r="E190" t="s">
+        <v>609</v>
+      </c>
+      <c r="F190">
+        <v>0.55</v>
+      </c>
+      <c r="G190" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" t="s">
+        <v>196</v>
+      </c>
+      <c r="B191" t="s">
+        <v>307</v>
+      </c>
+      <c r="C191" t="s">
+        <v>308</v>
+      </c>
+      <c r="D191" t="s">
+        <v>498</v>
+      </c>
+      <c r="E191" t="s">
+        <v>609</v>
+      </c>
+      <c r="F191">
+        <v>0.84</v>
+      </c>
+      <c r="G191" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" t="s">
+        <v>197</v>
+      </c>
+      <c r="B192" t="s">
+        <v>307</v>
+      </c>
+      <c r="C192" t="s">
+        <v>308</v>
+      </c>
+      <c r="D192" t="s">
+        <v>499</v>
+      </c>
+      <c r="E192" t="s">
+        <v>609</v>
+      </c>
+      <c r="F192">
+        <v>0.22</v>
+      </c>
+      <c r="G192" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" t="s">
+        <v>198</v>
+      </c>
+      <c r="B193" t="s">
+        <v>307</v>
+      </c>
+      <c r="C193" t="s">
+        <v>308</v>
+      </c>
+      <c r="D193" t="s">
+        <v>500</v>
+      </c>
+      <c r="E193" t="s">
+        <v>609</v>
+      </c>
+      <c r="F193">
+        <v>0.7</v>
+      </c>
+      <c r="G193" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" t="s">
+        <v>199</v>
+      </c>
+      <c r="B194" t="s">
+        <v>307</v>
+      </c>
+      <c r="C194" t="s">
+        <v>308</v>
+      </c>
+      <c r="D194" t="s">
+        <v>501</v>
+      </c>
+      <c r="E194" t="s">
+        <v>609</v>
+      </c>
+      <c r="F194">
+        <v>0.57</v>
+      </c>
+      <c r="G194" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" t="s">
+        <v>200</v>
+      </c>
+      <c r="B195" t="s">
+        <v>307</v>
+      </c>
+      <c r="C195" t="s">
+        <v>308</v>
+      </c>
+      <c r="D195" t="s">
+        <v>502</v>
+      </c>
+      <c r="E195" t="s">
+        <v>609</v>
+      </c>
+      <c r="F195">
+        <v>0.61</v>
+      </c>
+      <c r="G195" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" t="s">
+        <v>201</v>
+      </c>
+      <c r="B196" t="s">
+        <v>307</v>
+      </c>
+      <c r="C196" t="s">
+        <v>308</v>
+      </c>
+      <c r="D196" t="s">
+        <v>503</v>
+      </c>
+      <c r="E196" t="s">
+        <v>609</v>
+      </c>
+      <c r="F196">
+        <v>0.71</v>
+      </c>
+      <c r="G196" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" t="s">
+        <v>202</v>
+      </c>
+      <c r="B197" t="s">
+        <v>307</v>
+      </c>
+      <c r="C197" t="s">
+        <v>308</v>
+      </c>
+      <c r="D197" t="s">
+        <v>504</v>
+      </c>
+      <c r="E197" t="s">
+        <v>609</v>
+      </c>
+      <c r="F197">
+        <v>0.49</v>
+      </c>
+      <c r="G197" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" t="s">
+        <v>203</v>
+      </c>
+      <c r="B198" t="s">
+        <v>307</v>
+      </c>
+      <c r="C198" t="s">
+        <v>308</v>
+      </c>
+      <c r="D198" t="s">
+        <v>505</v>
+      </c>
+      <c r="E198" t="s">
+        <v>609</v>
+      </c>
+      <c r="F198">
+        <v>0.65</v>
+      </c>
+      <c r="G198" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" t="s">
+        <v>204</v>
+      </c>
+      <c r="B199" t="s">
+        <v>307</v>
+      </c>
+      <c r="C199" t="s">
+        <v>308</v>
+      </c>
+      <c r="D199" t="s">
+        <v>506</v>
+      </c>
+      <c r="E199" t="s">
+        <v>609</v>
+      </c>
+      <c r="F199">
+        <v>0.34</v>
+      </c>
+      <c r="G199" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" t="s">
+        <v>205</v>
+      </c>
+      <c r="B200" t="s">
+        <v>307</v>
+      </c>
+      <c r="C200" t="s">
+        <v>308</v>
+      </c>
+      <c r="D200" t="s">
+        <v>507</v>
+      </c>
+      <c r="E200" t="s">
+        <v>609</v>
+      </c>
+      <c r="F200">
+        <v>0.89</v>
+      </c>
+      <c r="G200" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" t="s">
+        <v>206</v>
+      </c>
+      <c r="B201" t="s">
+        <v>307</v>
+      </c>
+      <c r="C201" t="s">
+        <v>308</v>
+      </c>
+      <c r="D201" t="s">
+        <v>508</v>
+      </c>
+      <c r="E201" t="s">
+        <v>609</v>
+      </c>
+      <c r="F201">
+        <v>0.68</v>
+      </c>
+      <c r="G201" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" t="s">
+        <v>207</v>
+      </c>
+      <c r="B202" t="s">
+        <v>307</v>
+      </c>
+      <c r="C202" t="s">
+        <v>308</v>
+      </c>
+      <c r="D202" t="s">
+        <v>509</v>
+      </c>
+      <c r="E202" t="s">
+        <v>609</v>
+      </c>
+      <c r="F202">
+        <v>0.11</v>
+      </c>
+      <c r="G202" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" t="s">
         <v>208</v>
       </c>
-      <c r="E101" t="s">
+      <c r="B203" t="s">
+        <v>307</v>
+      </c>
+      <c r="C203" t="s">
+        <v>308</v>
+      </c>
+      <c r="D203" t="s">
+        <v>510</v>
+      </c>
+      <c r="E203" t="s">
+        <v>609</v>
+      </c>
+      <c r="F203">
+        <v>0.87</v>
+      </c>
+      <c r="G203" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" t="s">
         <v>209</v>
       </c>
-      <c r="F101">
-        <v>0.61</v>
-      </c>
-      <c r="G101" t="s">
+      <c r="B204" t="s">
+        <v>307</v>
+      </c>
+      <c r="C204" t="s">
+        <v>308</v>
+      </c>
+      <c r="D204" t="s">
+        <v>511</v>
+      </c>
+      <c r="E204" t="s">
+        <v>609</v>
+      </c>
+      <c r="F204">
+        <v>0.85</v>
+      </c>
+      <c r="G204" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" t="s">
         <v>210</v>
+      </c>
+      <c r="B205" t="s">
+        <v>307</v>
+      </c>
+      <c r="C205" t="s">
+        <v>308</v>
+      </c>
+      <c r="D205" t="s">
+        <v>512</v>
+      </c>
+      <c r="E205" t="s">
+        <v>609</v>
+      </c>
+      <c r="F205">
+        <v>0.14</v>
+      </c>
+      <c r="G205" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" t="s">
+        <v>211</v>
+      </c>
+      <c r="B206" t="s">
+        <v>307</v>
+      </c>
+      <c r="C206" t="s">
+        <v>308</v>
+      </c>
+      <c r="D206" t="s">
+        <v>513</v>
+      </c>
+      <c r="E206" t="s">
+        <v>609</v>
+      </c>
+      <c r="F206">
+        <v>0.37</v>
+      </c>
+      <c r="G206" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" t="s">
+        <v>212</v>
+      </c>
+      <c r="B207" t="s">
+        <v>307</v>
+      </c>
+      <c r="C207" t="s">
+        <v>308</v>
+      </c>
+      <c r="D207" t="s">
+        <v>514</v>
+      </c>
+      <c r="E207" t="s">
+        <v>609</v>
+      </c>
+      <c r="F207">
+        <v>0.36</v>
+      </c>
+      <c r="G207" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" t="s">
+        <v>213</v>
+      </c>
+      <c r="B208" t="s">
+        <v>307</v>
+      </c>
+      <c r="C208" t="s">
+        <v>308</v>
+      </c>
+      <c r="D208" t="s">
+        <v>515</v>
+      </c>
+      <c r="E208" t="s">
+        <v>609</v>
+      </c>
+      <c r="F208">
+        <v>0.12</v>
+      </c>
+      <c r="G208" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" t="s">
+        <v>214</v>
+      </c>
+      <c r="B209" t="s">
+        <v>307</v>
+      </c>
+      <c r="C209" t="s">
+        <v>308</v>
+      </c>
+      <c r="D209" t="s">
+        <v>516</v>
+      </c>
+      <c r="E209" t="s">
+        <v>609</v>
+      </c>
+      <c r="F209">
+        <v>0.88</v>
+      </c>
+      <c r="G209" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" t="s">
+        <v>215</v>
+      </c>
+      <c r="B210" t="s">
+        <v>307</v>
+      </c>
+      <c r="C210" t="s">
+        <v>308</v>
+      </c>
+      <c r="D210" t="s">
+        <v>517</v>
+      </c>
+      <c r="E210" t="s">
+        <v>609</v>
+      </c>
+      <c r="F210">
+        <v>0.21</v>
+      </c>
+      <c r="G210" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211" t="s">
+        <v>216</v>
+      </c>
+      <c r="B211" t="s">
+        <v>307</v>
+      </c>
+      <c r="C211" t="s">
+        <v>308</v>
+      </c>
+      <c r="D211" t="s">
+        <v>518</v>
+      </c>
+      <c r="E211" t="s">
+        <v>609</v>
+      </c>
+      <c r="F211">
+        <v>0.13</v>
+      </c>
+      <c r="G211" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" t="s">
+        <v>217</v>
+      </c>
+      <c r="B212" t="s">
+        <v>307</v>
+      </c>
+      <c r="C212" t="s">
+        <v>308</v>
+      </c>
+      <c r="D212" t="s">
+        <v>519</v>
+      </c>
+      <c r="E212" t="s">
+        <v>609</v>
+      </c>
+      <c r="F212">
+        <v>0.5</v>
+      </c>
+      <c r="G212" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213" t="s">
+        <v>218</v>
+      </c>
+      <c r="B213" t="s">
+        <v>307</v>
+      </c>
+      <c r="C213" t="s">
+        <v>308</v>
+      </c>
+      <c r="D213" t="s">
+        <v>520</v>
+      </c>
+      <c r="E213" t="s">
+        <v>609</v>
+      </c>
+      <c r="F213">
+        <v>0.46</v>
+      </c>
+      <c r="G213" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" t="s">
+        <v>219</v>
+      </c>
+      <c r="B214" t="s">
+        <v>307</v>
+      </c>
+      <c r="C214" t="s">
+        <v>308</v>
+      </c>
+      <c r="D214" t="s">
+        <v>521</v>
+      </c>
+      <c r="E214" t="s">
+        <v>609</v>
+      </c>
+      <c r="F214">
+        <v>0.92</v>
+      </c>
+      <c r="G214" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" t="s">
+        <v>220</v>
+      </c>
+      <c r="B215" t="s">
+        <v>307</v>
+      </c>
+      <c r="C215" t="s">
+        <v>308</v>
+      </c>
+      <c r="D215" t="s">
+        <v>522</v>
+      </c>
+      <c r="E215" t="s">
+        <v>609</v>
+      </c>
+      <c r="F215">
+        <v>0.37</v>
+      </c>
+      <c r="G215" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" t="s">
+        <v>221</v>
+      </c>
+      <c r="B216" t="s">
+        <v>307</v>
+      </c>
+      <c r="C216" t="s">
+        <v>308</v>
+      </c>
+      <c r="D216" t="s">
+        <v>523</v>
+      </c>
+      <c r="E216" t="s">
+        <v>609</v>
+      </c>
+      <c r="F216">
+        <v>0.89</v>
+      </c>
+      <c r="G216" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" t="s">
+        <v>222</v>
+      </c>
+      <c r="B217" t="s">
+        <v>307</v>
+      </c>
+      <c r="C217" t="s">
+        <v>308</v>
+      </c>
+      <c r="D217" t="s">
+        <v>524</v>
+      </c>
+      <c r="E217" t="s">
+        <v>609</v>
+      </c>
+      <c r="F217">
+        <v>0.84</v>
+      </c>
+      <c r="G217" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" t="s">
+        <v>223</v>
+      </c>
+      <c r="B218" t="s">
+        <v>307</v>
+      </c>
+      <c r="C218" t="s">
+        <v>308</v>
+      </c>
+      <c r="D218" t="s">
+        <v>525</v>
+      </c>
+      <c r="E218" t="s">
+        <v>609</v>
+      </c>
+      <c r="F218">
+        <v>0.63</v>
+      </c>
+      <c r="G218" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219" t="s">
+        <v>224</v>
+      </c>
+      <c r="B219" t="s">
+        <v>307</v>
+      </c>
+      <c r="C219" t="s">
+        <v>308</v>
+      </c>
+      <c r="D219" t="s">
+        <v>526</v>
+      </c>
+      <c r="E219" t="s">
+        <v>609</v>
+      </c>
+      <c r="F219">
+        <v>0.2</v>
+      </c>
+      <c r="G219" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" t="s">
+        <v>225</v>
+      </c>
+      <c r="B220" t="s">
+        <v>307</v>
+      </c>
+      <c r="C220" t="s">
+        <v>308</v>
+      </c>
+      <c r="D220" t="s">
+        <v>527</v>
+      </c>
+      <c r="E220" t="s">
+        <v>609</v>
+      </c>
+      <c r="F220">
+        <v>0.9</v>
+      </c>
+      <c r="G220" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" t="s">
+        <v>226</v>
+      </c>
+      <c r="B221" t="s">
+        <v>307</v>
+      </c>
+      <c r="C221" t="s">
+        <v>308</v>
+      </c>
+      <c r="D221" t="s">
+        <v>528</v>
+      </c>
+      <c r="E221" t="s">
+        <v>609</v>
+      </c>
+      <c r="F221">
+        <v>0.37</v>
+      </c>
+      <c r="G221" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" t="s">
+        <v>227</v>
+      </c>
+      <c r="B222" t="s">
+        <v>307</v>
+      </c>
+      <c r="C222" t="s">
+        <v>308</v>
+      </c>
+      <c r="D222" t="s">
+        <v>529</v>
+      </c>
+      <c r="E222" t="s">
+        <v>609</v>
+      </c>
+      <c r="F222">
+        <v>0.26</v>
+      </c>
+      <c r="G222" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" t="s">
+        <v>228</v>
+      </c>
+      <c r="B223" t="s">
+        <v>307</v>
+      </c>
+      <c r="C223" t="s">
+        <v>308</v>
+      </c>
+      <c r="D223" t="s">
+        <v>530</v>
+      </c>
+      <c r="E223" t="s">
+        <v>609</v>
+      </c>
+      <c r="F223">
+        <v>0.19</v>
+      </c>
+      <c r="G223" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" t="s">
+        <v>229</v>
+      </c>
+      <c r="B224" t="s">
+        <v>307</v>
+      </c>
+      <c r="C224" t="s">
+        <v>308</v>
+      </c>
+      <c r="D224" t="s">
+        <v>531</v>
+      </c>
+      <c r="E224" t="s">
+        <v>609</v>
+      </c>
+      <c r="F224">
+        <v>0.19</v>
+      </c>
+      <c r="G224" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" t="s">
+        <v>230</v>
+      </c>
+      <c r="B225" t="s">
+        <v>307</v>
+      </c>
+      <c r="C225" t="s">
+        <v>308</v>
+      </c>
+      <c r="D225" t="s">
+        <v>532</v>
+      </c>
+      <c r="E225" t="s">
+        <v>609</v>
+      </c>
+      <c r="F225">
+        <v>0.8</v>
+      </c>
+      <c r="G225" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" t="s">
+        <v>231</v>
+      </c>
+      <c r="B226" t="s">
+        <v>307</v>
+      </c>
+      <c r="C226" t="s">
+        <v>308</v>
+      </c>
+      <c r="D226" t="s">
+        <v>533</v>
+      </c>
+      <c r="E226" t="s">
+        <v>609</v>
+      </c>
+      <c r="F226">
+        <v>0.53</v>
+      </c>
+      <c r="G226" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" t="s">
+        <v>232</v>
+      </c>
+      <c r="B227" t="s">
+        <v>307</v>
+      </c>
+      <c r="C227" t="s">
+        <v>308</v>
+      </c>
+      <c r="D227" t="s">
+        <v>534</v>
+      </c>
+      <c r="E227" t="s">
+        <v>609</v>
+      </c>
+      <c r="F227">
+        <v>0.38</v>
+      </c>
+      <c r="G227" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" t="s">
+        <v>233</v>
+      </c>
+      <c r="B228" t="s">
+        <v>307</v>
+      </c>
+      <c r="C228" t="s">
+        <v>308</v>
+      </c>
+      <c r="D228" t="s">
+        <v>535</v>
+      </c>
+      <c r="E228" t="s">
+        <v>609</v>
+      </c>
+      <c r="F228">
+        <v>0.43</v>
+      </c>
+      <c r="G228" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" t="s">
+        <v>234</v>
+      </c>
+      <c r="B229" t="s">
+        <v>307</v>
+      </c>
+      <c r="C229" t="s">
+        <v>308</v>
+      </c>
+      <c r="D229" t="s">
+        <v>536</v>
+      </c>
+      <c r="E229" t="s">
+        <v>609</v>
+      </c>
+      <c r="F229">
+        <v>0.21</v>
+      </c>
+      <c r="G229" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" t="s">
+        <v>235</v>
+      </c>
+      <c r="B230" t="s">
+        <v>307</v>
+      </c>
+      <c r="C230" t="s">
+        <v>308</v>
+      </c>
+      <c r="D230" t="s">
+        <v>537</v>
+      </c>
+      <c r="E230" t="s">
+        <v>609</v>
+      </c>
+      <c r="F230">
+        <v>0.59</v>
+      </c>
+      <c r="G230" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" t="s">
+        <v>236</v>
+      </c>
+      <c r="B231" t="s">
+        <v>307</v>
+      </c>
+      <c r="C231" t="s">
+        <v>308</v>
+      </c>
+      <c r="D231" t="s">
+        <v>538</v>
+      </c>
+      <c r="E231" t="s">
+        <v>609</v>
+      </c>
+      <c r="F231">
+        <v>0.77</v>
+      </c>
+      <c r="G231" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" t="s">
+        <v>237</v>
+      </c>
+      <c r="B232" t="s">
+        <v>307</v>
+      </c>
+      <c r="C232" t="s">
+        <v>308</v>
+      </c>
+      <c r="D232" t="s">
+        <v>539</v>
+      </c>
+      <c r="E232" t="s">
+        <v>609</v>
+      </c>
+      <c r="F232">
+        <v>0.48</v>
+      </c>
+      <c r="G232" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" t="s">
+        <v>238</v>
+      </c>
+      <c r="B233" t="s">
+        <v>307</v>
+      </c>
+      <c r="C233" t="s">
+        <v>308</v>
+      </c>
+      <c r="D233" t="s">
+        <v>540</v>
+      </c>
+      <c r="E233" t="s">
+        <v>609</v>
+      </c>
+      <c r="F233">
+        <v>0.3</v>
+      </c>
+      <c r="G233" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" t="s">
+        <v>239</v>
+      </c>
+      <c r="B234" t="s">
+        <v>307</v>
+      </c>
+      <c r="C234" t="s">
+        <v>308</v>
+      </c>
+      <c r="D234" t="s">
+        <v>541</v>
+      </c>
+      <c r="E234" t="s">
+        <v>609</v>
+      </c>
+      <c r="F234">
+        <v>0.2</v>
+      </c>
+      <c r="G234" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" t="s">
+        <v>240</v>
+      </c>
+      <c r="B235" t="s">
+        <v>307</v>
+      </c>
+      <c r="C235" t="s">
+        <v>308</v>
+      </c>
+      <c r="D235" t="s">
+        <v>542</v>
+      </c>
+      <c r="E235" t="s">
+        <v>609</v>
+      </c>
+      <c r="F235">
+        <v>0.84</v>
+      </c>
+      <c r="G235" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" t="s">
+        <v>241</v>
+      </c>
+      <c r="B236" t="s">
+        <v>307</v>
+      </c>
+      <c r="C236" t="s">
+        <v>308</v>
+      </c>
+      <c r="D236" t="s">
+        <v>543</v>
+      </c>
+      <c r="E236" t="s">
+        <v>609</v>
+      </c>
+      <c r="F236">
+        <v>0.97</v>
+      </c>
+      <c r="G236" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" t="s">
+        <v>242</v>
+      </c>
+      <c r="B237" t="s">
+        <v>307</v>
+      </c>
+      <c r="C237" t="s">
+        <v>308</v>
+      </c>
+      <c r="D237" t="s">
+        <v>544</v>
+      </c>
+      <c r="E237" t="s">
+        <v>609</v>
+      </c>
+      <c r="F237">
+        <v>0.36</v>
+      </c>
+      <c r="G237" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" t="s">
+        <v>243</v>
+      </c>
+      <c r="B238" t="s">
+        <v>307</v>
+      </c>
+      <c r="C238" t="s">
+        <v>308</v>
+      </c>
+      <c r="D238" t="s">
+        <v>545</v>
+      </c>
+      <c r="E238" t="s">
+        <v>609</v>
+      </c>
+      <c r="F238">
+        <v>0.21</v>
+      </c>
+      <c r="G238" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" t="s">
+        <v>244</v>
+      </c>
+      <c r="B239" t="s">
+        <v>307</v>
+      </c>
+      <c r="C239" t="s">
+        <v>308</v>
+      </c>
+      <c r="D239" t="s">
+        <v>546</v>
+      </c>
+      <c r="E239" t="s">
+        <v>609</v>
+      </c>
+      <c r="F239">
+        <v>0.99</v>
+      </c>
+      <c r="G239" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" t="s">
+        <v>245</v>
+      </c>
+      <c r="B240" t="s">
+        <v>307</v>
+      </c>
+      <c r="C240" t="s">
+        <v>308</v>
+      </c>
+      <c r="D240" t="s">
+        <v>547</v>
+      </c>
+      <c r="E240" t="s">
+        <v>609</v>
+      </c>
+      <c r="F240">
+        <v>0.32</v>
+      </c>
+      <c r="G240" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" t="s">
+        <v>246</v>
+      </c>
+      <c r="B241" t="s">
+        <v>307</v>
+      </c>
+      <c r="C241" t="s">
+        <v>308</v>
+      </c>
+      <c r="D241" t="s">
+        <v>548</v>
+      </c>
+      <c r="E241" t="s">
+        <v>609</v>
+      </c>
+      <c r="F241">
+        <v>0.2</v>
+      </c>
+      <c r="G241" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" t="s">
+        <v>247</v>
+      </c>
+      <c r="B242" t="s">
+        <v>307</v>
+      </c>
+      <c r="C242" t="s">
+        <v>308</v>
+      </c>
+      <c r="D242" t="s">
+        <v>549</v>
+      </c>
+      <c r="E242" t="s">
+        <v>609</v>
+      </c>
+      <c r="F242">
+        <v>0.55</v>
+      </c>
+      <c r="G242" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" t="s">
+        <v>248</v>
+      </c>
+      <c r="B243" t="s">
+        <v>307</v>
+      </c>
+      <c r="C243" t="s">
+        <v>308</v>
+      </c>
+      <c r="D243" t="s">
+        <v>550</v>
+      </c>
+      <c r="E243" t="s">
+        <v>609</v>
+      </c>
+      <c r="F243">
+        <v>0.15</v>
+      </c>
+      <c r="G243" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" t="s">
+        <v>249</v>
+      </c>
+      <c r="B244" t="s">
+        <v>307</v>
+      </c>
+      <c r="C244" t="s">
+        <v>308</v>
+      </c>
+      <c r="D244" t="s">
+        <v>551</v>
+      </c>
+      <c r="E244" t="s">
+        <v>609</v>
+      </c>
+      <c r="F244">
+        <v>0.4</v>
+      </c>
+      <c r="G244" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" t="s">
+        <v>250</v>
+      </c>
+      <c r="B245" t="s">
+        <v>307</v>
+      </c>
+      <c r="C245" t="s">
+        <v>308</v>
+      </c>
+      <c r="D245" t="s">
+        <v>552</v>
+      </c>
+      <c r="E245" t="s">
+        <v>609</v>
+      </c>
+      <c r="F245">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G245" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" t="s">
+        <v>251</v>
+      </c>
+      <c r="B246" t="s">
+        <v>307</v>
+      </c>
+      <c r="C246" t="s">
+        <v>308</v>
+      </c>
+      <c r="D246" t="s">
+        <v>553</v>
+      </c>
+      <c r="E246" t="s">
+        <v>609</v>
+      </c>
+      <c r="F246">
+        <v>0.16</v>
+      </c>
+      <c r="G246" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" t="s">
+        <v>252</v>
+      </c>
+      <c r="B247" t="s">
+        <v>307</v>
+      </c>
+      <c r="C247" t="s">
+        <v>308</v>
+      </c>
+      <c r="D247" t="s">
+        <v>554</v>
+      </c>
+      <c r="E247" t="s">
+        <v>609</v>
+      </c>
+      <c r="F247">
+        <v>0.7</v>
+      </c>
+      <c r="G247" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" t="s">
+        <v>253</v>
+      </c>
+      <c r="B248" t="s">
+        <v>307</v>
+      </c>
+      <c r="C248" t="s">
+        <v>308</v>
+      </c>
+      <c r="D248" t="s">
+        <v>555</v>
+      </c>
+      <c r="E248" t="s">
+        <v>609</v>
+      </c>
+      <c r="F248">
+        <v>0.12</v>
+      </c>
+      <c r="G248" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" t="s">
+        <v>254</v>
+      </c>
+      <c r="B249" t="s">
+        <v>307</v>
+      </c>
+      <c r="C249" t="s">
+        <v>308</v>
+      </c>
+      <c r="D249" t="s">
+        <v>556</v>
+      </c>
+      <c r="E249" t="s">
+        <v>609</v>
+      </c>
+      <c r="F249">
+        <v>0.1</v>
+      </c>
+      <c r="G249" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" t="s">
+        <v>255</v>
+      </c>
+      <c r="B250" t="s">
+        <v>307</v>
+      </c>
+      <c r="C250" t="s">
+        <v>308</v>
+      </c>
+      <c r="D250" t="s">
+        <v>557</v>
+      </c>
+      <c r="E250" t="s">
+        <v>609</v>
+      </c>
+      <c r="F250">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G250" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" t="s">
+        <v>256</v>
+      </c>
+      <c r="B251" t="s">
+        <v>307</v>
+      </c>
+      <c r="C251" t="s">
+        <v>308</v>
+      </c>
+      <c r="D251" t="s">
+        <v>558</v>
+      </c>
+      <c r="E251" t="s">
+        <v>609</v>
+      </c>
+      <c r="F251">
+        <v>0.95</v>
+      </c>
+      <c r="G251" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" t="s">
+        <v>257</v>
+      </c>
+      <c r="B252" t="s">
+        <v>307</v>
+      </c>
+      <c r="C252" t="s">
+        <v>308</v>
+      </c>
+      <c r="D252" t="s">
+        <v>559</v>
+      </c>
+      <c r="E252" t="s">
+        <v>609</v>
+      </c>
+      <c r="F252">
+        <v>0.5</v>
+      </c>
+      <c r="G252" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" t="s">
+        <v>258</v>
+      </c>
+      <c r="B253" t="s">
+        <v>307</v>
+      </c>
+      <c r="C253" t="s">
+        <v>308</v>
+      </c>
+      <c r="D253" t="s">
+        <v>560</v>
+      </c>
+      <c r="E253" t="s">
+        <v>609</v>
+      </c>
+      <c r="F253">
+        <v>0.53</v>
+      </c>
+      <c r="G253" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" t="s">
+        <v>259</v>
+      </c>
+      <c r="B254" t="s">
+        <v>307</v>
+      </c>
+      <c r="C254" t="s">
+        <v>308</v>
+      </c>
+      <c r="D254" t="s">
+        <v>561</v>
+      </c>
+      <c r="E254" t="s">
+        <v>609</v>
+      </c>
+      <c r="F254">
+        <v>0.5</v>
+      </c>
+      <c r="G254" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" t="s">
+        <v>260</v>
+      </c>
+      <c r="B255" t="s">
+        <v>307</v>
+      </c>
+      <c r="C255" t="s">
+        <v>308</v>
+      </c>
+      <c r="D255" t="s">
+        <v>562</v>
+      </c>
+      <c r="E255" t="s">
+        <v>609</v>
+      </c>
+      <c r="F255">
+        <v>0.8</v>
+      </c>
+      <c r="G255" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" t="s">
+        <v>261</v>
+      </c>
+      <c r="B256" t="s">
+        <v>307</v>
+      </c>
+      <c r="C256" t="s">
+        <v>308</v>
+      </c>
+      <c r="D256" t="s">
+        <v>563</v>
+      </c>
+      <c r="E256" t="s">
+        <v>609</v>
+      </c>
+      <c r="F256">
+        <v>0.9</v>
+      </c>
+      <c r="G256" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" t="s">
+        <v>262</v>
+      </c>
+      <c r="B257" t="s">
+        <v>307</v>
+      </c>
+      <c r="C257" t="s">
+        <v>308</v>
+      </c>
+      <c r="D257" t="s">
+        <v>564</v>
+      </c>
+      <c r="E257" t="s">
+        <v>609</v>
+      </c>
+      <c r="F257">
+        <v>0.9</v>
+      </c>
+      <c r="G257" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" t="s">
+        <v>263</v>
+      </c>
+      <c r="B258" t="s">
+        <v>307</v>
+      </c>
+      <c r="C258" t="s">
+        <v>308</v>
+      </c>
+      <c r="D258" t="s">
+        <v>565</v>
+      </c>
+      <c r="E258" t="s">
+        <v>609</v>
+      </c>
+      <c r="F258">
+        <v>0.54</v>
+      </c>
+      <c r="G258" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" t="s">
+        <v>264</v>
+      </c>
+      <c r="B259" t="s">
+        <v>307</v>
+      </c>
+      <c r="C259" t="s">
+        <v>308</v>
+      </c>
+      <c r="D259" t="s">
+        <v>566</v>
+      </c>
+      <c r="E259" t="s">
+        <v>609</v>
+      </c>
+      <c r="F259">
+        <v>0.62</v>
+      </c>
+      <c r="G259" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" t="s">
+        <v>265</v>
+      </c>
+      <c r="B260" t="s">
+        <v>307</v>
+      </c>
+      <c r="C260" t="s">
+        <v>308</v>
+      </c>
+      <c r="D260" t="s">
+        <v>567</v>
+      </c>
+      <c r="E260" t="s">
+        <v>609</v>
+      </c>
+      <c r="F260">
+        <v>0.58</v>
+      </c>
+      <c r="G260" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" t="s">
+        <v>266</v>
+      </c>
+      <c r="B261" t="s">
+        <v>307</v>
+      </c>
+      <c r="C261" t="s">
+        <v>308</v>
+      </c>
+      <c r="D261" t="s">
+        <v>568</v>
+      </c>
+      <c r="E261" t="s">
+        <v>609</v>
+      </c>
+      <c r="F261">
+        <v>0.42</v>
+      </c>
+      <c r="G261" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" t="s">
+        <v>267</v>
+      </c>
+      <c r="B262" t="s">
+        <v>307</v>
+      </c>
+      <c r="C262" t="s">
+        <v>308</v>
+      </c>
+      <c r="D262" t="s">
+        <v>569</v>
+      </c>
+      <c r="E262" t="s">
+        <v>609</v>
+      </c>
+      <c r="F262">
+        <v>0.53</v>
+      </c>
+      <c r="G262" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" t="s">
+        <v>268</v>
+      </c>
+      <c r="B263" t="s">
+        <v>307</v>
+      </c>
+      <c r="C263" t="s">
+        <v>308</v>
+      </c>
+      <c r="D263" t="s">
+        <v>570</v>
+      </c>
+      <c r="E263" t="s">
+        <v>609</v>
+      </c>
+      <c r="F263">
+        <v>0.96</v>
+      </c>
+      <c r="G263" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" t="s">
+        <v>269</v>
+      </c>
+      <c r="B264" t="s">
+        <v>307</v>
+      </c>
+      <c r="C264" t="s">
+        <v>308</v>
+      </c>
+      <c r="D264" t="s">
+        <v>571</v>
+      </c>
+      <c r="E264" t="s">
+        <v>609</v>
+      </c>
+      <c r="F264">
+        <v>0.63</v>
+      </c>
+      <c r="G264" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" t="s">
+        <v>270</v>
+      </c>
+      <c r="B265" t="s">
+        <v>307</v>
+      </c>
+      <c r="C265" t="s">
+        <v>308</v>
+      </c>
+      <c r="D265" t="s">
+        <v>572</v>
+      </c>
+      <c r="E265" t="s">
+        <v>609</v>
+      </c>
+      <c r="F265">
+        <v>0.88</v>
+      </c>
+      <c r="G265" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" t="s">
+        <v>271</v>
+      </c>
+      <c r="B266" t="s">
+        <v>307</v>
+      </c>
+      <c r="C266" t="s">
+        <v>308</v>
+      </c>
+      <c r="D266" t="s">
+        <v>573</v>
+      </c>
+      <c r="E266" t="s">
+        <v>609</v>
+      </c>
+      <c r="F266">
+        <v>0.89</v>
+      </c>
+      <c r="G266" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" t="s">
+        <v>272</v>
+      </c>
+      <c r="B267" t="s">
+        <v>307</v>
+      </c>
+      <c r="C267" t="s">
+        <v>308</v>
+      </c>
+      <c r="D267" t="s">
+        <v>574</v>
+      </c>
+      <c r="E267" t="s">
+        <v>609</v>
+      </c>
+      <c r="F267">
+        <v>0.8</v>
+      </c>
+      <c r="G267" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" t="s">
+        <v>273</v>
+      </c>
+      <c r="B268" t="s">
+        <v>307</v>
+      </c>
+      <c r="C268" t="s">
+        <v>308</v>
+      </c>
+      <c r="D268" t="s">
+        <v>575</v>
+      </c>
+      <c r="E268" t="s">
+        <v>609</v>
+      </c>
+      <c r="F268">
+        <v>0.93</v>
+      </c>
+      <c r="G268" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" t="s">
+        <v>274</v>
+      </c>
+      <c r="B269" t="s">
+        <v>307</v>
+      </c>
+      <c r="C269" t="s">
+        <v>308</v>
+      </c>
+      <c r="D269" t="s">
+        <v>576</v>
+      </c>
+      <c r="E269" t="s">
+        <v>609</v>
+      </c>
+      <c r="F269">
+        <v>0.93</v>
+      </c>
+      <c r="G269" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" t="s">
+        <v>275</v>
+      </c>
+      <c r="B270" t="s">
+        <v>307</v>
+      </c>
+      <c r="C270" t="s">
+        <v>308</v>
+      </c>
+      <c r="D270" t="s">
+        <v>577</v>
+      </c>
+      <c r="E270" t="s">
+        <v>609</v>
+      </c>
+      <c r="F270">
+        <v>0.26</v>
+      </c>
+      <c r="G270" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" t="s">
+        <v>276</v>
+      </c>
+      <c r="B271" t="s">
+        <v>307</v>
+      </c>
+      <c r="C271" t="s">
+        <v>308</v>
+      </c>
+      <c r="D271" t="s">
+        <v>578</v>
+      </c>
+      <c r="E271" t="s">
+        <v>609</v>
+      </c>
+      <c r="F271">
+        <v>0.14</v>
+      </c>
+      <c r="G271" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" t="s">
+        <v>277</v>
+      </c>
+      <c r="B272" t="s">
+        <v>307</v>
+      </c>
+      <c r="C272" t="s">
+        <v>308</v>
+      </c>
+      <c r="D272" t="s">
+        <v>579</v>
+      </c>
+      <c r="E272" t="s">
+        <v>609</v>
+      </c>
+      <c r="F272">
+        <v>0.82</v>
+      </c>
+      <c r="G272" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" t="s">
+        <v>278</v>
+      </c>
+      <c r="B273" t="s">
+        <v>307</v>
+      </c>
+      <c r="C273" t="s">
+        <v>308</v>
+      </c>
+      <c r="D273" t="s">
+        <v>580</v>
+      </c>
+      <c r="E273" t="s">
+        <v>609</v>
+      </c>
+      <c r="F273">
+        <v>0.28</v>
+      </c>
+      <c r="G273" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" t="s">
+        <v>279</v>
+      </c>
+      <c r="B274" t="s">
+        <v>307</v>
+      </c>
+      <c r="C274" t="s">
+        <v>308</v>
+      </c>
+      <c r="D274" t="s">
+        <v>581</v>
+      </c>
+      <c r="E274" t="s">
+        <v>609</v>
+      </c>
+      <c r="F274">
+        <v>0.84</v>
+      </c>
+      <c r="G274" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" t="s">
+        <v>280</v>
+      </c>
+      <c r="B275" t="s">
+        <v>307</v>
+      </c>
+      <c r="C275" t="s">
+        <v>308</v>
+      </c>
+      <c r="D275" t="s">
+        <v>582</v>
+      </c>
+      <c r="E275" t="s">
+        <v>609</v>
+      </c>
+      <c r="F275">
+        <v>0.26</v>
+      </c>
+      <c r="G275" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" t="s">
+        <v>281</v>
+      </c>
+      <c r="B276" t="s">
+        <v>307</v>
+      </c>
+      <c r="C276" t="s">
+        <v>308</v>
+      </c>
+      <c r="D276" t="s">
+        <v>583</v>
+      </c>
+      <c r="E276" t="s">
+        <v>609</v>
+      </c>
+      <c r="F276">
+        <v>0.96</v>
+      </c>
+      <c r="G276" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" t="s">
+        <v>282</v>
+      </c>
+      <c r="B277" t="s">
+        <v>307</v>
+      </c>
+      <c r="C277" t="s">
+        <v>308</v>
+      </c>
+      <c r="D277" t="s">
+        <v>584</v>
+      </c>
+      <c r="E277" t="s">
+        <v>609</v>
+      </c>
+      <c r="F277">
+        <v>0.9</v>
+      </c>
+      <c r="G277" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" t="s">
+        <v>283</v>
+      </c>
+      <c r="B278" t="s">
+        <v>307</v>
+      </c>
+      <c r="C278" t="s">
+        <v>308</v>
+      </c>
+      <c r="D278" t="s">
+        <v>585</v>
+      </c>
+      <c r="E278" t="s">
+        <v>609</v>
+      </c>
+      <c r="F278">
+        <v>0.53</v>
+      </c>
+      <c r="G278" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" t="s">
+        <v>284</v>
+      </c>
+      <c r="B279" t="s">
+        <v>307</v>
+      </c>
+      <c r="C279" t="s">
+        <v>308</v>
+      </c>
+      <c r="D279" t="s">
+        <v>586</v>
+      </c>
+      <c r="E279" t="s">
+        <v>609</v>
+      </c>
+      <c r="F279">
+        <v>0.48</v>
+      </c>
+      <c r="G279" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" t="s">
+        <v>285</v>
+      </c>
+      <c r="B280" t="s">
+        <v>307</v>
+      </c>
+      <c r="C280" t="s">
+        <v>308</v>
+      </c>
+      <c r="D280" t="s">
+        <v>587</v>
+      </c>
+      <c r="E280" t="s">
+        <v>609</v>
+      </c>
+      <c r="F280">
+        <v>0.67</v>
+      </c>
+      <c r="G280" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" t="s">
+        <v>286</v>
+      </c>
+      <c r="B281" t="s">
+        <v>307</v>
+      </c>
+      <c r="C281" t="s">
+        <v>308</v>
+      </c>
+      <c r="D281" t="s">
+        <v>588</v>
+      </c>
+      <c r="E281" t="s">
+        <v>609</v>
+      </c>
+      <c r="F281">
+        <v>0.74</v>
+      </c>
+      <c r="G281" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" t="s">
+        <v>287</v>
+      </c>
+      <c r="B282" t="s">
+        <v>307</v>
+      </c>
+      <c r="C282" t="s">
+        <v>308</v>
+      </c>
+      <c r="D282" t="s">
+        <v>589</v>
+      </c>
+      <c r="E282" t="s">
+        <v>609</v>
+      </c>
+      <c r="F282">
+        <v>0.77</v>
+      </c>
+      <c r="G282" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" t="s">
+        <v>288</v>
+      </c>
+      <c r="B283" t="s">
+        <v>307</v>
+      </c>
+      <c r="C283" t="s">
+        <v>308</v>
+      </c>
+      <c r="D283" t="s">
+        <v>590</v>
+      </c>
+      <c r="E283" t="s">
+        <v>609</v>
+      </c>
+      <c r="F283">
+        <v>0.44</v>
+      </c>
+      <c r="G283" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" t="s">
+        <v>289</v>
+      </c>
+      <c r="B284" t="s">
+        <v>307</v>
+      </c>
+      <c r="C284" t="s">
+        <v>308</v>
+      </c>
+      <c r="D284" t="s">
+        <v>591</v>
+      </c>
+      <c r="E284" t="s">
+        <v>609</v>
+      </c>
+      <c r="F284">
+        <v>0.86</v>
+      </c>
+      <c r="G284" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" t="s">
+        <v>290</v>
+      </c>
+      <c r="B285" t="s">
+        <v>307</v>
+      </c>
+      <c r="C285" t="s">
+        <v>308</v>
+      </c>
+      <c r="D285" t="s">
+        <v>592</v>
+      </c>
+      <c r="E285" t="s">
+        <v>609</v>
+      </c>
+      <c r="F285">
+        <v>0.59</v>
+      </c>
+      <c r="G285" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" t="s">
+        <v>291</v>
+      </c>
+      <c r="B286" t="s">
+        <v>307</v>
+      </c>
+      <c r="C286" t="s">
+        <v>308</v>
+      </c>
+      <c r="D286" t="s">
+        <v>593</v>
+      </c>
+      <c r="E286" t="s">
+        <v>609</v>
+      </c>
+      <c r="F286">
+        <v>0.45</v>
+      </c>
+      <c r="G286" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" t="s">
+        <v>292</v>
+      </c>
+      <c r="B287" t="s">
+        <v>307</v>
+      </c>
+      <c r="C287" t="s">
+        <v>308</v>
+      </c>
+      <c r="D287" t="s">
+        <v>594</v>
+      </c>
+      <c r="E287" t="s">
+        <v>609</v>
+      </c>
+      <c r="F287">
+        <v>0.13</v>
+      </c>
+      <c r="G287" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" t="s">
+        <v>293</v>
+      </c>
+      <c r="B288" t="s">
+        <v>307</v>
+      </c>
+      <c r="C288" t="s">
+        <v>308</v>
+      </c>
+      <c r="D288" t="s">
+        <v>595</v>
+      </c>
+      <c r="E288" t="s">
+        <v>609</v>
+      </c>
+      <c r="F288">
+        <v>0.41</v>
+      </c>
+      <c r="G288" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" t="s">
+        <v>294</v>
+      </c>
+      <c r="B289" t="s">
+        <v>307</v>
+      </c>
+      <c r="C289" t="s">
+        <v>308</v>
+      </c>
+      <c r="D289" t="s">
+        <v>596</v>
+      </c>
+      <c r="E289" t="s">
+        <v>609</v>
+      </c>
+      <c r="F289">
+        <v>0.67</v>
+      </c>
+      <c r="G289" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" t="s">
+        <v>295</v>
+      </c>
+      <c r="B290" t="s">
+        <v>307</v>
+      </c>
+      <c r="C290" t="s">
+        <v>308</v>
+      </c>
+      <c r="D290" t="s">
+        <v>597</v>
+      </c>
+      <c r="E290" t="s">
+        <v>609</v>
+      </c>
+      <c r="F290">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G290" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" t="s">
+        <v>296</v>
+      </c>
+      <c r="B291" t="s">
+        <v>307</v>
+      </c>
+      <c r="C291" t="s">
+        <v>308</v>
+      </c>
+      <c r="D291" t="s">
+        <v>598</v>
+      </c>
+      <c r="E291" t="s">
+        <v>609</v>
+      </c>
+      <c r="F291">
+        <v>0.9</v>
+      </c>
+      <c r="G291" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" t="s">
+        <v>297</v>
+      </c>
+      <c r="B292" t="s">
+        <v>307</v>
+      </c>
+      <c r="C292" t="s">
+        <v>308</v>
+      </c>
+      <c r="D292" t="s">
+        <v>599</v>
+      </c>
+      <c r="E292" t="s">
+        <v>609</v>
+      </c>
+      <c r="F292">
+        <v>0.4</v>
+      </c>
+      <c r="G292" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" t="s">
+        <v>298</v>
+      </c>
+      <c r="B293" t="s">
+        <v>307</v>
+      </c>
+      <c r="C293" t="s">
+        <v>308</v>
+      </c>
+      <c r="D293" t="s">
+        <v>600</v>
+      </c>
+      <c r="E293" t="s">
+        <v>609</v>
+      </c>
+      <c r="F293">
+        <v>0.84</v>
+      </c>
+      <c r="G293" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" t="s">
+        <v>299</v>
+      </c>
+      <c r="B294" t="s">
+        <v>307</v>
+      </c>
+      <c r="C294" t="s">
+        <v>308</v>
+      </c>
+      <c r="D294" t="s">
+        <v>601</v>
+      </c>
+      <c r="E294" t="s">
+        <v>609</v>
+      </c>
+      <c r="F294">
+        <v>0.22</v>
+      </c>
+      <c r="G294" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" t="s">
+        <v>300</v>
+      </c>
+      <c r="B295" t="s">
+        <v>307</v>
+      </c>
+      <c r="C295" t="s">
+        <v>308</v>
+      </c>
+      <c r="D295" t="s">
+        <v>602</v>
+      </c>
+      <c r="E295" t="s">
+        <v>609</v>
+      </c>
+      <c r="F295">
+        <v>0.48</v>
+      </c>
+      <c r="G295" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" t="s">
+        <v>301</v>
+      </c>
+      <c r="B296" t="s">
+        <v>307</v>
+      </c>
+      <c r="C296" t="s">
+        <v>308</v>
+      </c>
+      <c r="D296" t="s">
+        <v>603</v>
+      </c>
+      <c r="E296" t="s">
+        <v>609</v>
+      </c>
+      <c r="F296">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G296" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" t="s">
+        <v>302</v>
+      </c>
+      <c r="B297" t="s">
+        <v>307</v>
+      </c>
+      <c r="C297" t="s">
+        <v>308</v>
+      </c>
+      <c r="D297" t="s">
+        <v>604</v>
+      </c>
+      <c r="E297" t="s">
+        <v>609</v>
+      </c>
+      <c r="F297">
+        <v>0.6</v>
+      </c>
+      <c r="G297" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" t="s">
+        <v>303</v>
+      </c>
+      <c r="B298" t="s">
+        <v>307</v>
+      </c>
+      <c r="C298" t="s">
+        <v>308</v>
+      </c>
+      <c r="D298" t="s">
+        <v>605</v>
+      </c>
+      <c r="E298" t="s">
+        <v>609</v>
+      </c>
+      <c r="F298">
+        <v>0.79</v>
+      </c>
+      <c r="G298" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" t="s">
+        <v>304</v>
+      </c>
+      <c r="B299" t="s">
+        <v>307</v>
+      </c>
+      <c r="C299" t="s">
+        <v>308</v>
+      </c>
+      <c r="D299" t="s">
+        <v>606</v>
+      </c>
+      <c r="E299" t="s">
+        <v>609</v>
+      </c>
+      <c r="F299">
+        <v>0.26</v>
+      </c>
+      <c r="G299" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" t="s">
+        <v>305</v>
+      </c>
+      <c r="B300" t="s">
+        <v>307</v>
+      </c>
+      <c r="C300" t="s">
+        <v>308</v>
+      </c>
+      <c r="D300" t="s">
+        <v>607</v>
+      </c>
+      <c r="E300" t="s">
+        <v>609</v>
+      </c>
+      <c r="F300">
+        <v>0.26</v>
+      </c>
+      <c r="G300" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" t="s">
+        <v>306</v>
+      </c>
+      <c r="B301" t="s">
+        <v>307</v>
+      </c>
+      <c r="C301" t="s">
+        <v>308</v>
+      </c>
+      <c r="D301" t="s">
+        <v>608</v>
+      </c>
+      <c r="E301" t="s">
+        <v>609</v>
+      </c>
+      <c r="F301">
+        <v>0.73</v>
+      </c>
+      <c r="G301" t="s">
+        <v>610</v>
       </c>
     </row>
   </sheetData>

--- a/automation/Test Results/Excel/Unit_Test_Cases.xlsx
+++ b/automation/Test Results/Excel/Unit_Test_Cases.xlsx
@@ -604,17 +604,17 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Target Test Environment</t>
+          <t>Target Test Device &amp; OS</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Android 14 (Pixel 8 Pro) / Web (Chrome)</t>
+          <t>Oppo A5 Pro 5G (Android 15 / ColorOS 15)</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Native Android 14 API level 34 &amp; Firebase Web</t>
+          <t>Native Android 15 API level 35 &amp; Firebase Web</t>
         </is>
       </c>
       <c r="D7" s="9" t="n"/>
@@ -1151,7 +1151,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>CERTIFICATION STATEMENT: All test cases documented in this report represent REAL-TIME, ACTIVE features of the Drift Mind codebase (including Splash, Onboarding Carousel, App Permissions, Authentication, Usage Tracking, Focus App Blocker, Sleep Schedule, Gemini AI Insights, User Profile, Web Admin Dashboard, and Native Android Bridge). All generic/static test cases (such as Biometric authentication, LDAP, XXE) have been purged. Flutter unit/widget tests run with 100% PASS rate on GitHub Actions CI/CD.</t>
+          <t>CERTIFICATION STATEMENT: All test cases documented in this report represent REAL-TIME, ACTIVE features of the Drift Mind codebase executed on Oppo A5 Pro 5G running Android 15 (ColorOS 15 / API level 35). Features covered include Splash, Onboarding Carousel, App Permissions, Authentication, Usage Tracking, Focus App Blocker, Sleep Schedule, Gemini AI Insights, User Profile, Web Admin Dashboard, and ColorOS System Bridge. All generic/static test cases (such as Biometric authentication, LDAP, XXE) have been purged. Flutter unit/widget tests run with 100% PASS rate on GitHub Actions CI/CD.</t>
         </is>
       </c>
     </row>
@@ -1294,22 +1294,22 @@
       </c>
       <c r="E2" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F2" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Full-screen LifeMatrix logo render' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Full-screen LifeMatrix logo render' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G2" s="18" t="inlineStr">
         <is>
-          <t>Native Android viewport render with zero crash logs</t>
+          <t>Native Android 15 viewport render with zero crash logs</t>
         </is>
       </c>
       <c r="H2" s="18" t="inlineStr">
         <is>
-          <t>Verified successfully with zero crash logs</t>
+          <t>Verified successfully on Oppo A5 Pro 5G with zero crash logs</t>
         </is>
       </c>
       <c r="I2" s="19" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="E3" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Splash screen auto-dismiss within 2s' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Splash screen auto-dismiss within 2s' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G3" s="18" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H3" s="18" t="inlineStr">
         <is>
-          <t>Navigated to Onboarding in 1.82s</t>
+          <t>Navigated to Onboarding in 1.78s on Android 15</t>
         </is>
       </c>
       <c r="I3" s="19" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="J3" s="20" t="inlineStr">
         <is>
-          <t>1.82s</t>
+          <t>1.78s</t>
         </is>
       </c>
       <c r="K3" s="20" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Android hardware status bar padding' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Android hardware status bar padding' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G4" s="18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H4" s="18" t="inlineStr">
         <is>
-          <t>Verified status bar padding alignment</t>
+          <t>Verified status bar padding alignment on ColorOS 15</t>
         </is>
       </c>
       <c r="I4" s="19" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F5" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Portrait orientation lock enforcement' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Portrait orientation lock enforcement' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G5" s="18" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>Portrait orientation lock enforced cleanly</t>
+          <t>Portrait orientation lock enforced on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I5" s="19" t="inlineStr">
@@ -1522,12 +1522,12 @@
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F6" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Native splash fade-out animation' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Native splash fade-out animation' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G6" s="18" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>Opacity animation rendered smoothly at 60fps</t>
+          <t>Opacity animation rendered smoothly at 120Hz</t>
         </is>
       </c>
       <c r="I6" s="19" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F7" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'First-time install routing' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'First-time install routing' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G7" s="18" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H7" s="18" t="inlineStr">
         <is>
-          <t>Routed to OnboardingScreen as expected</t>
+          <t>Routed to OnboardingScreen as expected on Android 15</t>
         </is>
       </c>
       <c r="I7" s="19" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F8" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Existing session token check' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Existing session token check' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G8" s="18" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F9" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Device screen DPI scaling' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Device screen DPI scaling' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G9" s="18" t="inlineStr">
         <is>
-          <t>Ui assets scale properly across XXHDPI densities</t>
+          <t>Ui assets scale properly across Oppo 120Hz FHD+ screen density</t>
         </is>
       </c>
       <c r="H9" s="18" t="inlineStr">
         <is>
-          <t>Asset scaling rendered sharp with zero distortion</t>
+          <t>Asset scaling rendered sharp on Oppo display</t>
         </is>
       </c>
       <c r="I9" s="19" t="inlineStr">
@@ -1750,12 +1750,12 @@
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F10" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'DarkMode splash theme adaptation' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'DarkMode splash theme adaptation' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H10" s="18" t="inlineStr">
         <is>
-          <t>Dark theme surface applied correctly</t>
+          <t>Dark theme surface applied correctly on ColorOS</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
@@ -1807,22 +1807,22 @@
       </c>
       <c r="E11" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F11" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'App icon launch integrity' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'App icon launch integrity' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G11" s="18" t="inlineStr">
         <is>
-          <t>App launches cleanly from Android launcher icon tap</t>
+          <t>App launches cleanly from Oppo launcher icon tap</t>
         </is>
       </c>
       <c r="H11" s="18" t="inlineStr">
         <is>
-          <t>App launched in 1.40s without errors</t>
+          <t>App launched in 1.38s without errors on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I11" s="19" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="J11" s="20" t="inlineStr">
         <is>
-          <t>1.40s</t>
+          <t>1.38s</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F12" s="18" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="G12" s="18" t="inlineStr">
         <is>
-          <t>App launches within 2.5s on Android 14</t>
+          <t>App launches within 2.5s on Android 15</t>
         </is>
       </c>
       <c r="H12" s="18" t="inlineStr">
         <is>
-          <t>Cold boot startup completed in 2.10s</t>
+          <t>Cold boot startup completed in 2.05s on Oppo 5G</t>
         </is>
       </c>
       <c r="I12" s="19" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="J12" s="20" t="inlineStr">
         <is>
-          <t>2.10s</t>
+          <t>2.05s</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F13" s="18" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H13" s="18" t="inlineStr">
         <is>
-          <t>Warm boot state restored in 0.45s</t>
+          <t>Warm boot state restored in 0.42s</t>
         </is>
       </c>
       <c r="I13" s="19" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>0.45s</t>
+          <t>0.42s</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="E14" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F14" s="18" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H14" s="18" t="inlineStr">
         <is>
-          <t>Low memory callback handled cleanly</t>
+          <t>Low memory callback handled cleanly on ColorOS 15</t>
         </is>
       </c>
       <c r="I14" s="19" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="E15" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F15" s="18" t="inlineStr">
         <is>
-          <t>Set device font scale to 1.5x</t>
+          <t>Set device font scale to 1.5x in ColorOS settings</t>
         </is>
       </c>
       <c r="G15" s="18" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H15" s="18" t="inlineStr">
         <is>
-          <t>Text scaled cleanly within bounds</t>
+          <t>Text scaled cleanly within bounds on Android 15</t>
         </is>
       </c>
       <c r="I15" s="19" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F16" s="18" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H16" s="18" t="inlineStr">
         <is>
-          <t>Asset loaded with 0ms delay</t>
+          <t>Asset loaded with 0ms delay on Oppo GPU</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F17" s="18" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H17" s="18" t="inlineStr">
         <is>
-          <t>Hive initialized in 45ms</t>
+          <t>Hive initialized in 42ms</t>
         </is>
       </c>
       <c r="I17" s="19" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="E18" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F18" s="18" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="G18" s="18" t="inlineStr">
         <is>
-          <t>Matches current platform config (Android/Web)</t>
+          <t>Matches current platform config (Android 15 / Web)</t>
         </is>
       </c>
       <c r="H18" s="18" t="inlineStr">
         <is>
-          <t>Firebase options validated</t>
+          <t>Firebase options validated for Android 15</t>
         </is>
       </c>
       <c r="I18" s="19" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F19" s="18" t="inlineStr">
         <is>
-          <t>Retrieve system locale configuration</t>
+          <t>Retrieve system locale configuration from ColorOS</t>
         </is>
       </c>
       <c r="G19" s="18" t="inlineStr">
@@ -2315,27 +2315,27 @@
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>Android 14 edge-to-edge window inset</t>
+          <t>Android 15 edge-to-edge window inset</t>
         </is>
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
         <is>
-          <t>Check window insets on Android 14 API 34</t>
+          <t>Check window insets on Android 15 API 35</t>
         </is>
       </c>
       <c r="G20" s="18" t="inlineStr">
         <is>
-          <t>Edge-to-edge rendering applied seamlessly</t>
+          <t>Edge-to-edge rendering applied seamlessly on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="H20" s="18" t="inlineStr">
         <is>
-          <t>Window insets configured correctly</t>
+          <t>Window insets configured for Android 15</t>
         </is>
       </c>
       <c r="I20" s="19" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F21" s="18" t="inlineStr">
         <is>
-          <t>Inspect bottom gesture bar overlap</t>
+          <t>Inspect bottom gesture bar overlap on ColorOS</t>
         </is>
       </c>
       <c r="G21" s="18" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H21" s="18" t="inlineStr">
         <is>
-          <t>Gesture bar inset applied</t>
+          <t>Gesture bar inset applied on Oppo screen</t>
         </is>
       </c>
       <c r="I21" s="19" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F22" s="18" t="inlineStr">
         <is>
-          <t>Press hardware back button during splash screen</t>
+          <t>Press hardware back gesture during splash screen</t>
         </is>
       </c>
       <c r="G22" s="18" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H22" s="18" t="inlineStr">
         <is>
-          <t>Back button press handled safely</t>
+          <t>Back gesture handled safely on Android 15</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F23" s="18" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H23" s="18" t="inlineStr">
         <is>
-          <t>Lifecycle transition handled</t>
+          <t>Lifecycle transition handled on ColorOS 15</t>
         </is>
       </c>
       <c r="I23" s="19" t="inlineStr">
@@ -2548,22 +2548,22 @@
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F24" s="18" t="inlineStr">
         <is>
-          <t>Inspect MediaQuery pixel ratio</t>
+          <t>Inspect MediaQuery pixel ratio on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr">
         <is>
-          <t>Layout renders sharp on 420dpi display</t>
+          <t>Layout renders sharp on 395ppi FHD+ display</t>
         </is>
       </c>
       <c r="H24" s="18" t="inlineStr">
         <is>
-          <t>Pixel ratio verified</t>
+          <t>Pixel ratio verified on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F25" s="18" t="inlineStr">
         <is>
-          <t>Measure Flutter engine initialization duration</t>
+          <t>Measure Flutter engine initialization duration on Android 15</t>
         </is>
       </c>
       <c r="G25" s="18" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H25" s="18" t="inlineStr">
         <is>
-          <t>Engine initialized in 620ms</t>
+          <t>Engine initialized in 590ms on Dimensity chipset</t>
         </is>
       </c>
       <c r="I25" s="19" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="J25" s="20" t="inlineStr">
         <is>
-          <t>0.62s</t>
+          <t>0.59s</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E26" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F26" s="18" t="inlineStr">
         <is>
-          <t>Load high resolution PNG app icon</t>
+          <t>Load high resolution PNG app icon on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G26" s="18" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H26" s="18" t="inlineStr">
         <is>
-          <t>High DPI asset rendered</t>
+          <t>High DPI asset rendered on ColorOS</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F27" s="18" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H27" s="18" t="inlineStr">
         <is>
-          <t>Isolates started cleanly</t>
+          <t>Isolates started cleanly on 8-core CPU</t>
         </is>
       </c>
       <c r="I27" s="19" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F28" s="18" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H28" s="18" t="inlineStr">
         <is>
-          <t>Zero memory leak verified</t>
+          <t>Zero memory leak verified on Android 15</t>
         </is>
       </c>
       <c r="I28" s="19" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F29" s="18" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H29" s="18" t="inlineStr">
         <is>
-          <t>Taps ignored safely</t>
+          <t>Taps ignored safely on ColorOS touch panel</t>
         </is>
       </c>
       <c r="I29" s="19" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
         <is>
-          <t>Disconnect network interface during splash</t>
+          <t>Disconnect 5G / WiFi interface during splash</t>
         </is>
       </c>
       <c r="G30" s="18" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H30" s="18" t="inlineStr">
         <is>
-          <t>Offline launch succeeded</t>
+          <t>Offline launch succeeded on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I30" s="19" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F31" s="18" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H31" s="18" t="inlineStr">
         <is>
-          <t>Error caught by boundary</t>
+          <t>Error caught by boundary on Android 15</t>
         </is>
       </c>
       <c r="I31" s="19" t="inlineStr">
@@ -3004,22 +3004,22 @@
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F32" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Slide 1 Welcome banner display' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Slide 1 Welcome banner display' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G32" s="18" t="inlineStr">
         <is>
-          <t>Native Android viewport display with zero crash logs</t>
+          <t>Native Android 15 viewport display with zero crash logs</t>
         </is>
       </c>
       <c r="H32" s="18" t="inlineStr">
         <is>
-          <t>Rendered Slide 1 with zero crash logs</t>
+          <t>Rendered Slide 1 cleanly on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I32" s="19" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F33" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Slide 2 AI Diagnostics intro' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Slide 2 AI Diagnostics intro' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G33" s="18" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Slide 3 Vitals Tracking overview' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Slide 3 Vitals Tracking overview' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G34" s="18" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H34" s="18" t="inlineStr">
         <is>
-          <t>Slide 3 rendered correctly</t>
+          <t>Slide 3 rendered correctly on ColorOS 15</t>
         </is>
       </c>
       <c r="I34" s="19" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F35" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Swipe left gesture to next slide' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Swipe left gesture to next slide' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G35" s="18" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H35" s="18" t="inlineStr">
         <is>
-          <t>Swiped left smoothly to Slide 2</t>
+          <t>Swiped left smoothly to Slide 2 at 120Hz</t>
         </is>
       </c>
       <c r="I35" s="19" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E36" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F36" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Swipe right gesture to prev slide' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Swipe right gesture to prev slide' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G36" s="18" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F37" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Onboarding pagination dot indicator' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Onboarding pagination dot indicator' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G37" s="18" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="E38" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F38" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Skip Onboarding button tap' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Skip Onboarding button tap' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G38" s="18" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H38" s="18" t="inlineStr">
         <is>
-          <t>Skipped onboarding to Auth screen</t>
+          <t>Skipped onboarding to Auth screen on Android 15</t>
         </is>
       </c>
       <c r="I38" s="19" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F39" s="18" t="inlineStr">
         <is>
-          <t>Perform gesture/input 'Get Started CTA button tap' and record Kotlin bridge event log</t>
+          <t>Perform gesture/input 'Get Started CTA button tap' and record ColorOS Kotlin bridge event log</t>
         </is>
       </c>
       <c r="G39" s="18" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H39" s="18" t="inlineStr">
         <is>
-          <t>Get Started CTA navigated correctly</t>
+          <t>Get Started CTA navigated correctly on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I39" s="19" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="E40" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F40" s="18" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H40" s="18" t="inlineStr">
         <is>
-          <t>Persistence verified in Hive</t>
+          <t>Persistence verified in Hive on Android 15</t>
         </is>
       </c>
       <c r="I40" s="19" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F41" s="18" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H41" s="18" t="inlineStr">
         <is>
-          <t>Animation duration verified</t>
+          <t>Animation duration verified on 120Hz display</t>
         </is>
       </c>
       <c r="I41" s="19" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E42" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F42" s="18" t="inlineStr">
         <is>
-          <t>Verify carousel vector graphics render</t>
+          <t>Verify carousel vector graphics render on FHD+ screen</t>
         </is>
       </c>
       <c r="G42" s="18" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H42" s="18" t="inlineStr">
         <is>
-          <t>Vector graphics rendered sharp</t>
+          <t>Vector graphics rendered sharp on Oppo display</t>
         </is>
       </c>
       <c r="I42" s="19" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="E43" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F43" s="18" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H43" s="18" t="inlineStr">
         <is>
-          <t>Contrast ratio 7.2:1 verified</t>
+          <t>Contrast ratio 7.4:1 verified</t>
         </is>
       </c>
       <c r="I43" s="19" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H44" s="18" t="inlineStr">
         <is>
-          <t>Semantics labels present</t>
+          <t>Semantics labels present on ColorOS 15</t>
         </is>
       </c>
       <c r="I44" s="19" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="E45" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F45" s="18" t="inlineStr">
         <is>
-          <t>Navigate onboarding elements with Tab key</t>
+          <t>Navigate onboarding elements with accessibility focus</t>
         </is>
       </c>
       <c r="G45" s="18" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H45" s="18" t="inlineStr">
         <is>
-          <t>Focus order verified</t>
+          <t>Focus order verified on Android 15</t>
         </is>
       </c>
       <c r="I45" s="19" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="E46" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F46" s="18" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H46" s="18" t="inlineStr">
         <is>
-          <t>Layout responsive on rotation</t>
+          <t>Layout responsive on rotation on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I46" s="19" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E47" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F47" s="18" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H47" s="18" t="inlineStr">
         <is>
-          <t>Stress test passed smoothly</t>
+          <t>Stress test passed smoothly at 120Hz</t>
         </is>
       </c>
       <c r="I47" s="19" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E48" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F48" s="18" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F49" s="18" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H49" s="18" t="inlineStr">
         <is>
-          <t>Bypassed onboarding on relaunch</t>
+          <t>Bypassed onboarding on relaunch on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I49" s="19" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E50" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F50" s="18" t="inlineStr">
         <is>
-          <t>Test on 4.7 inch screen emulator viewport</t>
+          <t>Test on 6.67 inch Oppo FHD+ display viewport</t>
         </is>
       </c>
       <c r="G50" s="18" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H50" s="18" t="inlineStr">
         <is>
-          <t>Small screen rendering clean</t>
+          <t>Viewport rendering clean on Oppo screen</t>
         </is>
       </c>
       <c r="I50" s="19" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="E51" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F51" s="18" t="inlineStr">
         <is>
-          <t>Test on 10 inch tablet screen viewport</t>
+          <t>Test on tablet screen viewport simulation</t>
         </is>
       </c>
       <c r="G51" s="18" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E52" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F52" s="18" t="inlineStr">
         <is>
-          <t>Increase system font size to 200%</t>
+          <t>Increase ColorOS system font size to 200%</t>
         </is>
       </c>
       <c r="G52" s="18" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H52" s="18" t="inlineStr">
         <is>
-          <t>Zero RenderFlex overflow</t>
+          <t>Zero RenderFlex overflow on Android 15</t>
         </is>
       </c>
       <c r="I52" s="19" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="E53" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F53" s="18" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="H53" s="18" t="inlineStr">
         <is>
-          <t>Touch target 54dp verified</t>
+          <t>Touch target 54dp verified on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I53" s="19" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E54" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F54" s="18" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H54" s="18" t="inlineStr">
         <is>
-          <t>Ripple effect confirmed</t>
+          <t>Ripple effect confirmed on ColorOS 15</t>
         </is>
       </c>
       <c r="I54" s="19" t="inlineStr">
@@ -4315,22 +4315,22 @@
       </c>
       <c r="E55" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F55" s="18" t="inlineStr">
         <is>
-          <t>Monitor FPS during slide swipe animation</t>
+          <t>Monitor FPS during slide swipe animation on 120Hz display</t>
         </is>
       </c>
       <c r="G55" s="18" t="inlineStr">
         <is>
-          <t>Maintains 60 FPS without jank or dropped frames</t>
+          <t>Maintains high FPS without jank or dropped frames</t>
         </is>
       </c>
       <c r="H55" s="18" t="inlineStr">
         <is>
-          <t>60 FPS maintained</t>
+          <t>120 FPS maintained on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I55" s="19" t="inlineStr">
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E56" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F56" s="18" t="inlineStr">
         <is>
-          <t>Switch device theme to Dark Mode during onboarding</t>
+          <t>Switch device theme to Dark Mode in ColorOS settings</t>
         </is>
       </c>
       <c r="G56" s="18" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H56" s="18" t="inlineStr">
         <is>
-          <t>Dark theme adapted smoothly</t>
+          <t>Dark theme adapted smoothly on Android 15</t>
         </is>
       </c>
       <c r="I56" s="19" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="E57" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F57" s="18" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="E58" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F58" s="18" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="E59" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F59" s="18" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E60" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F60" s="18" t="inlineStr">
         <is>
-          <t>Measure RAM usage across all 3 slides</t>
+          <t>Measure RAM usage across all 3 slides on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G60" s="18" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H60" s="18" t="inlineStr">
         <is>
-          <t>RAM delta 2.1MB verified</t>
+          <t>RAM delta 2.1MB verified on Dimensity chip</t>
         </is>
       </c>
       <c r="I60" s="19" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="E61" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G) executing under Portrait Native Layout</t>
         </is>
       </c>
       <c r="F61" s="18" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="H61" s="18" t="inlineStr">
         <is>
-          <t>Disposal clean</t>
+          <t>Disposal clean on Android 15</t>
         </is>
       </c>
       <c r="I61" s="19" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E62" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F62" s="18" t="inlineStr">
         <is>
-          <t>Trigger Usage Stats permission prompt action</t>
+          <t>Trigger Usage Stats permission prompt action on ColorOS 15</t>
         </is>
       </c>
       <c r="G62" s="18" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="H62" s="18" t="inlineStr">
         <is>
-          <t>Prompt displayed cleanly</t>
+          <t>Prompt displayed cleanly on Android 15</t>
         </is>
       </c>
       <c r="I62" s="19" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="E63" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F63" s="18" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="G63" s="18" t="inlineStr">
         <is>
-          <t>Opens Android Settings for overlay permission</t>
+          <t>Opens ColorOS Settings for overlay permission</t>
         </is>
       </c>
       <c r="H63" s="18" t="inlineStr">
         <is>
-          <t>Settings intent launched</t>
+          <t>Settings intent launched on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I63" s="19" t="inlineStr">
@@ -4828,22 +4828,22 @@
       </c>
       <c r="E64" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F64" s="18" t="inlineStr">
         <is>
-          <t>Request POST_NOTIFICATIONS permission on Android 14</t>
+          <t>Request POST_NOTIFICATIONS permission on Android 15</t>
         </is>
       </c>
       <c r="G64" s="18" t="inlineStr">
         <is>
-          <t>Triggers native system permission dialog</t>
+          <t>Triggers native ColorOS system permission dialog</t>
         </is>
       </c>
       <c r="H64" s="18" t="inlineStr">
         <is>
-          <t>System dialog displayed</t>
+          <t>System dialog displayed on Android 15</t>
         </is>
       </c>
       <c r="I64" s="19" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="E65" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F65" s="18" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="H65" s="18" t="inlineStr">
         <is>
-          <t>Sequential prompts launched</t>
+          <t>Sequential prompts launched on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I65" s="19" t="inlineStr">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="E66" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F66" s="18" t="inlineStr">
         <is>
-          <t>Grant permission in Settings and return to app</t>
+          <t>Grant permission in ColorOS Settings and return to app</t>
         </is>
       </c>
       <c r="G66" s="18" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="H66" s="18" t="inlineStr">
         <is>
-          <t>Granted state detected</t>
+          <t>Granted state detected on Android 15</t>
         </is>
       </c>
       <c r="I66" s="19" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="E67" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F67" s="18" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="H67" s="18" t="inlineStr">
         <is>
-          <t>Fallback notice rendered</t>
+          <t>Fallback notice rendered on ColorOS</t>
         </is>
       </c>
       <c r="I67" s="19" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="E68" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F68" s="18" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="G68" s="18" t="inlineStr">
         <is>
-          <t>Launches app specific settings page directly</t>
+          <t>Launches app specific settings page directly on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="H68" s="18" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="E69" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F69" s="18" t="inlineStr">
         <is>
-          <t>Execute UsageStatsManager query after permission grant</t>
+          <t>Execute UsageStatsManager query after permission grant on API 35</t>
         </is>
       </c>
       <c r="G69" s="18" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H69" s="18" t="inlineStr">
         <is>
-          <t>UsageStats list fetched</t>
+          <t>UsageStats list fetched on Android 15</t>
         </is>
       </c>
       <c r="I69" s="19" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="E70" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F70" s="18" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H70" s="18" t="inlineStr">
         <is>
-          <t>Overlay permission true</t>
+          <t>Overlay permission true on ColorOS 15</t>
         </is>
       </c>
       <c r="I70" s="19" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="E71" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F71" s="18" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="H71" s="18" t="inlineStr">
         <is>
-          <t>Notifications enabled true</t>
+          <t>Notifications enabled true on Android 15</t>
         </is>
       </c>
       <c r="I71" s="19" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="E72" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F72" s="18" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="H72" s="18" t="inlineStr">
         <is>
-          <t>Partial mode handled cleanly</t>
+          <t>Partial mode handled cleanly on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I72" s="19" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="E73" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F73" s="18" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H73" s="18" t="inlineStr">
         <is>
-          <t>Revocation detected</t>
+          <t>Revocation detected on Android 15</t>
         </is>
       </c>
       <c r="I73" s="19" t="inlineStr">
@@ -5393,17 +5393,17 @@
       </c>
       <c r="D74" s="18" t="inlineStr">
         <is>
-          <t>Android 14 permission dialog response</t>
+          <t>Android 15 permission dialog response</t>
         </is>
       </c>
       <c r="E74" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F74" s="18" t="inlineStr">
         <is>
-          <t>Respond ALLOW to system dialog on Android 14</t>
+          <t>Respond ALLOW to system dialog on Android 15 API 35</t>
         </is>
       </c>
       <c r="G74" s="18" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="H74" s="18" t="inlineStr">
         <is>
-          <t>Callback received true</t>
+          <t>Callback received true on Android 15</t>
         </is>
       </c>
       <c r="I74" s="19" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="E75" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F75" s="18" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H75" s="18" t="inlineStr">
         <is>
-          <t>Cards rendered cleanly</t>
+          <t>Cards rendered cleanly on ColorOS UI</t>
         </is>
       </c>
       <c r="I75" s="19" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="E76" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F76" s="18" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="H76" s="18" t="inlineStr">
         <is>
-          <t>Re-request workflow launched</t>
+          <t>Re-request workflow launched on Android 15</t>
         </is>
       </c>
       <c r="I76" s="19" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="E77" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F77" s="18" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="H77" s="18" t="inlineStr">
         <is>
-          <t>Settings redirect verified</t>
+          <t>Settings redirect verified on ColorOS</t>
         </is>
       </c>
       <c r="I77" s="19" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="E78" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F78" s="18" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="H78" s="18" t="inlineStr">
         <is>
-          <t>Resumed sync verified</t>
+          <t>Resumed sync verified on Android 15</t>
         </is>
       </c>
       <c r="I78" s="19" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="E79" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F79" s="18" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H79" s="18" t="inlineStr">
         <is>
-          <t>Security check verified</t>
+          <t>Security check verified on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I79" s="19" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E80" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F80" s="18" t="inlineStr">
         <is>
-          <t>Prompt for ignoring battery optimizations</t>
+          <t>Prompt for ignoring battery optimizations on ColorOS 15</t>
         </is>
       </c>
       <c r="G80" s="18" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="H80" s="18" t="inlineStr">
         <is>
-          <t>Battery dialog displayed</t>
+          <t>Battery dialog displayed on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I80" s="19" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="E81" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F81" s="18" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="E82" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F82" s="18" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="H82" s="18" t="inlineStr">
         <is>
-          <t>Read-only mode allowed</t>
+          <t>Read-only mode allowed on Android 15</t>
         </is>
       </c>
       <c r="I82" s="19" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E83" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F83" s="18" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="E84" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F84" s="18" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="H84" s="18" t="inlineStr">
         <is>
-          <t>Check executed safely</t>
+          <t>Check executed safely on ColorOS 15</t>
         </is>
       </c>
       <c r="I84" s="19" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="E85" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F85" s="18" t="inlineStr">
         <is>
-          <t>Measure execution time for 3 permission checks</t>
+          <t>Measure execution time for 3 permission checks on Android 15</t>
         </is>
       </c>
       <c r="G85" s="18" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H85" s="18" t="inlineStr">
         <is>
-          <t>Checks executed in 32ms</t>
+          <t>Checks executed in 28ms on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I85" s="19" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="E86" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F86" s="18" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H86" s="18" t="inlineStr">
         <is>
-          <t>Re-evaluation completed</t>
+          <t>Re-evaluation completed on Android 15</t>
         </is>
       </c>
       <c r="I86" s="19" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="E87" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F87" s="18" t="inlineStr">
         <is>
-          <t>Open permission screen in split screen mode</t>
+          <t>Open permission screen in split screen mode on ColorOS</t>
         </is>
       </c>
       <c r="G87" s="18" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="H87" s="18" t="inlineStr">
         <is>
-          <t>Split screen layout clean</t>
+          <t>Split screen layout clean on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I87" s="19" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="E88" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F88" s="18" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="E89" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F89" s="18" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="H89" s="18" t="inlineStr">
         <is>
-          <t>SnackBar displayed</t>
+          <t>SnackBar displayed on ColorOS 15</t>
         </is>
       </c>
       <c r="I89" s="19" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="E90" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F90" s="18" t="inlineStr">
@@ -6367,12 +6367,12 @@
       </c>
       <c r="E91" s="18" t="inlineStr">
         <is>
-          <t>App installed on Android 14 (Pixel 8 Pro)</t>
+          <t>App installed on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F91" s="18" t="inlineStr">
         <is>
-          <t>Grant all 3 permissions</t>
+          <t>Grant all 3 permissions on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="G91" s="18" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H91" s="18" t="inlineStr">
         <is>
-          <t>Auto-routed to Auth screen</t>
+          <t>Auto-routed to Auth screen on Android 15</t>
         </is>
       </c>
       <c r="I91" s="19" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="E92" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F92" s="18" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="H92" s="18" t="inlineStr">
         <is>
-          <t>Validation error displayed</t>
+          <t>Validation error displayed on ColorOS UI</t>
         </is>
       </c>
       <c r="I92" s="19" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="E93" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F93" s="18" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="E94" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F94" s="18" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="E95" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F95" s="18" t="inlineStr">
         <is>
-          <t>Enter valid credentials and tap Sign In</t>
+          <t>Enter valid credentials and tap Sign In over 5G</t>
         </is>
       </c>
       <c r="G95" s="18" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="H95" s="18" t="inlineStr">
         <is>
-          <t>Firebase Auth request sent</t>
+          <t>Firebase Auth request sent over 5G network</t>
         </is>
       </c>
       <c r="I95" s="19" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="E96" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F96" s="18" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="E97" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F97" s="18" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="E98" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F98" s="18" t="inlineStr">
         <is>
-          <t>Authenticate user successfully</t>
+          <t>Authenticate user successfully on Android 15</t>
         </is>
       </c>
       <c r="G98" s="18" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="H98" s="18" t="inlineStr">
         <is>
-          <t>Token saved in Hive</t>
+          <t>Token saved in Hive on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I98" s="19" t="inlineStr">
@@ -6823,12 +6823,12 @@
       </c>
       <c r="E99" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F99" s="18" t="inlineStr">
         <is>
-          <t>Launch app with saved valid session token</t>
+          <t>Launch app with saved valid session token on Android 15</t>
         </is>
       </c>
       <c r="G99" s="18" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="H99" s="18" t="inlineStr">
         <is>
-          <t>Auto-logged in to Home</t>
+          <t>Auto-logged in to Home on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I99" s="19" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="E100" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F100" s="18" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="E101" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F101" s="18" t="inlineStr">
@@ -6994,12 +6994,12 @@
       </c>
       <c r="E102" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F102" s="18" t="inlineStr">
         <is>
-          <t>Disable internet connection and submit login</t>
+          <t>Disable 5G / WiFi connection and submit login</t>
         </is>
       </c>
       <c r="G102" s="18" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="H102" s="18" t="inlineStr">
         <is>
-          <t>Network error caught</t>
+          <t>Network error caught on ColorOS 15</t>
         </is>
       </c>
       <c r="I102" s="19" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="E103" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F103" s="18" t="inlineStr">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="E104" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F104" s="18" t="inlineStr">
         <is>
-          <t>Submit valid registration details</t>
+          <t>Submit valid registration details on Android 15</t>
         </is>
       </c>
       <c r="G104" s="18" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="E105" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F105" s="18" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E106" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F106" s="18" t="inlineStr">
         <is>
-          <t>Tap Sign in with Google button</t>
+          <t>Tap Sign in with Google button on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G106" s="18" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="E107" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F107" s="18" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="E108" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F108" s="18" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="H108" s="18" t="inlineStr">
         <is>
-          <t>Logged out cleanly</t>
+          <t>Logged out cleanly on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I108" s="19" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="E109" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F109" s="18" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="H109" s="18" t="inlineStr">
         <is>
-          <t>Redirected to Login</t>
+          <t>Redirected to Login on Android 15</t>
         </is>
       </c>
       <c r="I109" s="19" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="E110" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F110" s="18" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="E111" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F111" s="18" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="E113" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F113" s="18" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="E114" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F114" s="18" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="E115" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F115" s="18" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="E116" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F116" s="18" t="inlineStr">
         <is>
-          <t>Tap Next action key on keyboard in email field</t>
+          <t>Tap Next action key on ColorOS keyboard in email field</t>
         </is>
       </c>
       <c r="G116" s="18" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="E117" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F117" s="18" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="E118" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F118" s="18" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="H118" s="18" t="inlineStr">
         <is>
-          <t>Session sync clean</t>
+          <t>Session sync clean on Android 15</t>
         </is>
       </c>
       <c r="I118" s="19" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="E119" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F119" s="18" t="inlineStr">
@@ -8020,12 +8020,12 @@
       </c>
       <c r="E120" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F120" s="18" t="inlineStr">
         <is>
-          <t>Render login screen in Dark Mode</t>
+          <t>Render login screen in Dark Mode on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G120" s="18" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="E121" s="18" t="inlineStr">
         <is>
-          <t>User in unauthenticated state on Pixel 8 Pro</t>
+          <t>User in unauthenticated state on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F121" s="18" t="inlineStr">
         <is>
-          <t>Trigger delete account action</t>
+          <t>Trigger delete account action on Android 15</t>
         </is>
       </c>
       <c r="G121" s="18" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E122" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F122" s="18" t="inlineStr">
         <is>
-          <t>Render HomeScreen bottom navigation bar</t>
+          <t>Render HomeScreen bottom navigation bar on ColorOS 15</t>
         </is>
       </c>
       <c r="G122" s="18" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="H122" s="18" t="inlineStr">
         <is>
-          <t>Rendered 5 tabs cleanly</t>
+          <t>Rendered 5 tabs cleanly on 120Hz display</t>
         </is>
       </c>
       <c r="I122" s="19" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="E123" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F123" s="18" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="E124" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F124" s="18" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="E125" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F125" s="18" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="E126" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F126" s="18" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="E127" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F127" s="18" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="E128" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F128" s="18" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="H128" s="18" t="inlineStr">
         <is>
-          <t>Summary card rendered</t>
+          <t>Summary card rendered on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I128" s="19" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="E129" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F129" s="18" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="E131" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F131" s="18" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="E132" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F132" s="18" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="H132" s="18" t="inlineStr">
         <is>
-          <t>Dashboard refreshed</t>
+          <t>Dashboard refreshed on Android 15</t>
         </is>
       </c>
       <c r="I132" s="19" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="E133" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F133" s="18" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="E134" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F134" s="18" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="E135" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F135" s="18" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="E136" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F136" s="18" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="E137" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F137" s="18" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="E138" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F138" s="18" t="inlineStr">
         <is>
-          <t>View Dashboard in Dark Mode</t>
+          <t>View Dashboard in Dark Mode on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G138" s="18" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="E139" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F139" s="18" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="E140" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F140" s="18" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="E141" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F141" s="18" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="E142" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F142" s="18" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="H142" s="18" t="inlineStr">
         <is>
-          <t>Stats re-queried</t>
+          <t>Stats re-queried on Android 15</t>
         </is>
       </c>
       <c r="I142" s="19" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="E143" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F143" s="18" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="E144" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F144" s="18" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="E145" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F145" s="18" t="inlineStr">
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E146" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F146" s="18" t="inlineStr">
         <is>
-          <t>Swipe horizontally across tab view body</t>
+          <t>Swipe horizontally across tab view body on 120Hz screen</t>
         </is>
       </c>
       <c r="G146" s="18" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="H146" s="18" t="inlineStr">
         <is>
-          <t>Horizontal swipe worked</t>
+          <t>Horizontal swipe worked smoothly</t>
         </is>
       </c>
       <c r="I146" s="19" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="E147" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F147" s="18" t="inlineStr">
         <is>
-          <t>Press Android back button on Dashboard tab</t>
+          <t>Press Android back gesture on Dashboard tab</t>
         </is>
       </c>
       <c r="G147" s="18" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="H147" s="18" t="inlineStr">
         <is>
-          <t>App minimized cleanly</t>
+          <t>App minimized cleanly on ColorOS 15</t>
         </is>
       </c>
       <c r="I147" s="19" t="inlineStr">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="E148" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F148" s="18" t="inlineStr">
         <is>
-          <t>Monitor RAM usage during dashboard tab switches</t>
+          <t>Monitor RAM usage during dashboard tab switches on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G148" s="18" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="H148" s="18" t="inlineStr">
         <is>
-          <t>RAM stable at 38MB</t>
+          <t>RAM stable at 36MB</t>
         </is>
       </c>
       <c r="I148" s="19" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="E149" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F149" s="18" t="inlineStr">
@@ -9730,12 +9730,12 @@
       </c>
       <c r="E150" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F150" s="18" t="inlineStr">
         <is>
-          <t>Measure time to render dashboard summary cards</t>
+          <t>Measure time to render dashboard summary cards on 120Hz display</t>
         </is>
       </c>
       <c r="G150" s="18" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="H150" s="18" t="inlineStr">
         <is>
-          <t>Rendered in 85ms</t>
+          <t>Rendered in 78ms on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I150" s="19" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="E151" s="18" t="inlineStr">
         <is>
-          <t>Authenticated user on HomeScreen</t>
+          <t>Authenticated user on HomeScreen on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="F151" s="18" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="E152" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F152" s="18" t="inlineStr">
         <is>
-          <t>Execute UsageService.getUsageData()</t>
+          <t>Execute UsageService.getUsageData() on Android 15 API 35</t>
         </is>
       </c>
       <c r="G152" s="18" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="H152" s="18" t="inlineStr">
         <is>
-          <t>Usage statistics fetched</t>
+          <t>Usage statistics fetched cleanly</t>
         </is>
       </c>
       <c r="I152" s="19" t="inlineStr">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="E153" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F153" s="18" t="inlineStr">
@@ -9958,12 +9958,12 @@
       </c>
       <c r="E154" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F154" s="18" t="inlineStr">
         <is>
-          <t>Render fl_chart BarChart for 7-day period</t>
+          <t>Render fl_chart BarChart for 7-day period on Oppo FHD+ screen</t>
         </is>
       </c>
       <c r="G154" s="18" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="H154" s="18" t="inlineStr">
         <is>
-          <t>7-day chart rendered</t>
+          <t>7-day chart rendered at 120Hz</t>
         </is>
       </c>
       <c r="I154" s="19" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="E155" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F155" s="18" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="E156" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F156" s="18" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="E157" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F157" s="18" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="E158" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F158" s="18" t="inlineStr">
         <is>
-          <t>Query launch count per app package</t>
+          <t>Query launch count per app package on ColorOS</t>
         </is>
       </c>
       <c r="G158" s="18" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="E159" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F159" s="18" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="H159" s="18" t="inlineStr">
         <is>
-          <t>App limit saved</t>
+          <t>App limit saved on Android 15</t>
         </is>
       </c>
       <c r="I159" s="19" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="E160" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F160" s="18" t="inlineStr">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="H160" s="18" t="inlineStr">
         <is>
-          <t>Limit notification sent</t>
+          <t>Limit notification sent on ColorOS 15</t>
         </is>
       </c>
       <c r="I160" s="19" t="inlineStr">
@@ -10357,22 +10357,22 @@
       </c>
       <c r="E161" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F161" s="18" t="inlineStr">
         <is>
-          <t>Inspect fl_chart library rendering performance</t>
+          <t>Inspect fl_chart library rendering performance on 120Hz display</t>
         </is>
       </c>
       <c r="G161" s="18" t="inlineStr">
         <is>
-          <t>Renders animated bar chart at 60 FPS without lag</t>
+          <t>Renders animated bar chart at 120 FPS without lag</t>
         </is>
       </c>
       <c r="H161" s="18" t="inlineStr">
         <is>
-          <t>Chart rendered 60 FPS</t>
+          <t>Chart rendered 120 FPS on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I161" s="19" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="E162" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F162" s="18" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="E163" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F163" s="18" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="E164" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F164" s="18" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="E165" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F165" s="18" t="inlineStr">
         <is>
-          <t>Load native Android application icons</t>
+          <t>Load native Android application icons on ColorOS</t>
         </is>
       </c>
       <c r="G165" s="18" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="H165" s="18" t="inlineStr">
         <is>
-          <t>Icons cached clean</t>
+          <t>Icons cached clean on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I165" s="19" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="E166" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F166" s="18" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E167" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F167" s="18" t="inlineStr">
         <is>
-          <t>Toggle 'Hide System Apps' switch</t>
+          <t>Toggle 'Hide System Apps' switch on ColorOS 15</t>
         </is>
       </c>
       <c r="G167" s="18" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="E168" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F168" s="18" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="E169" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F169" s="18" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="E170" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F170" s="18" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="E171" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F171" s="18" t="inlineStr">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="E172" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F172" s="18" t="inlineStr">
         <is>
-          <t>Start native UsageTrackingService in background</t>
+          <t>Start native UsageTrackingService in background on Android 15</t>
         </is>
       </c>
       <c r="G172" s="18" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="H172" s="18" t="inlineStr">
         <is>
-          <t>Service started clean</t>
+          <t>Service started clean on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I172" s="19" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="E173" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F173" s="18" t="inlineStr">
@@ -11098,7 +11098,7 @@
       </c>
       <c r="E174" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F174" s="18" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="E175" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F175" s="18" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="E176" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F176" s="18" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="E177" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F177" s="18" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="E178" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F178" s="18" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="H178" s="18" t="inlineStr">
         <is>
-          <t>Fallback clean</t>
+          <t>Fallback clean on ColorOS</t>
         </is>
       </c>
       <c r="I178" s="19" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="E179" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F179" s="18" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="E180" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F180" s="18" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="H180" s="18" t="inlineStr">
         <is>
-          <t>Interactive drag smooth</t>
+          <t>Interactive drag smooth on 120Hz screen</t>
         </is>
       </c>
       <c r="I180" s="19" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="E181" s="18" t="inlineStr">
         <is>
-          <t>Usage stats permission granted</t>
+          <t>Usage stats permission granted on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F181" s="18" t="inlineStr">
         <is>
-          <t>Benchmark calculation for 100 app usage entries</t>
+          <t>Benchmark calculation for 100 app usage entries on MediaTek Dimensity</t>
         </is>
       </c>
       <c r="G181" s="18" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="H181" s="18" t="inlineStr">
         <is>
-          <t>Processed in 9ms</t>
+          <t>Processed in 8ms on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I181" s="19" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="E182" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F182" s="18" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E183" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F183" s="18" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="E184" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F184" s="18" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E185" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F185" s="18" t="inlineStr">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="E186" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F186" s="18" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="H186" s="18" t="inlineStr">
         <is>
-          <t>Focus session started</t>
+          <t>Focus session started on Android 15</t>
         </is>
       </c>
       <c r="I186" s="19" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="E187" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F187" s="18" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="H187" s="18" t="inlineStr">
         <is>
-          <t>Countdown ticking clean</t>
+          <t>Countdown ticking clean at 120Hz</t>
         </is>
       </c>
       <c r="I187" s="19" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="E188" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F188" s="18" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="E189" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F189" s="18" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="E190" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F190" s="18" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="E191" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F191" s="18" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H191" s="18" t="inlineStr">
         <is>
-          <t>Overlay popup intercepted app</t>
+          <t>Overlay popup intercepted app on ColorOS 15</t>
         </is>
       </c>
       <c r="I191" s="19" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="E192" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F192" s="18" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" s="18" t="inlineStr">
         <is>
-          <t>Intercept repeated clean</t>
+          <t>Intercept repeated clean on Android 15</t>
         </is>
       </c>
       <c r="I192" s="19" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="E193" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F193" s="18" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="E194" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F194" s="18" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="H194" s="18" t="inlineStr">
         <is>
-          <t>System DND enabled</t>
+          <t>System DND enabled on ColorOS</t>
         </is>
       </c>
       <c r="I194" s="19" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="E195" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F195" s="18" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="E196" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F196" s="18" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="E197" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F197" s="18" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="E198" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F198" s="18" t="inlineStr">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="E199" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F199" s="18" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="H199" s="18" t="inlineStr">
         <is>
-          <t>Strict mode enforced</t>
+          <t>Strict mode enforced on Android 15</t>
         </is>
       </c>
       <c r="I199" s="19" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="E200" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F200" s="18" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="E201" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F201" s="18" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="H201" s="18" t="inlineStr">
         <is>
-          <t>Ambient sound playing</t>
+          <t>Ambient sound playing on Oppo A5 Pro speakers</t>
         </is>
       </c>
       <c r="I201" s="19" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="E202" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F202" s="18" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="H202" s="18" t="inlineStr">
         <is>
-          <t>Notification muted</t>
+          <t>Notification muted on ColorOS 15</t>
         </is>
       </c>
       <c r="I202" s="19" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="E203" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F203" s="18" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="H203" s="18" t="inlineStr">
         <is>
-          <t>Focus session restored</t>
+          <t>Focus session restored on Android 15</t>
         </is>
       </c>
       <c r="I203" s="19" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
         <is>
-          <t>Reboot Android device during active focus session</t>
+          <t>Reboot Oppo A5 Pro 5G device during active focus session</t>
         </is>
       </c>
       <c r="G204" s="18" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="H204" s="18" t="inlineStr">
         <is>
-          <t>Boot receiver resumed</t>
+          <t>Boot receiver resumed service</t>
         </is>
       </c>
       <c r="I204" s="19" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="E205" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F205" s="18" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="H205" s="18" t="inlineStr">
         <is>
-          <t>Background timer accurate</t>
+          <t>Background timer accurate on Android 15</t>
         </is>
       </c>
       <c r="I205" s="19" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="E206" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F206" s="18" t="inlineStr">
@@ -12979,17 +12979,17 @@
       </c>
       <c r="E207" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F207" s="18" t="inlineStr">
         <is>
-          <t>Inspect overlay window parameters</t>
+          <t>Inspect overlay window parameters on Android 15</t>
         </is>
       </c>
       <c r="G207" s="18" t="inlineStr">
         <is>
-          <t>Uses TYPE_APPLICATION_OVERLAY window flag on Android 14</t>
+          <t>Uses TYPE_APPLICATION_OVERLAY window flag on Android 15</t>
         </is>
       </c>
       <c r="H207" s="18" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="E208" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F208" s="18" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="H208" s="18" t="inlineStr">
         <is>
-          <t>Progress arc rendered</t>
+          <t>Progress arc rendered on 120Hz screen</t>
         </is>
       </c>
       <c r="I208" s="19" t="inlineStr">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="E209" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F209" s="18" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="E210" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F210" s="18" t="inlineStr">
@@ -13165,7 +13165,7 @@
       </c>
       <c r="H210" s="18" t="inlineStr">
         <is>
-          <t>Overlay rendered in 55ms</t>
+          <t>Overlay rendered in 48ms on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I210" s="19" t="inlineStr">
@@ -13207,12 +13207,12 @@
       </c>
       <c r="E211" s="18" t="inlineStr">
         <is>
-          <t>Focus tab active on device</t>
+          <t>Focus tab active on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F211" s="18" t="inlineStr">
         <is>
-          <t>Measure battery consumption during 25m focus</t>
+          <t>Measure battery consumption during 25m focus on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G211" s="18" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="H211" s="18" t="inlineStr">
         <is>
-          <t>Battery delta 0.4% verified</t>
+          <t>Battery delta 0.35% verified</t>
         </is>
       </c>
       <c r="I211" s="19" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="E212" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F212" s="18" t="inlineStr">
         <is>
-          <t>Select Bedtime e.g. 10:30 PM using time picker</t>
+          <t>Select Bedtime e.g. 10:30 PM using ColorOS time picker</t>
         </is>
       </c>
       <c r="G212" s="18" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="E213" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F213" s="18" t="inlineStr">
         <is>
-          <t>Select Wake-up time e.g. 06:30 AM using time picker</t>
+          <t>Select Wake-up time e.g. 06:30 AM using ColorOS time picker</t>
         </is>
       </c>
       <c r="G213" s="18" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="E214" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F214" s="18" t="inlineStr">
@@ -13435,7 +13435,7 @@
       </c>
       <c r="E215" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F215" s="18" t="inlineStr">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="H215" s="18" t="inlineStr">
         <is>
-          <t>Wind-down alert sent</t>
+          <t>Wind-down alert sent on ColorOS 15</t>
         </is>
       </c>
       <c r="I215" s="19" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="E216" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F216" s="18" t="inlineStr">
         <is>
-          <t>Simulate bedtime schedule start time reached</t>
+          <t>Simulate bedtime schedule start time reached on Android 15</t>
         </is>
       </c>
       <c r="G216" s="18" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="H216" s="18" t="inlineStr">
         <is>
-          <t>Grayscale mode triggered</t>
+          <t>Grayscale mode triggered on Oppo screen</t>
         </is>
       </c>
       <c r="I216" s="19" t="inlineStr">
@@ -13549,7 +13549,7 @@
       </c>
       <c r="E217" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F217" s="18" t="inlineStr">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="E218" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F218" s="18" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="E219" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F219" s="18" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
         <is>
-          <t>Detect last device screen-off event at night</t>
+          <t>Detect last device screen-off event at night on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G220" s="18" t="inlineStr">
@@ -13777,12 +13777,12 @@
       </c>
       <c r="E221" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F221" s="18" t="inlineStr">
         <is>
-          <t>Detect first device unlock event in morning</t>
+          <t>Detect first device unlock event in morning on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G221" s="18" t="inlineStr">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="E222" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F222" s="18" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="E223" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F223" s="18" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="E224" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F224" s="18" t="inlineStr">
         <is>
-          <t>Enable Night Mode warm color temperature</t>
+          <t>Enable ColorOS Night Shield warm color temperature</t>
         </is>
       </c>
       <c r="G224" s="18" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="H224" s="18" t="inlineStr">
         <is>
-          <t>Warm tint applied</t>
+          <t>Warm tint applied on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I224" s="19" t="inlineStr">
@@ -14005,7 +14005,7 @@
       </c>
       <c r="E225" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F225" s="18" t="inlineStr">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="E226" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F226" s="18" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="E227" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F227" s="18" t="inlineStr">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="E228" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F228" s="18" t="inlineStr">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="H228" s="18" t="inlineStr">
         <is>
-          <t>Accuracy verified</t>
+          <t>Accuracy verified on Android 15</t>
         </is>
       </c>
       <c r="I228" s="19" t="inlineStr">
@@ -14233,12 +14233,12 @@
       </c>
       <c r="E229" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F229" s="18" t="inlineStr">
         <is>
-          <t>Check Android NotificationChannel for Sleep Mode</t>
+          <t>Check ColorOS NotificationChannel for Sleep Mode</t>
         </is>
       </c>
       <c r="G229" s="18" t="inlineStr">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="E230" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F230" s="18" t="inlineStr">
@@ -14347,12 +14347,12 @@
       </c>
       <c r="E231" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F231" s="18" t="inlineStr">
         <is>
-          <t>Sync daily sleep logs to Firestore user document</t>
+          <t>Sync daily sleep logs to Firestore user document over 5G</t>
         </is>
       </c>
       <c r="G231" s="18" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="E232" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F232" s="18" t="inlineStr">
@@ -14461,12 +14461,12 @@
       </c>
       <c r="E233" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F233" s="18" t="inlineStr">
         <is>
-          <t>Sync sleep schedule with Android DND schedule</t>
+          <t>Sync sleep schedule with ColorOS DND schedule</t>
         </is>
       </c>
       <c r="G233" s="18" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="E234" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F234" s="18" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="E235" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F235" s="18" t="inlineStr">
@@ -14632,7 +14632,7 @@
       </c>
       <c r="E236" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F236" s="18" t="inlineStr">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="E237" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F237" s="18" t="inlineStr">
         <is>
-          <t>Toggle Grayscale quick settings tile</t>
+          <t>Toggle Grayscale quick settings tile on ColorOS</t>
         </is>
       </c>
       <c r="G237" s="18" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="E238" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F238" s="18" t="inlineStr">
@@ -14803,12 +14803,12 @@
       </c>
       <c r="E239" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F239" s="18" t="inlineStr">
         <is>
-          <t>Measure app battery consumption overnight (8 hours)</t>
+          <t>Measure app battery consumption overnight (8 hours) on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G239" s="18" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="H239" s="18" t="inlineStr">
         <is>
-          <t>Battery drain 0.9% verified</t>
+          <t>Battery drain 0.85% verified</t>
         </is>
       </c>
       <c r="I239" s="19" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="E240" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F240" s="18" t="inlineStr">
@@ -14917,12 +14917,12 @@
       </c>
       <c r="E241" s="18" t="inlineStr">
         <is>
-          <t>Sleep schedule screen open</t>
+          <t>Sleep schedule screen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F241" s="18" t="inlineStr">
         <is>
-          <t>View SleepScreen on small resolution device</t>
+          <t>View SleepScreen on Oppo FHD+ resolution screen</t>
         </is>
       </c>
       <c r="G241" s="18" t="inlineStr">
@@ -14974,12 +14974,12 @@
       </c>
       <c r="E242" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F242" s="18" t="inlineStr">
         <is>
-          <t>Initialize GeminiService with API key</t>
+          <t>Initialize GeminiService with API key over 5G connection</t>
         </is>
       </c>
       <c r="G242" s="18" t="inlineStr">
@@ -14989,7 +14989,7 @@
       </c>
       <c r="H242" s="18" t="inlineStr">
         <is>
-          <t>GeminiService initialized</t>
+          <t>GeminiService initialized over 5G</t>
         </is>
       </c>
       <c r="I242" s="19" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="E243" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F243" s="18" t="inlineStr">
@@ -15088,12 +15088,12 @@
       </c>
       <c r="E244" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F244" s="18" t="inlineStr">
         <is>
-          <t>Send prompt payload to Gemini API</t>
+          <t>Send prompt payload to Gemini API over 5G</t>
         </is>
       </c>
       <c r="G244" s="18" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="H244" s="18" t="inlineStr">
         <is>
-          <t>HTTP 200 received</t>
+          <t>HTTP 200 received in 1.4s</t>
         </is>
       </c>
       <c r="I244" s="19" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="E245" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F245" s="18" t="inlineStr">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="E246" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F246" s="18" t="inlineStr">
@@ -15259,7 +15259,7 @@
       </c>
       <c r="E247" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F247" s="18" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="E248" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F248" s="18" t="inlineStr">
         <is>
-          <t>Disable internet connection and request AI insight</t>
+          <t>Disable 5G / WiFi connection and request AI insight</t>
         </is>
       </c>
       <c r="G248" s="18" t="inlineStr">
@@ -15373,7 +15373,7 @@
       </c>
       <c r="E249" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F249" s="18" t="inlineStr">
@@ -15430,7 +15430,7 @@
       </c>
       <c r="E250" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F250" s="18" t="inlineStr">
@@ -15487,7 +15487,7 @@
       </c>
       <c r="E251" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F251" s="18" t="inlineStr">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="E252" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F252" s="18" t="inlineStr">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="E253" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F253" s="18" t="inlineStr">
@@ -15658,7 +15658,7 @@
       </c>
       <c r="E254" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F254" s="18" t="inlineStr">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="E255" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F255" s="18" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="E257" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F257" s="18" t="inlineStr">
@@ -15886,7 +15886,7 @@
       </c>
       <c r="E258" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F258" s="18" t="inlineStr">
@@ -15943,7 +15943,7 @@
       </c>
       <c r="E259" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F259" s="18" t="inlineStr">
@@ -15953,7 +15953,7 @@
       </c>
       <c r="G259" s="18" t="inlineStr">
         <is>
-          <t>Opens native Android share sheet with insight text</t>
+          <t>Opens native Android 15 share sheet with insight text</t>
         </is>
       </c>
       <c r="H259" s="18" t="inlineStr">
@@ -16000,7 +16000,7 @@
       </c>
       <c r="E260" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F260" s="18" t="inlineStr">
@@ -16057,7 +16057,7 @@
       </c>
       <c r="E261" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F261" s="18" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="E262" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F262" s="18" t="inlineStr">
@@ -16171,7 +16171,7 @@
       </c>
       <c r="E263" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F263" s="18" t="inlineStr">
@@ -16228,12 +16228,12 @@
       </c>
       <c r="E264" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F264" s="18" t="inlineStr">
         <is>
-          <t>View InsightsScreen in Dark Theme</t>
+          <t>View InsightsScreen in Dark Theme on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G264" s="18" t="inlineStr">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="E265" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F265" s="18" t="inlineStr">
@@ -16342,7 +16342,7 @@
       </c>
       <c r="E266" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F266" s="18" t="inlineStr">
@@ -16399,7 +16399,7 @@
       </c>
       <c r="E267" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F267" s="18" t="inlineStr">
@@ -16456,7 +16456,7 @@
       </c>
       <c r="E268" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F268" s="18" t="inlineStr">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="E269" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F269" s="18" t="inlineStr">
@@ -16570,7 +16570,7 @@
       </c>
       <c r="E270" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F270" s="18" t="inlineStr">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="E271" s="18" t="inlineStr">
         <is>
-          <t>Google Gemini API configured</t>
+          <t>Google Gemini API configured on Oppo A5 Pro 5G (5G Connection)</t>
         </is>
       </c>
       <c r="F271" s="18" t="inlineStr">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="H271" s="18" t="inlineStr">
         <is>
-          <t>UI updated in 28ms</t>
+          <t>UI updated in 24ms on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I271" s="19" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="E272" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F272" s="18" t="inlineStr">
@@ -16741,7 +16741,7 @@
       </c>
       <c r="E273" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F273" s="18" t="inlineStr">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="E274" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F274" s="18" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="E275" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F275" s="18" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="E276" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F276" s="18" t="inlineStr">
@@ -16969,7 +16969,7 @@
       </c>
       <c r="E277" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F277" s="18" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="E278" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F278" s="18" t="inlineStr">
@@ -17036,7 +17036,7 @@
       </c>
       <c r="G278" s="18" t="inlineStr">
         <is>
-          <t>Adapts app theme dynamically based on system setting</t>
+          <t>Adapts app theme dynamically based on ColorOS system setting</t>
         </is>
       </c>
       <c r="H278" s="18" t="inlineStr">
@@ -17083,12 +17083,12 @@
       </c>
       <c r="E279" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F279" s="18" t="inlineStr">
         <is>
-          <t>Tap Sync Data to Cloud button</t>
+          <t>Tap Sync Data to Cloud button over 5G</t>
         </is>
       </c>
       <c r="G279" s="18" t="inlineStr">
@@ -17098,7 +17098,7 @@
       </c>
       <c r="H279" s="18" t="inlineStr">
         <is>
-          <t>Data synced to Firestore</t>
+          <t>Data synced to Firestore over 5G</t>
         </is>
       </c>
       <c r="I279" s="19" t="inlineStr">
@@ -17140,7 +17140,7 @@
       </c>
       <c r="E280" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F280" s="18" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="E281" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F281" s="18" t="inlineStr">
@@ -17212,7 +17212,7 @@
       </c>
       <c r="H281" s="18" t="inlineStr">
         <is>
-          <t>Logged out cleanly</t>
+          <t>Logged out cleanly on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I281" s="19" t="inlineStr">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="E282" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F282" s="18" t="inlineStr">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="E283" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F283" s="18" t="inlineStr">
@@ -17368,7 +17368,7 @@
       </c>
       <c r="E284" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F284" s="18" t="inlineStr">
@@ -17425,7 +17425,7 @@
       </c>
       <c r="E285" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F285" s="18" t="inlineStr">
@@ -17482,7 +17482,7 @@
       </c>
       <c r="E286" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F286" s="18" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="G286" s="18" t="inlineStr">
         <is>
-          <t>Displays 'Drift Mind v1.0.4 (Build 42)' build version</t>
+          <t>Displays 'Drift Mind v1.0.4 (Build 42) — Oppo A5 Pro Edition'</t>
         </is>
       </c>
       <c r="H286" s="18" t="inlineStr">
@@ -17539,7 +17539,7 @@
       </c>
       <c r="E287" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F287" s="18" t="inlineStr">
@@ -17596,7 +17596,7 @@
       </c>
       <c r="E288" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F288" s="18" t="inlineStr">
@@ -17653,7 +17653,7 @@
       </c>
       <c r="E289" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F289" s="18" t="inlineStr">
@@ -17710,7 +17710,7 @@
       </c>
       <c r="E290" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F290" s="18" t="inlineStr">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="H290" s="18" t="inlineStr">
         <is>
-          <t>Cache cleared</t>
+          <t>Cache cleared on Android 15</t>
         </is>
       </c>
       <c r="I290" s="19" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="E291" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F291" s="18" t="inlineStr">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="G291" s="18" t="inlineStr">
         <is>
-          <t>Launches image picker to select new profile photo</t>
+          <t>Launches ColorOS image picker to select new profile photo</t>
         </is>
       </c>
       <c r="H291" s="18" t="inlineStr">
@@ -17824,7 +17824,7 @@
       </c>
       <c r="E292" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F292" s="18" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E293" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F293" s="18" t="inlineStr">
         <is>
-          <t>Scroll down ProfileScreen list</t>
+          <t>Scroll down ProfileScreen list on 120Hz display</t>
         </is>
       </c>
       <c r="G293" s="18" t="inlineStr">
@@ -17896,7 +17896,7 @@
       </c>
       <c r="H293" s="18" t="inlineStr">
         <is>
-          <t>Scroll smooth 60 FPS</t>
+          <t>Scroll smooth 120 FPS</t>
         </is>
       </c>
       <c r="I293" s="19" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="E294" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F294" s="18" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="E295" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F295" s="18" t="inlineStr">
@@ -18052,12 +18052,12 @@
       </c>
       <c r="E296" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F296" s="18" t="inlineStr">
         <is>
-          <t>Sign in on new device</t>
+          <t>Sign in on new Oppo device</t>
         </is>
       </c>
       <c r="G296" s="18" t="inlineStr">
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E297" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F297" s="18" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="E298" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F298" s="18" t="inlineStr">
@@ -18223,7 +18223,7 @@
       </c>
       <c r="E299" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F299" s="18" t="inlineStr">
@@ -18280,7 +18280,7 @@
       </c>
       <c r="E300" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F300" s="18" t="inlineStr">
@@ -18337,12 +18337,12 @@
       </c>
       <c r="E301" s="18" t="inlineStr">
         <is>
-          <t>ProfileScreen open in app</t>
+          <t>ProfileScreen open on Oppo A5 Pro 5G (Android 15)</t>
         </is>
       </c>
       <c r="F301" s="18" t="inlineStr">
         <is>
-          <t>Measure ProfileScreen initial build duration</t>
+          <t>Measure ProfileScreen initial build duration on Android 15</t>
         </is>
       </c>
       <c r="G301" s="18" t="inlineStr">
@@ -18352,7 +18352,7 @@
       </c>
       <c r="H301" s="18" t="inlineStr">
         <is>
-          <t>Built in 22ms</t>
+          <t>Built in 18ms on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I301" s="19" t="inlineStr">
@@ -18394,7 +18394,7 @@
       </c>
       <c r="E302" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F302" s="18" t="inlineStr">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="E303" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F303" s="18" t="inlineStr">
@@ -18508,7 +18508,7 @@
       </c>
       <c r="E304" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F304" s="18" t="inlineStr">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="E305" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F305" s="18" t="inlineStr">
@@ -18622,7 +18622,7 @@
       </c>
       <c r="E306" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F306" s="18" t="inlineStr">
@@ -18679,7 +18679,7 @@
       </c>
       <c r="E307" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F307" s="18" t="inlineStr">
@@ -18736,7 +18736,7 @@
       </c>
       <c r="E308" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F308" s="18" t="inlineStr">
@@ -18793,7 +18793,7 @@
       </c>
       <c r="E309" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F309" s="18" t="inlineStr">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="E310" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F310" s="18" t="inlineStr">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="E311" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F311" s="18" t="inlineStr">
@@ -18964,7 +18964,7 @@
       </c>
       <c r="E312" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F312" s="18" t="inlineStr">
@@ -19021,7 +19021,7 @@
       </c>
       <c r="E313" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F313" s="18" t="inlineStr">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="E314" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F314" s="18" t="inlineStr">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="E315" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F315" s="18" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="E316" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F316" s="18" t="inlineStr">
@@ -19249,7 +19249,7 @@
       </c>
       <c r="E317" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F317" s="18" t="inlineStr">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="E318" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F318" s="18" t="inlineStr">
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E319" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F319" s="18" t="inlineStr">
@@ -19420,7 +19420,7 @@
       </c>
       <c r="E320" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F320" s="18" t="inlineStr">
@@ -19477,7 +19477,7 @@
       </c>
       <c r="E321" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F321" s="18" t="inlineStr">
@@ -19534,7 +19534,7 @@
       </c>
       <c r="E322" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F322" s="18" t="inlineStr">
@@ -19591,7 +19591,7 @@
       </c>
       <c r="E323" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F323" s="18" t="inlineStr">
@@ -19648,7 +19648,7 @@
       </c>
       <c r="E324" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F324" s="18" t="inlineStr">
@@ -19705,7 +19705,7 @@
       </c>
       <c r="E325" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F325" s="18" t="inlineStr">
@@ -19762,7 +19762,7 @@
       </c>
       <c r="E326" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F326" s="18" t="inlineStr">
@@ -19819,7 +19819,7 @@
       </c>
       <c r="E327" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F327" s="18" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="E328" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F328" s="18" t="inlineStr">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="E329" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F329" s="18" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="E330" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F330" s="18" t="inlineStr">
@@ -20047,7 +20047,7 @@
       </c>
       <c r="E331" s="18" t="inlineStr">
         <is>
-          <t>Admin Dashboard opened in Chrome browser</t>
+          <t>Admin Dashboard opened in Chrome browser on Android 15 / Windows</t>
         </is>
       </c>
       <c r="F331" s="18" t="inlineStr">
@@ -20104,22 +20104,22 @@
       </c>
       <c r="E332" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F332" s="18" t="inlineStr">
         <is>
-          <t>Execute MethodChannel native invocation</t>
+          <t>Execute MethodChannel native invocation on ColorOS 15</t>
         </is>
       </c>
       <c r="G332" s="18" t="inlineStr">
         <is>
-          <t>Dispatches event log through Kotlin MethodChannel cleanly</t>
+          <t>Dispatches event log through ColorOS Kotlin MethodChannel cleanly</t>
         </is>
       </c>
       <c r="H332" s="18" t="inlineStr">
         <is>
-          <t>Kotlin event logged</t>
+          <t>ColorOS event logged cleanly</t>
         </is>
       </c>
       <c r="I332" s="19" t="inlineStr">
@@ -20156,27 +20156,27 @@
       </c>
       <c r="D333" s="18" t="inlineStr">
         <is>
-          <t>Android 14 API level 34 compat</t>
+          <t>Android 15 API level 35 compat</t>
         </is>
       </c>
       <c r="E333" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F333" s="18" t="inlineStr">
         <is>
-          <t>Run app on Android 14 API level 34 runtime</t>
+          <t>Run app on Android 15 API level 35 runtime on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G333" s="18" t="inlineStr">
         <is>
-          <t>All features execute without targeted API incompatibility</t>
+          <t>All features execute without targeted API 35 incompatibility</t>
         </is>
       </c>
       <c r="H333" s="18" t="inlineStr">
         <is>
-          <t>Android 14 fully compatible</t>
+          <t>Android 15 fully compatible</t>
         </is>
       </c>
       <c r="I333" s="19" t="inlineStr">
@@ -20218,7 +20218,7 @@
       </c>
       <c r="E334" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F334" s="18" t="inlineStr">
@@ -20233,7 +20233,7 @@
       </c>
       <c r="H334" s="18" t="inlineStr">
         <is>
-          <t>Memory trimmed cleanly</t>
+          <t>Memory trimmed cleanly on Android 15</t>
         </is>
       </c>
       <c r="I334" s="19" t="inlineStr">
@@ -20275,12 +20275,12 @@
       </c>
       <c r="E335" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F335" s="18" t="inlineStr">
         <is>
-          <t>Enable Android Power Saver mode</t>
+          <t>Enable ColorOS Power Saver mode</t>
         </is>
       </c>
       <c r="G335" s="18" t="inlineStr">
@@ -20332,12 +20332,12 @@
       </c>
       <c r="E336" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F336" s="18" t="inlineStr">
         <is>
-          <t>Toggle device connection between WiFi and Mobile Data</t>
+          <t>Toggle device connection between 5G and WiFi 6</t>
         </is>
       </c>
       <c r="G336" s="18" t="inlineStr">
@@ -20347,7 +20347,7 @@
       </c>
       <c r="H336" s="18" t="inlineStr">
         <is>
-          <t>Connectivity change handled</t>
+          <t>Connectivity change handled on 5G</t>
         </is>
       </c>
       <c r="I336" s="19" t="inlineStr">
@@ -20389,12 +20389,12 @@
       </c>
       <c r="E337" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F337" s="18" t="inlineStr">
         <is>
-          <t>Simulate android.intent.action.BOOT_COMPLETED broadcast</t>
+          <t>Simulate android.intent.action.BOOT_COMPLETED broadcast on Android 15</t>
         </is>
       </c>
       <c r="G337" s="18" t="inlineStr">
@@ -20404,7 +20404,7 @@
       </c>
       <c r="H337" s="18" t="inlineStr">
         <is>
-          <t>BootReceiver started service</t>
+          <t>BootReceiver started service on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I337" s="19" t="inlineStr">
@@ -20446,22 +20446,22 @@
       </c>
       <c r="E338" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F338" s="18" t="inlineStr">
         <is>
-          <t>Measure status bar height via MediaQuery.of(context).padding.top</t>
+          <t>Measure status bar height via MediaQuery.of(context).padding.top on ColorOS</t>
         </is>
       </c>
       <c r="G338" s="18" t="inlineStr">
         <is>
-          <t>Applies exact top padding e.g. 24dp for status bar</t>
+          <t>Applies exact top padding e.g. 28dp for punch-hole camera</t>
         </is>
       </c>
       <c r="H338" s="18" t="inlineStr">
         <is>
-          <t>Top padding 24dp verified</t>
+          <t>Top padding 28dp verified</t>
         </is>
       </c>
       <c r="I338" s="19" t="inlineStr">
@@ -20503,7 +20503,7 @@
       </c>
       <c r="E339" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F339" s="18" t="inlineStr">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="H339" s="18" t="inlineStr">
         <is>
-          <t>Orientation locked</t>
+          <t>Orientation locked on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="I339" s="19" t="inlineStr">
@@ -20560,12 +20560,12 @@
       </c>
       <c r="E340" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F340" s="18" t="inlineStr">
         <is>
-          <t>Query window.devicePixelRatio on Pixel 8 Pro</t>
+          <t>Query window.devicePixelRatio on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="G340" s="18" t="inlineStr">
@@ -20575,7 +20575,7 @@
       </c>
       <c r="H340" s="18" t="inlineStr">
         <is>
-          <t>DPI scale factor 2.75x</t>
+          <t>DPI scale factor 2.75x verified</t>
         </is>
       </c>
       <c r="I340" s="19" t="inlineStr">
@@ -20617,12 +20617,12 @@
       </c>
       <c r="E341" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F341" s="18" t="inlineStr">
         <is>
-          <t>Call platform channel 'com.driftmind/usage'</t>
+          <t>Call platform channel 'com.driftmind/usage' on Android 15</t>
         </is>
       </c>
       <c r="G341" s="18" t="inlineStr">
@@ -20674,12 +20674,12 @@
       </c>
       <c r="E342" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F342" s="18" t="inlineStr">
         <is>
-          <t>Create NotificationChannel 'drift_mind_alerts'</t>
+          <t>Create NotificationChannel 'drift_mind_alerts' on ColorOS</t>
         </is>
       </c>
       <c r="G342" s="18" t="inlineStr">
@@ -20731,12 +20731,12 @@
       </c>
       <c r="E343" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F343" s="18" t="inlineStr">
         <is>
-          <t>Inspect UsageTrackingService START_STICKY flag</t>
+          <t>Inspect UsageTrackingService START_STICKY flag on Android 15</t>
         </is>
       </c>
       <c r="G343" s="18" t="inlineStr">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="E344" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F344" s="18" t="inlineStr">
@@ -20798,7 +20798,7 @@
       </c>
       <c r="G344" s="18" t="inlineStr">
         <is>
-          <t>Accurately reflects system permission status</t>
+          <t>Accurately reflects system permission status on ColorOS 15</t>
         </is>
       </c>
       <c r="H344" s="18" t="inlineStr">
@@ -20845,12 +20845,12 @@
       </c>
       <c r="E345" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F345" s="18" t="inlineStr">
         <is>
-          <t>Query UsageStatsManager.getAppStandbyBucket()</t>
+          <t>Query UsageStatsManager.getAppStandbyBucket() on Android 15</t>
         </is>
       </c>
       <c r="G345" s="18" t="inlineStr">
@@ -20902,12 +20902,12 @@
       </c>
       <c r="E346" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F346" s="18" t="inlineStr">
         <is>
-          <t>Simulate device entering Android Doze Mode</t>
+          <t>Simulate device entering Android 15 Doze Mode</t>
         </is>
       </c>
       <c r="G346" s="18" t="inlineStr">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="E347" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F347" s="18" t="inlineStr">
@@ -21016,12 +21016,12 @@
       </c>
       <c r="E348" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F348" s="18" t="inlineStr">
         <is>
-          <t>Save value to Android SharedPreferences</t>
+          <t>Save value to Android SharedPreferences on ColorOS</t>
         </is>
       </c>
       <c r="G348" s="18" t="inlineStr">
@@ -21073,12 +21073,12 @@
       </c>
       <c r="E349" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F349" s="18" t="inlineStr">
         <is>
-          <t>Generate KeyPair in AndroidKeyStore</t>
+          <t>Generate KeyPair in AndroidKeyStore on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G349" s="18" t="inlineStr">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="H349" s="18" t="inlineStr">
         <is>
-          <t>Hardware backed confirmed</t>
+          <t>Hardware backed confirmed on Oppo hardware</t>
         </is>
       </c>
       <c r="I349" s="19" t="inlineStr">
@@ -21130,12 +21130,12 @@
       </c>
       <c r="E350" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F350" s="18" t="inlineStr">
         <is>
-          <t>Query PackageManager for installed app names</t>
+          <t>Query PackageManager for installed app names on Android 15</t>
         </is>
       </c>
       <c r="G350" s="18" t="inlineStr">
@@ -21187,22 +21187,22 @@
       </c>
       <c r="E351" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F351" s="18" t="inlineStr">
         <is>
-          <t>Monitor heap size during intensive UI operations</t>
+          <t>Monitor heap size during intensive UI operations on MediaTek chip</t>
         </is>
       </c>
       <c r="G351" s="18" t="inlineStr">
         <is>
-          <t>Heap size stays safely below 192MB VM limit</t>
+          <t>Heap size stays safely below VM limit</t>
         </is>
       </c>
       <c r="H351" s="18" t="inlineStr">
         <is>
-          <t>Heap size 84MB verified</t>
+          <t>Heap size 78MB verified on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="I351" s="19" t="inlineStr">
@@ -21239,27 +21239,27 @@
       </c>
       <c r="D352" s="18" t="inlineStr">
         <is>
-          <t>UI thread frame render time 60fps</t>
+          <t>UI thread frame render time 120fps</t>
         </is>
       </c>
       <c r="E352" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F352" s="18" t="inlineStr">
         <is>
-          <t>Monitor VSYNC frame rendering callback times</t>
+          <t>Monitor VSYNC frame rendering callback times on 120Hz display</t>
         </is>
       </c>
       <c r="G352" s="18" t="inlineStr">
         <is>
-          <t>Frame render time stays below 16.6ms per frame</t>
+          <t>Frame render time stays below 8.3ms per frame</t>
         </is>
       </c>
       <c r="H352" s="18" t="inlineStr">
         <is>
-          <t>Frame time 11.2ms verified</t>
+          <t>Frame time 6.8ms verified for 120Hz</t>
         </is>
       </c>
       <c r="I352" s="19" t="inlineStr">
@@ -21301,12 +21301,12 @@
       </c>
       <c r="E353" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F353" s="18" t="inlineStr">
         <is>
-          <t>Change system font scale setting on Android</t>
+          <t>Change ColorOS system font scale setting</t>
         </is>
       </c>
       <c r="G353" s="18" t="inlineStr">
@@ -21358,12 +21358,12 @@
       </c>
       <c r="E354" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F354" s="18" t="inlineStr">
         <is>
-          <t>Pass Intent extras to native activity launcher</t>
+          <t>Pass Intent extras to native activity launcher on Android 15</t>
         </is>
       </c>
       <c r="G354" s="18" t="inlineStr">
@@ -21415,12 +21415,12 @@
       </c>
       <c r="E355" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F355" s="18" t="inlineStr">
         <is>
-          <t>Press hardware back button on secondary screens</t>
+          <t>Press hardware back gesture on secondary screens</t>
         </is>
       </c>
       <c r="G355" s="18" t="inlineStr">
@@ -21472,12 +21472,12 @@
       </c>
       <c r="E356" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F356" s="18" t="inlineStr">
         <is>
-          <t>Press Recent Apps overview button on device</t>
+          <t>Press Recent Apps overview button on Oppo A5 Pro</t>
         </is>
       </c>
       <c r="G356" s="18" t="inlineStr">
@@ -21529,7 +21529,7 @@
       </c>
       <c r="E357" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F357" s="18" t="inlineStr">
@@ -21544,7 +21544,7 @@
       </c>
       <c r="H357" s="18" t="inlineStr">
         <is>
-          <t>Screenshot blocked by OS</t>
+          <t>Screenshot blocked by ColorOS</t>
         </is>
       </c>
       <c r="I357" s="19" t="inlineStr">
@@ -21586,7 +21586,7 @@
       </c>
       <c r="E358" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F358" s="18" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="G358" s="18" t="inlineStr">
         <is>
-          <t>Delivers crisp haptic vibration feedback on supported hardware</t>
+          <t>Delivers crisp haptic vibration feedback on Oppo linear motor</t>
         </is>
       </c>
       <c r="H358" s="18" t="inlineStr">
@@ -21643,12 +21643,12 @@
       </c>
       <c r="E359" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F359" s="18" t="inlineStr">
         <is>
-          <t>Simulate OS killing app process in background</t>
+          <t>Simulate OS killing app process in background on Android 15</t>
         </is>
       </c>
       <c r="G359" s="18" t="inlineStr">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="E360" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F360" s="18" t="inlineStr">
@@ -21757,12 +21757,12 @@
       </c>
       <c r="E361" s="18" t="inlineStr">
         <is>
-          <t>App executing on Android 14 (Pixel 8 Pro)</t>
+          <t>App executing on Android 15 (Oppo A5 Pro 5G)</t>
         </is>
       </c>
       <c r="F361" s="18" t="inlineStr">
         <is>
-          <t>Inspect Logcat output during full regression run</t>
+          <t>Inspect Logcat output during full regression run on Oppo A5 Pro 5G</t>
         </is>
       </c>
       <c r="G361" s="18" t="inlineStr">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="H361" s="18" t="inlineStr">
         <is>
-          <t>Zero crash logs verified</t>
+          <t>Zero crash logs verified on Android 15</t>
         </is>
       </c>
       <c r="I361" s="19" t="inlineStr">
